--- a/Data/EXCEL/Transfer/salemon/202206/5277-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/5277-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{63A20CCC-69F9-49A1-8323-C286185E9ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A5E2B8E-76E8-4692-9A36-9CCF9D156D03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="5277-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -261,7 +261,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -277,7 +277,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -1218,19 +1218,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q126"/>
+  <dimension ref="A1:Q127"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="10.5" customWidth="1"/>
-    <col min="10" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="10.5" customWidth="1"/>
-    <col min="15" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="11.375" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="5" width="12.5" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="13.75" customWidth="1"/>
+    <col min="8" max="8" width="12.5" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="13" width="12.5" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="16" width="12.5" customWidth="1"/>
+    <col min="17" max="17" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1383,2816 +1383,2816 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>13.35</v>
+        <v>13.8</v>
       </c>
       <c r="C5" s="7">
-        <v>13.8</v>
+        <v>11.05</v>
       </c>
       <c r="D5" s="7">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="E5" s="7">
-        <v>12.65</v>
+        <v>10.6</v>
       </c>
       <c r="F5" s="8">
-        <v>0.45</v>
+        <v>-2.75</v>
       </c>
       <c r="G5" s="8">
-        <v>3.37</v>
+        <v>-19.93</v>
       </c>
       <c r="H5" s="9">
-        <v>0.65200000000000002</v>
+        <v>0.60499999999999998</v>
       </c>
       <c r="I5" s="8">
-        <v>6.47</v>
-      </c>
-      <c r="J5" s="10">
-        <v>-32.700000000000003</v>
+        <v>-7.13</v>
+      </c>
+      <c r="J5" s="8">
+        <v>-33.4</v>
       </c>
       <c r="K5" s="9">
-        <v>2.82</v>
-      </c>
-      <c r="L5" s="10">
-        <v>-28.4</v>
+        <v>3.43</v>
+      </c>
+      <c r="L5" s="8">
+        <v>-29.3</v>
       </c>
       <c r="M5" s="9">
-        <v>0.65200000000000002</v>
+        <v>0.60499999999999998</v>
       </c>
       <c r="N5" s="8">
-        <v>6.47</v>
-      </c>
-      <c r="O5" s="10">
-        <v>-32.700000000000003</v>
+        <v>-7.13</v>
+      </c>
+      <c r="O5" s="8">
+        <v>-33.4</v>
       </c>
       <c r="P5" s="9">
-        <v>2.82</v>
-      </c>
-      <c r="Q5" s="10">
-        <v>-28.4</v>
+        <v>3.43</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>-29.3</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>15.9</v>
+        <v>13.35</v>
       </c>
       <c r="C6" s="7">
-        <v>13.35</v>
+        <v>13.8</v>
       </c>
       <c r="D6" s="7">
-        <v>16.25</v>
+        <v>14.4</v>
       </c>
       <c r="E6" s="7">
-        <v>12.9</v>
+        <v>12.65</v>
       </c>
       <c r="F6" s="10">
-        <v>-2.5499999999999998</v>
+        <v>0.45</v>
       </c>
       <c r="G6" s="10">
-        <v>-16.04</v>
+        <v>3.37</v>
       </c>
       <c r="H6" s="9">
-        <v>0.61199999999999999</v>
-      </c>
-      <c r="I6" s="8">
-        <v>7.8</v>
-      </c>
-      <c r="J6" s="10">
-        <v>-22.8</v>
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="I6" s="10">
+        <v>6.47</v>
+      </c>
+      <c r="J6" s="8">
+        <v>-32.700000000000003</v>
       </c>
       <c r="K6" s="9">
-        <v>2.17</v>
-      </c>
-      <c r="L6" s="10">
-        <v>-26.9</v>
+        <v>2.82</v>
+      </c>
+      <c r="L6" s="8">
+        <v>-28.4</v>
       </c>
       <c r="M6" s="9">
-        <v>0.61199999999999999</v>
-      </c>
-      <c r="N6" s="8">
-        <v>7.8</v>
-      </c>
-      <c r="O6" s="10">
-        <v>-22.8</v>
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="N6" s="10">
+        <v>6.47</v>
+      </c>
+      <c r="O6" s="8">
+        <v>-32.700000000000003</v>
       </c>
       <c r="P6" s="9">
-        <v>2.17</v>
-      </c>
-      <c r="Q6" s="10">
-        <v>-26.9</v>
+        <v>2.82</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>-28.4</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>18.100000000000001</v>
+        <v>15.9</v>
       </c>
       <c r="C7" s="7">
-        <v>15.9</v>
+        <v>13.35</v>
       </c>
       <c r="D7" s="7">
-        <v>19</v>
+        <v>16.25</v>
       </c>
       <c r="E7" s="7">
-        <v>15.45</v>
-      </c>
-      <c r="F7" s="10">
-        <v>-2.2000000000000002</v>
-      </c>
-      <c r="G7" s="10">
-        <v>-12.15</v>
+        <v>12.9</v>
+      </c>
+      <c r="F7" s="8">
+        <v>-2.5499999999999998</v>
+      </c>
+      <c r="G7" s="8">
+        <v>-16.04</v>
       </c>
       <c r="H7" s="9">
-        <v>0.56799999999999995</v>
-      </c>
-      <c r="I7" s="8">
-        <v>26.8</v>
-      </c>
-      <c r="J7" s="10">
-        <v>-35.700000000000003</v>
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="I7" s="10">
+        <v>7.8</v>
+      </c>
+      <c r="J7" s="8">
+        <v>-22.8</v>
       </c>
       <c r="K7" s="9">
-        <v>1.56</v>
-      </c>
-      <c r="L7" s="10">
-        <v>-28.4</v>
+        <v>2.17</v>
+      </c>
+      <c r="L7" s="8">
+        <v>-26.9</v>
       </c>
       <c r="M7" s="9">
-        <v>0.56799999999999995</v>
-      </c>
-      <c r="N7" s="8">
-        <v>26.8</v>
-      </c>
-      <c r="O7" s="10">
-        <v>-35.700000000000003</v>
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="N7" s="10">
+        <v>7.8</v>
+      </c>
+      <c r="O7" s="8">
+        <v>-22.8</v>
       </c>
       <c r="P7" s="9">
-        <v>1.56</v>
-      </c>
-      <c r="Q7" s="10">
-        <v>-28.4</v>
+        <v>2.17</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>-26.9</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>19.75</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="C8" s="7">
-        <v>18.100000000000001</v>
+        <v>15.9</v>
       </c>
       <c r="D8" s="7">
-        <v>19.95</v>
+        <v>19</v>
       </c>
       <c r="E8" s="7">
-        <v>17.95</v>
-      </c>
-      <c r="F8" s="10">
-        <v>-1.65</v>
-      </c>
-      <c r="G8" s="10">
-        <v>-8.35</v>
+        <v>15.45</v>
+      </c>
+      <c r="F8" s="8">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="G8" s="8">
+        <v>-12.15</v>
       </c>
       <c r="H8" s="9">
-        <v>0.44800000000000001</v>
+        <v>0.56799999999999995</v>
       </c>
       <c r="I8" s="10">
-        <v>-17.5</v>
-      </c>
-      <c r="J8" s="10">
-        <v>-25.2</v>
+        <v>26.8</v>
+      </c>
+      <c r="J8" s="8">
+        <v>-35.700000000000003</v>
       </c>
       <c r="K8" s="9">
-        <v>0.99099999999999999</v>
-      </c>
-      <c r="L8" s="10">
-        <v>-23.4</v>
+        <v>1.56</v>
+      </c>
+      <c r="L8" s="8">
+        <v>-28.4</v>
       </c>
       <c r="M8" s="9">
-        <v>0.44800000000000001</v>
+        <v>0.56799999999999995</v>
       </c>
       <c r="N8" s="10">
-        <v>-17.5</v>
-      </c>
-      <c r="O8" s="10">
-        <v>-25.2</v>
+        <v>26.8</v>
+      </c>
+      <c r="O8" s="8">
+        <v>-35.700000000000003</v>
       </c>
       <c r="P8" s="9">
-        <v>0.99099999999999999</v>
-      </c>
-      <c r="Q8" s="10">
-        <v>-23.4</v>
+        <v>1.56</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>-28.4</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7">
-        <v>18.149999999999999</v>
+        <v>19.75</v>
       </c>
       <c r="C9" s="7">
-        <v>19.75</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="D9" s="7">
-        <v>20.9</v>
+        <v>19.95</v>
       </c>
       <c r="E9" s="7">
-        <v>17.899999999999999</v>
+        <v>17.95</v>
       </c>
       <c r="F9" s="8">
-        <v>1.6</v>
+        <v>-1.65</v>
       </c>
       <c r="G9" s="8">
-        <v>8.82</v>
+        <v>-8.35</v>
       </c>
       <c r="H9" s="9">
-        <v>0.54300000000000004</v>
-      </c>
-      <c r="I9" s="10">
-        <v>-14.8</v>
-      </c>
-      <c r="J9" s="10">
-        <v>-21.9</v>
+        <v>0.44800000000000001</v>
+      </c>
+      <c r="I9" s="8">
+        <v>-17.5</v>
+      </c>
+      <c r="J9" s="8">
+        <v>-25.2</v>
       </c>
       <c r="K9" s="9">
-        <v>0.54300000000000004</v>
-      </c>
-      <c r="L9" s="10">
-        <v>-21.9</v>
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="L9" s="8">
+        <v>-23.4</v>
       </c>
       <c r="M9" s="9">
-        <v>0.54300000000000004</v>
-      </c>
-      <c r="N9" s="10">
-        <v>-14.8</v>
-      </c>
-      <c r="O9" s="10">
-        <v>-21.9</v>
+        <v>0.44800000000000001</v>
+      </c>
+      <c r="N9" s="8">
+        <v>-17.5</v>
+      </c>
+      <c r="O9" s="8">
+        <v>-25.2</v>
       </c>
       <c r="P9" s="9">
-        <v>0.54300000000000004</v>
-      </c>
-      <c r="Q9" s="10">
-        <v>-21.9</v>
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>-23.4</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7">
-        <v>18.2</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="C10" s="7">
-        <v>18.149999999999999</v>
+        <v>19.75</v>
       </c>
       <c r="D10" s="7">
-        <v>20.3</v>
+        <v>20.9</v>
       </c>
       <c r="E10" s="7">
-        <v>17.5</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="F10" s="10">
-        <v>-0.05</v>
+        <v>1.6</v>
       </c>
       <c r="G10" s="10">
-        <v>-0.27</v>
+        <v>8.82</v>
       </c>
       <c r="H10" s="9">
-        <v>0.63800000000000001</v>
-      </c>
-      <c r="I10" s="10">
-        <v>-12.3</v>
-      </c>
-      <c r="J10" s="10">
-        <v>-21.3</v>
+        <v>0.54300000000000004</v>
+      </c>
+      <c r="I10" s="8">
+        <v>-14.8</v>
+      </c>
+      <c r="J10" s="8">
+        <v>-21.9</v>
       </c>
       <c r="K10" s="9">
-        <v>9.66</v>
+        <v>0.54300000000000004</v>
       </c>
       <c r="L10" s="8">
-        <v>42.9</v>
+        <v>-21.9</v>
       </c>
       <c r="M10" s="9">
-        <v>0.63800000000000001</v>
-      </c>
-      <c r="N10" s="10">
-        <v>-12.3</v>
-      </c>
-      <c r="O10" s="10">
-        <v>-21.3</v>
+        <v>0.54300000000000004</v>
+      </c>
+      <c r="N10" s="8">
+        <v>-14.8</v>
+      </c>
+      <c r="O10" s="8">
+        <v>-21.9</v>
       </c>
       <c r="P10" s="9">
-        <v>9.66</v>
+        <v>0.54300000000000004</v>
       </c>
       <c r="Q10" s="8">
-        <v>42.9</v>
+        <v>-21.9</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7">
-        <v>20</v>
+        <v>18.2</v>
       </c>
       <c r="C11" s="7">
-        <v>18.2</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="D11" s="7">
-        <v>21</v>
+        <v>20.3</v>
       </c>
       <c r="E11" s="7">
-        <v>17.3</v>
-      </c>
-      <c r="F11" s="10">
-        <v>-1.8</v>
-      </c>
-      <c r="G11" s="10">
-        <v>-9</v>
+        <v>17.5</v>
+      </c>
+      <c r="F11" s="8">
+        <v>-0.05</v>
+      </c>
+      <c r="G11" s="8">
+        <v>-0.27</v>
       </c>
       <c r="H11" s="9">
-        <v>0.72699999999999998</v>
-      </c>
-      <c r="I11" s="10">
-        <v>-2.87</v>
+        <v>0.63800000000000001</v>
+      </c>
+      <c r="I11" s="8">
+        <v>-12.3</v>
       </c>
       <c r="J11" s="8">
-        <v>13.7</v>
+        <v>-21.3</v>
       </c>
       <c r="K11" s="9">
-        <v>9.02</v>
-      </c>
-      <c r="L11" s="8">
-        <v>51.7</v>
+        <v>9.66</v>
+      </c>
+      <c r="L11" s="10">
+        <v>42.9</v>
       </c>
       <c r="M11" s="9">
-        <v>0.72699999999999998</v>
-      </c>
-      <c r="N11" s="10">
-        <v>-2.87</v>
+        <v>0.63800000000000001</v>
+      </c>
+      <c r="N11" s="8">
+        <v>-12.3</v>
       </c>
       <c r="O11" s="8">
-        <v>13.7</v>
+        <v>-21.3</v>
       </c>
       <c r="P11" s="9">
-        <v>9.02</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>51.7</v>
+        <v>9.66</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>42.9</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B12" s="7">
-        <v>22.15</v>
+        <v>20</v>
       </c>
       <c r="C12" s="7">
-        <v>20</v>
+        <v>18.2</v>
       </c>
       <c r="D12" s="7">
-        <v>21.65</v>
+        <v>21</v>
       </c>
       <c r="E12" s="7">
-        <v>17.600000000000001</v>
-      </c>
-      <c r="F12" s="10">
-        <v>-2.15</v>
-      </c>
-      <c r="G12" s="10">
-        <v>-9.7100000000000009</v>
+        <v>17.3</v>
+      </c>
+      <c r="F12" s="8">
+        <v>-1.8</v>
+      </c>
+      <c r="G12" s="8">
+        <v>-9</v>
       </c>
       <c r="H12" s="9">
-        <v>0.749</v>
-      </c>
-      <c r="I12" s="10">
-        <v>-7.3</v>
-      </c>
-      <c r="J12" s="8">
-        <v>17.399999999999999</v>
+        <v>0.72699999999999998</v>
+      </c>
+      <c r="I12" s="8">
+        <v>-2.87</v>
+      </c>
+      <c r="J12" s="10">
+        <v>13.7</v>
       </c>
       <c r="K12" s="9">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="L12" s="8">
-        <v>56.3</v>
+        <v>9.02</v>
+      </c>
+      <c r="L12" s="10">
+        <v>51.7</v>
       </c>
       <c r="M12" s="9">
-        <v>0.749</v>
-      </c>
-      <c r="N12" s="10">
-        <v>-7.3</v>
-      </c>
-      <c r="O12" s="8">
-        <v>17.399999999999999</v>
+        <v>0.72699999999999998</v>
+      </c>
+      <c r="N12" s="8">
+        <v>-2.87</v>
+      </c>
+      <c r="O12" s="10">
+        <v>13.7</v>
       </c>
       <c r="P12" s="9">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>56.3</v>
+        <v>9.02</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>51.7</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B13" s="7">
-        <v>23</v>
+        <v>22.15</v>
       </c>
       <c r="C13" s="7">
-        <v>22.15</v>
+        <v>20</v>
       </c>
       <c r="D13" s="7">
-        <v>23.6</v>
+        <v>21.65</v>
       </c>
       <c r="E13" s="7">
-        <v>21.3</v>
-      </c>
-      <c r="F13" s="10">
-        <v>-0.85</v>
-      </c>
-      <c r="G13" s="10">
-        <v>-3.7</v>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="F13" s="8">
+        <v>-2.15</v>
+      </c>
+      <c r="G13" s="8">
+        <v>-9.7100000000000009</v>
       </c>
       <c r="H13" s="9">
-        <v>0.80800000000000005</v>
-      </c>
-      <c r="I13" s="10">
-        <v>-11.8</v>
-      </c>
-      <c r="J13" s="8">
-        <v>34.799999999999997</v>
+        <v>0.749</v>
+      </c>
+      <c r="I13" s="8">
+        <v>-7.3</v>
+      </c>
+      <c r="J13" s="10">
+        <v>17.399999999999999</v>
       </c>
       <c r="K13" s="9">
-        <v>7.55</v>
-      </c>
-      <c r="L13" s="8">
-        <v>61.6</v>
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="L13" s="10">
+        <v>56.3</v>
       </c>
       <c r="M13" s="9">
-        <v>0.80800000000000005</v>
-      </c>
-      <c r="N13" s="10">
-        <v>-11.8</v>
-      </c>
-      <c r="O13" s="8">
-        <v>34.799999999999997</v>
+        <v>0.749</v>
+      </c>
+      <c r="N13" s="8">
+        <v>-7.3</v>
+      </c>
+      <c r="O13" s="10">
+        <v>17.399999999999999</v>
       </c>
       <c r="P13" s="9">
-        <v>7.55</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>61.6</v>
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>56.3</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B14" s="7">
-        <v>22.2</v>
+        <v>23</v>
       </c>
       <c r="C14" s="7">
-        <v>23</v>
+        <v>22.15</v>
       </c>
       <c r="D14" s="7">
-        <v>23.95</v>
+        <v>23.6</v>
       </c>
       <c r="E14" s="7">
         <v>21.3</v>
       </c>
       <c r="F14" s="8">
-        <v>0.8</v>
+        <v>-0.85</v>
       </c>
       <c r="G14" s="8">
-        <v>3.6</v>
+        <v>-3.7</v>
       </c>
       <c r="H14" s="9">
-        <v>0.91700000000000004</v>
-      </c>
-      <c r="I14" s="10">
-        <v>-5.84</v>
-      </c>
-      <c r="J14" s="8">
-        <v>44.2</v>
+        <v>0.80800000000000005</v>
+      </c>
+      <c r="I14" s="8">
+        <v>-11.8</v>
+      </c>
+      <c r="J14" s="10">
+        <v>34.799999999999997</v>
       </c>
       <c r="K14" s="9">
-        <v>6.74</v>
-      </c>
-      <c r="L14" s="8">
-        <v>65.5</v>
+        <v>7.55</v>
+      </c>
+      <c r="L14" s="10">
+        <v>61.6</v>
       </c>
       <c r="M14" s="9">
-        <v>0.91700000000000004</v>
-      </c>
-      <c r="N14" s="10">
-        <v>-5.84</v>
-      </c>
-      <c r="O14" s="8">
-        <v>44.2</v>
+        <v>0.80800000000000005</v>
+      </c>
+      <c r="N14" s="8">
+        <v>-11.8</v>
+      </c>
+      <c r="O14" s="10">
+        <v>34.799999999999997</v>
       </c>
       <c r="P14" s="9">
-        <v>6.74</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>65.5</v>
+        <v>7.55</v>
+      </c>
+      <c r="Q14" s="10">
+        <v>61.6</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B15" s="7">
-        <v>22.15</v>
+        <v>22.2</v>
       </c>
       <c r="C15" s="7">
-        <v>22.2</v>
+        <v>23</v>
       </c>
       <c r="D15" s="7">
-        <v>23.6</v>
+        <v>23.95</v>
       </c>
       <c r="E15" s="7">
-        <v>19.3</v>
-      </c>
-      <c r="F15" s="8">
-        <v>0.05</v>
-      </c>
-      <c r="G15" s="8">
-        <v>0.23</v>
+        <v>21.3</v>
+      </c>
+      <c r="F15" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="G15" s="10">
+        <v>3.6</v>
       </c>
       <c r="H15" s="9">
-        <v>0.97299999999999998</v>
+        <v>0.91700000000000004</v>
       </c>
       <c r="I15" s="8">
-        <v>7.03</v>
-      </c>
-      <c r="J15" s="8">
-        <v>63.7</v>
+        <v>-5.84</v>
+      </c>
+      <c r="J15" s="10">
+        <v>44.2</v>
       </c>
       <c r="K15" s="9">
-        <v>5.82</v>
-      </c>
-      <c r="L15" s="8">
-        <v>69.5</v>
+        <v>6.74</v>
+      </c>
+      <c r="L15" s="10">
+        <v>65.5</v>
       </c>
       <c r="M15" s="9">
-        <v>0.97299999999999998</v>
+        <v>0.91700000000000004</v>
       </c>
       <c r="N15" s="8">
-        <v>7.03</v>
-      </c>
-      <c r="O15" s="8">
-        <v>63.7</v>
+        <v>-5.84</v>
+      </c>
+      <c r="O15" s="10">
+        <v>44.2</v>
       </c>
       <c r="P15" s="9">
-        <v>5.82</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>69.5</v>
+        <v>6.74</v>
+      </c>
+      <c r="Q15" s="10">
+        <v>65.5</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B16" s="7">
-        <v>22.05</v>
+        <v>22.15</v>
       </c>
       <c r="C16" s="7">
-        <v>22.15</v>
+        <v>22.2</v>
       </c>
       <c r="D16" s="7">
-        <v>24.75</v>
+        <v>23.6</v>
       </c>
       <c r="E16" s="7">
-        <v>21.15</v>
-      </c>
-      <c r="F16" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G16" s="8">
-        <v>0.45</v>
+        <v>19.3</v>
+      </c>
+      <c r="F16" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="G16" s="10">
+        <v>0.23</v>
       </c>
       <c r="H16" s="9">
-        <v>0.90900000000000003</v>
+        <v>0.97299999999999998</v>
       </c>
       <c r="I16" s="10">
-        <v>-6.14</v>
-      </c>
-      <c r="J16" s="8">
-        <v>68</v>
+        <v>7.03</v>
+      </c>
+      <c r="J16" s="10">
+        <v>63.7</v>
       </c>
       <c r="K16" s="9">
-        <v>4.8499999999999996</v>
-      </c>
-      <c r="L16" s="8">
-        <v>70.7</v>
+        <v>5.82</v>
+      </c>
+      <c r="L16" s="10">
+        <v>69.5</v>
       </c>
       <c r="M16" s="9">
-        <v>0.90900000000000003</v>
+        <v>0.97299999999999998</v>
       </c>
       <c r="N16" s="10">
-        <v>-6.14</v>
-      </c>
-      <c r="O16" s="8">
-        <v>68</v>
+        <v>7.03</v>
+      </c>
+      <c r="O16" s="10">
+        <v>63.7</v>
       </c>
       <c r="P16" s="9">
-        <v>4.8499999999999996</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>70.7</v>
+        <v>5.82</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>69.5</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B17" s="7">
-        <v>25</v>
+        <v>22.05</v>
       </c>
       <c r="C17" s="7">
-        <v>22.05</v>
+        <v>22.15</v>
       </c>
       <c r="D17" s="7">
-        <v>24.65</v>
+        <v>24.75</v>
       </c>
       <c r="E17" s="7">
-        <v>16.05</v>
+        <v>21.15</v>
       </c>
       <c r="F17" s="10">
-        <v>-2.95</v>
+        <v>0.1</v>
       </c>
       <c r="G17" s="10">
-        <v>-11.8</v>
+        <v>0.45</v>
       </c>
       <c r="H17" s="9">
-        <v>0.96899999999999997</v>
+        <v>0.90900000000000003</v>
       </c>
       <c r="I17" s="8">
-        <v>22.1</v>
-      </c>
-      <c r="J17" s="8">
-        <v>84.5</v>
+        <v>-6.14</v>
+      </c>
+      <c r="J17" s="10">
+        <v>68</v>
       </c>
       <c r="K17" s="9">
-        <v>3.94</v>
-      </c>
-      <c r="L17" s="8">
-        <v>71.3</v>
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="L17" s="10">
+        <v>70.7</v>
       </c>
       <c r="M17" s="9">
-        <v>0.96899999999999997</v>
+        <v>0.90900000000000003</v>
       </c>
       <c r="N17" s="8">
-        <v>22.1</v>
-      </c>
-      <c r="O17" s="8">
-        <v>84.5</v>
+        <v>-6.14</v>
+      </c>
+      <c r="O17" s="10">
+        <v>68</v>
       </c>
       <c r="P17" s="9">
-        <v>3.94</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>71.3</v>
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>70.7</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B18" s="7">
-        <v>21.8</v>
+        <v>25</v>
       </c>
       <c r="C18" s="7">
-        <v>25</v>
+        <v>22.05</v>
       </c>
       <c r="D18" s="7">
-        <v>27.35</v>
+        <v>24.65</v>
       </c>
       <c r="E18" s="7">
-        <v>21.45</v>
+        <v>16.05</v>
       </c>
       <c r="F18" s="8">
-        <v>3.2</v>
+        <v>-2.95</v>
       </c>
       <c r="G18" s="8">
-        <v>14.68</v>
+        <v>-11.8</v>
       </c>
       <c r="H18" s="9">
-        <v>0.79300000000000004</v>
+        <v>0.96899999999999997</v>
       </c>
       <c r="I18" s="10">
-        <v>-10.199999999999999</v>
-      </c>
-      <c r="J18" s="8">
-        <v>53.1</v>
+        <v>22.1</v>
+      </c>
+      <c r="J18" s="10">
+        <v>84.5</v>
       </c>
       <c r="K18" s="9">
-        <v>2.97</v>
-      </c>
-      <c r="L18" s="8">
-        <v>67.400000000000006</v>
+        <v>3.94</v>
+      </c>
+      <c r="L18" s="10">
+        <v>71.3</v>
       </c>
       <c r="M18" s="9">
-        <v>0.79300000000000004</v>
+        <v>0.96899999999999997</v>
       </c>
       <c r="N18" s="10">
-        <v>-10.199999999999999</v>
-      </c>
-      <c r="O18" s="8">
-        <v>53.1</v>
+        <v>22.1</v>
+      </c>
+      <c r="O18" s="10">
+        <v>84.5</v>
       </c>
       <c r="P18" s="9">
-        <v>2.97</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>67.400000000000006</v>
+        <v>3.94</v>
+      </c>
+      <c r="Q18" s="10">
+        <v>71.3</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B19" s="7">
-        <v>22.45</v>
+        <v>21.8</v>
       </c>
       <c r="C19" s="7">
-        <v>21.8</v>
+        <v>25</v>
       </c>
       <c r="D19" s="7">
-        <v>25.5</v>
+        <v>27.35</v>
       </c>
       <c r="E19" s="7">
-        <v>21.35</v>
+        <v>21.45</v>
       </c>
       <c r="F19" s="10">
-        <v>-0.65</v>
+        <v>3.2</v>
       </c>
       <c r="G19" s="10">
-        <v>-2.9</v>
+        <v>14.68</v>
       </c>
       <c r="H19" s="9">
-        <v>0.88400000000000001</v>
+        <v>0.79300000000000004</v>
       </c>
       <c r="I19" s="8">
-        <v>47.6</v>
-      </c>
-      <c r="J19" s="8">
-        <v>68.8</v>
+        <v>-10.199999999999999</v>
+      </c>
+      <c r="J19" s="10">
+        <v>53.1</v>
       </c>
       <c r="K19" s="9">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="L19" s="8">
-        <v>73.3</v>
+        <v>2.97</v>
+      </c>
+      <c r="L19" s="10">
+        <v>67.400000000000006</v>
       </c>
       <c r="M19" s="9">
-        <v>0.88400000000000001</v>
+        <v>0.79300000000000004</v>
       </c>
       <c r="N19" s="8">
-        <v>47.6</v>
-      </c>
-      <c r="O19" s="8">
-        <v>68.8</v>
+        <v>-10.199999999999999</v>
+      </c>
+      <c r="O19" s="10">
+        <v>53.1</v>
       </c>
       <c r="P19" s="9">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="Q19" s="8">
-        <v>73.3</v>
+        <v>2.97</v>
+      </c>
+      <c r="Q19" s="10">
+        <v>67.400000000000006</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B20" s="7">
-        <v>20.95</v>
+        <v>22.45</v>
       </c>
       <c r="C20" s="7">
-        <v>22.45</v>
+        <v>21.8</v>
       </c>
       <c r="D20" s="7">
-        <v>23.4</v>
+        <v>25.5</v>
       </c>
       <c r="E20" s="7">
-        <v>19.600000000000001</v>
+        <v>21.35</v>
       </c>
       <c r="F20" s="8">
-        <v>1.5</v>
+        <v>-0.65</v>
       </c>
       <c r="G20" s="8">
-        <v>7.16</v>
+        <v>-2.9</v>
       </c>
       <c r="H20" s="9">
-        <v>0.59899999999999998</v>
+        <v>0.88400000000000001</v>
       </c>
       <c r="I20" s="10">
-        <v>-13.9</v>
-      </c>
-      <c r="J20" s="8">
-        <v>48</v>
+        <v>47.6</v>
+      </c>
+      <c r="J20" s="10">
+        <v>68.8</v>
       </c>
       <c r="K20" s="9">
-        <v>1.29</v>
-      </c>
-      <c r="L20" s="8">
-        <v>76.5</v>
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="L20" s="10">
+        <v>73.3</v>
       </c>
       <c r="M20" s="9">
-        <v>0.59899999999999998</v>
+        <v>0.88400000000000001</v>
       </c>
       <c r="N20" s="10">
-        <v>-13.9</v>
-      </c>
-      <c r="O20" s="8">
-        <v>48</v>
+        <v>47.6</v>
+      </c>
+      <c r="O20" s="10">
+        <v>68.8</v>
       </c>
       <c r="P20" s="9">
-        <v>1.29</v>
-      </c>
-      <c r="Q20" s="8">
-        <v>76.5</v>
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="Q20" s="10">
+        <v>73.3</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B21" s="7">
-        <v>18.95</v>
+        <v>20.95</v>
       </c>
       <c r="C21" s="7">
-        <v>20.95</v>
+        <v>22.45</v>
       </c>
       <c r="D21" s="7">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="E21" s="7">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="F21" s="8">
-        <v>2</v>
-      </c>
-      <c r="G21" s="8">
-        <v>10.55</v>
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F21" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="G21" s="10">
+        <v>7.16</v>
       </c>
       <c r="H21" s="9">
-        <v>0.69499999999999995</v>
-      </c>
-      <c r="I21" s="10">
-        <v>-14.2</v>
-      </c>
-      <c r="J21" s="8">
-        <v>111.8</v>
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="I21" s="8">
+        <v>-13.9</v>
+      </c>
+      <c r="J21" s="10">
+        <v>48</v>
       </c>
       <c r="K21" s="9">
-        <v>0.69499999999999995</v>
-      </c>
-      <c r="L21" s="8">
-        <v>111.8</v>
+        <v>1.29</v>
+      </c>
+      <c r="L21" s="10">
+        <v>76.5</v>
       </c>
       <c r="M21" s="9">
-        <v>0.69499999999999995</v>
-      </c>
-      <c r="N21" s="10">
-        <v>-14.2</v>
-      </c>
-      <c r="O21" s="8">
-        <v>111.8</v>
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="N21" s="8">
+        <v>-13.9</v>
+      </c>
+      <c r="O21" s="10">
+        <v>48</v>
       </c>
       <c r="P21" s="9">
-        <v>0.69499999999999995</v>
-      </c>
-      <c r="Q21" s="8">
-        <v>111.8</v>
+        <v>1.29</v>
+      </c>
+      <c r="Q21" s="10">
+        <v>76.5</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B22" s="7">
-        <v>18.3</v>
+        <v>18.95</v>
       </c>
       <c r="C22" s="7">
-        <v>18.95</v>
+        <v>20.95</v>
       </c>
       <c r="D22" s="7">
-        <v>19.600000000000001</v>
+        <v>23.1</v>
       </c>
       <c r="E22" s="7">
-        <v>15.7</v>
-      </c>
-      <c r="F22" s="8">
-        <v>0.65</v>
-      </c>
-      <c r="G22" s="8">
-        <v>3.55</v>
+        <v>18.399999999999999</v>
+      </c>
+      <c r="F22" s="10">
+        <v>2</v>
+      </c>
+      <c r="G22" s="10">
+        <v>10.55</v>
       </c>
       <c r="H22" s="9">
-        <v>0.81100000000000005</v>
+        <v>0.69499999999999995</v>
       </c>
       <c r="I22" s="8">
-        <v>26.7</v>
-      </c>
-      <c r="J22" s="8">
-        <v>66.599999999999994</v>
+        <v>-14.2</v>
+      </c>
+      <c r="J22" s="10">
+        <v>111.8</v>
       </c>
       <c r="K22" s="9">
-        <v>6.76</v>
-      </c>
-      <c r="L22" s="8">
-        <v>10.8</v>
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="L22" s="10">
+        <v>111.8</v>
       </c>
       <c r="M22" s="9">
-        <v>0.81100000000000005</v>
+        <v>0.69499999999999995</v>
       </c>
       <c r="N22" s="8">
-        <v>26.7</v>
-      </c>
-      <c r="O22" s="8">
-        <v>66.599999999999994</v>
+        <v>-14.2</v>
+      </c>
+      <c r="O22" s="10">
+        <v>111.8</v>
       </c>
       <c r="P22" s="9">
-        <v>6.76</v>
-      </c>
-      <c r="Q22" s="8">
-        <v>10.8</v>
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="Q22" s="10">
+        <v>111.8</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B23" s="7">
-        <v>15.95</v>
+        <v>18.3</v>
       </c>
       <c r="C23" s="7">
-        <v>18.3</v>
+        <v>18.95</v>
       </c>
       <c r="D23" s="7">
-        <v>19.05</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="E23" s="7">
-        <v>15.25</v>
-      </c>
-      <c r="F23" s="8">
-        <v>2.35</v>
-      </c>
-      <c r="G23" s="8">
-        <v>14.73</v>
+        <v>15.7</v>
+      </c>
+      <c r="F23" s="10">
+        <v>0.65</v>
+      </c>
+      <c r="G23" s="10">
+        <v>3.55</v>
       </c>
       <c r="H23" s="9">
-        <v>0.64</v>
-      </c>
-      <c r="I23" s="8">
-        <v>0.35</v>
-      </c>
-      <c r="J23" s="8">
-        <v>25.4</v>
+        <v>0.81100000000000005</v>
+      </c>
+      <c r="I23" s="10">
+        <v>26.7</v>
+      </c>
+      <c r="J23" s="10">
+        <v>66.599999999999994</v>
       </c>
       <c r="K23" s="9">
-        <v>5.95</v>
-      </c>
-      <c r="L23" s="8">
-        <v>5.98</v>
+        <v>6.76</v>
+      </c>
+      <c r="L23" s="10">
+        <v>10.8</v>
       </c>
       <c r="M23" s="9">
-        <v>0.64</v>
-      </c>
-      <c r="N23" s="8">
-        <v>0.35</v>
-      </c>
-      <c r="O23" s="8">
-        <v>25.4</v>
+        <v>0.81100000000000005</v>
+      </c>
+      <c r="N23" s="10">
+        <v>26.7</v>
+      </c>
+      <c r="O23" s="10">
+        <v>66.599999999999994</v>
       </c>
       <c r="P23" s="9">
-        <v>5.95</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>5.98</v>
+        <v>6.76</v>
+      </c>
+      <c r="Q23" s="10">
+        <v>10.8</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B24" s="7">
-        <v>17.8</v>
+        <v>15.95</v>
       </c>
       <c r="C24" s="7">
-        <v>15.95</v>
+        <v>18.3</v>
       </c>
       <c r="D24" s="7">
-        <v>18.350000000000001</v>
+        <v>19.05</v>
       </c>
       <c r="E24" s="7">
-        <v>15.6</v>
+        <v>15.25</v>
       </c>
       <c r="F24" s="10">
-        <v>-1.85</v>
+        <v>2.35</v>
       </c>
       <c r="G24" s="10">
-        <v>-10.39</v>
+        <v>14.73</v>
       </c>
       <c r="H24" s="9">
-        <v>0.63800000000000001</v>
-      </c>
-      <c r="I24" s="8">
-        <v>6.42</v>
-      </c>
-      <c r="J24" s="8">
-        <v>28.3</v>
+        <v>0.64</v>
+      </c>
+      <c r="I24" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="J24" s="10">
+        <v>25.4</v>
       </c>
       <c r="K24" s="9">
-        <v>5.31</v>
-      </c>
-      <c r="L24" s="8">
-        <v>4.04</v>
+        <v>5.95</v>
+      </c>
+      <c r="L24" s="10">
+        <v>5.98</v>
       </c>
       <c r="M24" s="9">
-        <v>0.63800000000000001</v>
-      </c>
-      <c r="N24" s="8">
-        <v>6.42</v>
-      </c>
-      <c r="O24" s="8">
-        <v>28.3</v>
+        <v>0.64</v>
+      </c>
+      <c r="N24" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="O24" s="10">
+        <v>25.4</v>
       </c>
       <c r="P24" s="9">
-        <v>5.31</v>
-      </c>
-      <c r="Q24" s="8">
-        <v>4.04</v>
+        <v>5.95</v>
+      </c>
+      <c r="Q24" s="10">
+        <v>5.98</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B25" s="7">
-        <v>19.2</v>
+        <v>17.8</v>
       </c>
       <c r="C25" s="7">
-        <v>17.8</v>
+        <v>15.95</v>
       </c>
       <c r="D25" s="7">
-        <v>20.100000000000001</v>
+        <v>18.350000000000001</v>
       </c>
       <c r="E25" s="7">
-        <v>15.5</v>
-      </c>
-      <c r="F25" s="10">
-        <v>-1.4</v>
-      </c>
-      <c r="G25" s="10">
-        <v>-7.29</v>
+        <v>15.6</v>
+      </c>
+      <c r="F25" s="8">
+        <v>-1.85</v>
+      </c>
+      <c r="G25" s="8">
+        <v>-10.39</v>
       </c>
       <c r="H25" s="9">
-        <v>0.59899999999999998</v>
+        <v>0.63800000000000001</v>
       </c>
       <c r="I25" s="10">
-        <v>-5.77</v>
-      </c>
-      <c r="J25" s="8">
-        <v>26.6</v>
+        <v>6.42</v>
+      </c>
+      <c r="J25" s="10">
+        <v>28.3</v>
       </c>
       <c r="K25" s="9">
-        <v>4.67</v>
-      </c>
-      <c r="L25" s="8">
-        <v>1.43</v>
+        <v>5.31</v>
+      </c>
+      <c r="L25" s="10">
+        <v>4.04</v>
       </c>
       <c r="M25" s="9">
-        <v>0.59899999999999998</v>
+        <v>0.63800000000000001</v>
       </c>
       <c r="N25" s="10">
-        <v>-5.77</v>
-      </c>
-      <c r="O25" s="8">
-        <v>26.6</v>
+        <v>6.42</v>
+      </c>
+      <c r="O25" s="10">
+        <v>28.3</v>
       </c>
       <c r="P25" s="9">
-        <v>4.67</v>
-      </c>
-      <c r="Q25" s="8">
-        <v>1.43</v>
+        <v>5.31</v>
+      </c>
+      <c r="Q25" s="10">
+        <v>4.04</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B26" s="7">
-        <v>20.25</v>
+        <v>19.2</v>
       </c>
       <c r="C26" s="7">
-        <v>19.2</v>
+        <v>17.8</v>
       </c>
       <c r="D26" s="7">
-        <v>22</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="E26" s="7">
-        <v>18.149999999999999</v>
-      </c>
-      <c r="F26" s="10">
-        <v>-1.05</v>
-      </c>
-      <c r="G26" s="10">
-        <v>-5.19</v>
+        <v>15.5</v>
+      </c>
+      <c r="F26" s="8">
+        <v>-1.4</v>
+      </c>
+      <c r="G26" s="8">
+        <v>-7.29</v>
       </c>
       <c r="H26" s="9">
-        <v>0.63600000000000001</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="I26" s="8">
-        <v>6.89</v>
-      </c>
-      <c r="J26" s="8">
-        <v>20.100000000000001</v>
+        <v>-5.77</v>
+      </c>
+      <c r="J26" s="10">
+        <v>26.6</v>
       </c>
       <c r="K26" s="9">
-        <v>4.07</v>
+        <v>4.67</v>
       </c>
       <c r="L26" s="10">
-        <v>-1.45</v>
+        <v>1.43</v>
       </c>
       <c r="M26" s="9">
-        <v>0.63600000000000001</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="N26" s="8">
-        <v>6.89</v>
-      </c>
-      <c r="O26" s="8">
-        <v>20.100000000000001</v>
+        <v>-5.77</v>
+      </c>
+      <c r="O26" s="10">
+        <v>26.6</v>
       </c>
       <c r="P26" s="9">
-        <v>4.07</v>
+        <v>4.67</v>
       </c>
       <c r="Q26" s="10">
-        <v>-1.45</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B27" s="7">
-        <v>25</v>
+        <v>20.25</v>
       </c>
       <c r="C27" s="7">
-        <v>20.25</v>
+        <v>19.2</v>
       </c>
       <c r="D27" s="7">
-        <v>26.3</v>
+        <v>22</v>
       </c>
       <c r="E27" s="7">
-        <v>18.45</v>
-      </c>
-      <c r="F27" s="10">
-        <v>-4.75</v>
-      </c>
-      <c r="G27" s="10">
-        <v>-19</v>
+        <v>18.149999999999999</v>
+      </c>
+      <c r="F27" s="8">
+        <v>-1.05</v>
+      </c>
+      <c r="G27" s="8">
+        <v>-5.19</v>
       </c>
       <c r="H27" s="9">
-        <v>0.59499999999999997</v>
-      </c>
-      <c r="I27" s="8">
-        <v>9.86</v>
-      </c>
-      <c r="J27" s="8">
-        <v>11.4</v>
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="I27" s="10">
+        <v>6.89</v>
+      </c>
+      <c r="J27" s="10">
+        <v>20.100000000000001</v>
       </c>
       <c r="K27" s="9">
-        <v>3.44</v>
-      </c>
-      <c r="L27" s="10">
-        <v>-4.6100000000000003</v>
+        <v>4.07</v>
+      </c>
+      <c r="L27" s="8">
+        <v>-1.45</v>
       </c>
       <c r="M27" s="9">
-        <v>0.59499999999999997</v>
-      </c>
-      <c r="N27" s="8">
-        <v>9.86</v>
-      </c>
-      <c r="O27" s="8">
-        <v>11.4</v>
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="N27" s="10">
+        <v>6.89</v>
+      </c>
+      <c r="O27" s="10">
+        <v>20.100000000000001</v>
       </c>
       <c r="P27" s="9">
-        <v>3.44</v>
-      </c>
-      <c r="Q27" s="10">
-        <v>-4.6100000000000003</v>
+        <v>4.07</v>
+      </c>
+      <c r="Q27" s="8">
+        <v>-1.45</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B28" s="7">
-        <v>21.75</v>
+        <v>25</v>
       </c>
       <c r="C28" s="7">
-        <v>25</v>
+        <v>20.25</v>
       </c>
       <c r="D28" s="7">
-        <v>30.5</v>
+        <v>26.3</v>
       </c>
       <c r="E28" s="7">
-        <v>21.1</v>
+        <v>18.45</v>
       </c>
       <c r="F28" s="8">
-        <v>3.25</v>
+        <v>-4.75</v>
       </c>
       <c r="G28" s="8">
-        <v>14.94</v>
+        <v>-19</v>
       </c>
       <c r="H28" s="9">
-        <v>0.54100000000000004</v>
-      </c>
-      <c r="I28" s="8">
-        <v>3.06</v>
-      </c>
-      <c r="J28" s="8">
-        <v>0.21</v>
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="I28" s="10">
+        <v>9.86</v>
+      </c>
+      <c r="J28" s="10">
+        <v>11.4</v>
       </c>
       <c r="K28" s="9">
-        <v>2.84</v>
-      </c>
-      <c r="L28" s="10">
-        <v>-7.41</v>
+        <v>3.44</v>
+      </c>
+      <c r="L28" s="8">
+        <v>-4.6100000000000003</v>
       </c>
       <c r="M28" s="9">
-        <v>0.54100000000000004</v>
-      </c>
-      <c r="N28" s="8">
-        <v>3.06</v>
-      </c>
-      <c r="O28" s="8">
-        <v>0.21</v>
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="N28" s="10">
+        <v>9.86</v>
+      </c>
+      <c r="O28" s="10">
+        <v>11.4</v>
       </c>
       <c r="P28" s="9">
-        <v>2.84</v>
-      </c>
-      <c r="Q28" s="10">
-        <v>-7.41</v>
+        <v>3.44</v>
+      </c>
+      <c r="Q28" s="8">
+        <v>-4.6100000000000003</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B29" s="7">
-        <v>16</v>
+        <v>21.75</v>
       </c>
       <c r="C29" s="7">
-        <v>21.75</v>
+        <v>25</v>
       </c>
       <c r="D29" s="7">
-        <v>25.45</v>
+        <v>30.5</v>
       </c>
       <c r="E29" s="7">
-        <v>14.95</v>
-      </c>
-      <c r="F29" s="8">
-        <v>5.75</v>
-      </c>
-      <c r="G29" s="8">
-        <v>35.94</v>
+        <v>21.1</v>
+      </c>
+      <c r="F29" s="10">
+        <v>3.25</v>
+      </c>
+      <c r="G29" s="10">
+        <v>14.94</v>
       </c>
       <c r="H29" s="9">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="I29" s="8">
-        <v>1.33</v>
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="I29" s="10">
+        <v>3.06</v>
       </c>
       <c r="J29" s="10">
-        <v>-12.2</v>
+        <v>0.21</v>
       </c>
       <c r="K29" s="9">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="L29" s="10">
-        <v>-9.0399999999999991</v>
+        <v>2.84</v>
+      </c>
+      <c r="L29" s="8">
+        <v>-7.41</v>
       </c>
       <c r="M29" s="9">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="N29" s="8">
-        <v>1.33</v>
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="N29" s="10">
+        <v>3.06</v>
       </c>
       <c r="O29" s="10">
-        <v>-12.2</v>
+        <v>0.21</v>
       </c>
       <c r="P29" s="9">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="Q29" s="10">
-        <v>-9.0399999999999991</v>
+        <v>2.84</v>
+      </c>
+      <c r="Q29" s="8">
+        <v>-7.41</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B30" s="7">
-        <v>11.85</v>
+        <v>16</v>
       </c>
       <c r="C30" s="7">
-        <v>16</v>
+        <v>21.75</v>
       </c>
       <c r="D30" s="7">
-        <v>17.850000000000001</v>
+        <v>25.45</v>
       </c>
       <c r="E30" s="7">
-        <v>11.6</v>
-      </c>
-      <c r="F30" s="8">
-        <v>4.1500000000000004</v>
-      </c>
-      <c r="G30" s="8">
-        <v>35.020000000000003</v>
+        <v>14.95</v>
+      </c>
+      <c r="F30" s="10">
+        <v>5.75</v>
+      </c>
+      <c r="G30" s="10">
+        <v>35.94</v>
       </c>
       <c r="H30" s="9">
-        <v>0.51800000000000002</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="I30" s="10">
-        <v>-0.98</v>
-      </c>
-      <c r="J30" s="10">
-        <v>-3.72</v>
+        <v>1.33</v>
+      </c>
+      <c r="J30" s="8">
+        <v>-12.2</v>
       </c>
       <c r="K30" s="9">
-        <v>1.77</v>
-      </c>
-      <c r="L30" s="10">
-        <v>-8.0399999999999991</v>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="L30" s="8">
+        <v>-9.0399999999999991</v>
       </c>
       <c r="M30" s="9">
-        <v>0.51800000000000002</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="N30" s="10">
-        <v>-0.98</v>
-      </c>
-      <c r="O30" s="10">
-        <v>-3.72</v>
+        <v>1.33</v>
+      </c>
+      <c r="O30" s="8">
+        <v>-12.2</v>
       </c>
       <c r="P30" s="9">
-        <v>1.77</v>
-      </c>
-      <c r="Q30" s="10">
-        <v>-8.0399999999999991</v>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Q30" s="8">
+        <v>-9.0399999999999991</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B31" s="7">
-        <v>12.9</v>
+        <v>11.85</v>
       </c>
       <c r="C31" s="7">
-        <v>11.85</v>
+        <v>16</v>
       </c>
       <c r="D31" s="7">
-        <v>16.52</v>
+        <v>17.850000000000001</v>
       </c>
       <c r="E31" s="7">
-        <v>9.17</v>
+        <v>11.6</v>
       </c>
       <c r="F31" s="10">
-        <v>-1.05</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="G31" s="10">
-        <v>-8.14</v>
+        <v>35.020000000000003</v>
       </c>
       <c r="H31" s="9">
-        <v>0.52400000000000002</v>
+        <v>0.51800000000000002</v>
       </c>
       <c r="I31" s="8">
-        <v>29.4</v>
+        <v>-0.98</v>
       </c>
       <c r="J31" s="8">
-        <v>2.42</v>
+        <v>-3.72</v>
       </c>
       <c r="K31" s="9">
-        <v>1.26</v>
-      </c>
-      <c r="L31" s="10">
-        <v>-9.7100000000000009</v>
+        <v>1.77</v>
+      </c>
+      <c r="L31" s="8">
+        <v>-8.0399999999999991</v>
       </c>
       <c r="M31" s="9">
-        <v>0.52400000000000002</v>
+        <v>0.51800000000000002</v>
       </c>
       <c r="N31" s="8">
-        <v>29.4</v>
+        <v>-0.98</v>
       </c>
       <c r="O31" s="8">
-        <v>2.42</v>
+        <v>-3.72</v>
       </c>
       <c r="P31" s="9">
-        <v>1.26</v>
-      </c>
-      <c r="Q31" s="10">
-        <v>-9.7100000000000009</v>
+        <v>1.77</v>
+      </c>
+      <c r="Q31" s="8">
+        <v>-8.0399999999999991</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B32" s="7">
-        <v>15.7</v>
+        <v>12.9</v>
       </c>
       <c r="C32" s="7">
-        <v>12.9</v>
+        <v>11.85</v>
       </c>
       <c r="D32" s="7">
-        <v>19</v>
+        <v>16.52</v>
       </c>
       <c r="E32" s="7">
-        <v>12.84</v>
-      </c>
-      <c r="F32" s="10">
-        <v>-2.8</v>
-      </c>
-      <c r="G32" s="10">
-        <v>-17.829999999999998</v>
+        <v>9.17</v>
+      </c>
+      <c r="F32" s="8">
+        <v>-1.05</v>
+      </c>
+      <c r="G32" s="8">
+        <v>-8.14</v>
       </c>
       <c r="H32" s="9">
-        <v>0.40500000000000003</v>
-      </c>
-      <c r="I32" s="8">
-        <v>23.2</v>
-      </c>
-      <c r="J32" s="8">
-        <v>9.2200000000000006</v>
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="I32" s="10">
+        <v>29.4</v>
+      </c>
+      <c r="J32" s="10">
+        <v>2.42</v>
       </c>
       <c r="K32" s="9">
-        <v>0.73299999999999998</v>
-      </c>
-      <c r="L32" s="10">
-        <v>-16.8</v>
+        <v>1.26</v>
+      </c>
+      <c r="L32" s="8">
+        <v>-9.7100000000000009</v>
       </c>
       <c r="M32" s="9">
-        <v>0.40500000000000003</v>
-      </c>
-      <c r="N32" s="8">
-        <v>23.2</v>
-      </c>
-      <c r="O32" s="8">
-        <v>9.2200000000000006</v>
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="N32" s="10">
+        <v>29.4</v>
+      </c>
+      <c r="O32" s="10">
+        <v>2.42</v>
       </c>
       <c r="P32" s="9">
-        <v>0.73299999999999998</v>
-      </c>
-      <c r="Q32" s="10">
-        <v>-16.8</v>
+        <v>1.26</v>
+      </c>
+      <c r="Q32" s="8">
+        <v>-9.7100000000000009</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B33" s="7">
-        <v>11.2</v>
+        <v>15.7</v>
       </c>
       <c r="C33" s="7">
-        <v>15.7</v>
+        <v>12.9</v>
       </c>
       <c r="D33" s="7">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="E33" s="7">
-        <v>10.1</v>
+        <v>12.84</v>
       </c>
       <c r="F33" s="8">
-        <v>4.5</v>
+        <v>-2.8</v>
       </c>
       <c r="G33" s="8">
-        <v>40.18</v>
+        <v>-17.829999999999998</v>
       </c>
       <c r="H33" s="9">
-        <v>0.32800000000000001</v>
+        <v>0.40500000000000003</v>
       </c>
       <c r="I33" s="10">
-        <v>-32.5</v>
+        <v>23.2</v>
       </c>
       <c r="J33" s="10">
-        <v>-35.6</v>
+        <v>9.2200000000000006</v>
       </c>
       <c r="K33" s="9">
-        <v>0.32800000000000001</v>
-      </c>
-      <c r="L33" s="10">
-        <v>-35.6</v>
+        <v>0.73299999999999998</v>
+      </c>
+      <c r="L33" s="8">
+        <v>-16.8</v>
       </c>
       <c r="M33" s="9">
-        <v>0.32800000000000001</v>
+        <v>0.40500000000000003</v>
       </c>
       <c r="N33" s="10">
-        <v>-32.5</v>
+        <v>23.2</v>
       </c>
       <c r="O33" s="10">
-        <v>-35.6</v>
+        <v>9.2200000000000006</v>
       </c>
       <c r="P33" s="9">
-        <v>0.32800000000000001</v>
-      </c>
-      <c r="Q33" s="10">
-        <v>-35.6</v>
+        <v>0.73299999999999998</v>
+      </c>
+      <c r="Q33" s="8">
+        <v>-16.8</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B34" s="7">
-        <v>11.07</v>
+        <v>11.2</v>
       </c>
       <c r="C34" s="7">
-        <v>11.2</v>
+        <v>15.7</v>
       </c>
       <c r="D34" s="7">
-        <v>11.7</v>
+        <v>18.8</v>
       </c>
       <c r="E34" s="7">
-        <v>10.53</v>
-      </c>
-      <c r="F34" s="8">
-        <v>0.13</v>
-      </c>
-      <c r="G34" s="8">
-        <v>1.17</v>
+        <v>10.1</v>
+      </c>
+      <c r="F34" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="G34" s="10">
+        <v>40.18</v>
       </c>
       <c r="H34" s="9">
-        <v>0.48599999999999999</v>
-      </c>
-      <c r="I34" s="10">
-        <v>-4.6500000000000004</v>
-      </c>
-      <c r="J34" s="10">
-        <v>-6.34</v>
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="I34" s="8">
+        <v>-32.5</v>
+      </c>
+      <c r="J34" s="8">
+        <v>-35.6</v>
       </c>
       <c r="K34" s="9">
-        <v>6.1</v>
-      </c>
-      <c r="L34" s="10">
-        <v>-2.93</v>
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="L34" s="8">
+        <v>-35.6</v>
       </c>
       <c r="M34" s="9">
-        <v>0.48599999999999999</v>
-      </c>
-      <c r="N34" s="10">
-        <v>-4.6500000000000004</v>
-      </c>
-      <c r="O34" s="10">
-        <v>-6.34</v>
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="N34" s="8">
+        <v>-32.5</v>
+      </c>
+      <c r="O34" s="8">
+        <v>-35.6</v>
       </c>
       <c r="P34" s="9">
-        <v>6.1</v>
-      </c>
-      <c r="Q34" s="10">
-        <v>-2.93</v>
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="Q34" s="8">
+        <v>-35.6</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B35" s="7">
-        <v>10.85</v>
+        <v>11.07</v>
       </c>
       <c r="C35" s="7">
-        <v>11.07</v>
+        <v>11.2</v>
       </c>
       <c r="D35" s="7">
-        <v>11.25</v>
+        <v>11.7</v>
       </c>
       <c r="E35" s="7">
-        <v>9.82</v>
-      </c>
-      <c r="F35" s="8">
-        <v>0.22</v>
-      </c>
-      <c r="G35" s="8">
-        <v>2.0299999999999998</v>
+        <v>10.53</v>
+      </c>
+      <c r="F35" s="10">
+        <v>0.13</v>
+      </c>
+      <c r="G35" s="10">
+        <v>1.17</v>
       </c>
       <c r="H35" s="9">
-        <v>0.51</v>
+        <v>0.48599999999999999</v>
       </c>
       <c r="I35" s="8">
-        <v>2.65</v>
-      </c>
-      <c r="J35" s="10">
-        <v>-9.0399999999999991</v>
+        <v>-4.6500000000000004</v>
+      </c>
+      <c r="J35" s="8">
+        <v>-6.34</v>
       </c>
       <c r="K35" s="9">
-        <v>5.61</v>
-      </c>
-      <c r="L35" s="10">
-        <v>-2.62</v>
+        <v>6.1</v>
+      </c>
+      <c r="L35" s="8">
+        <v>-2.93</v>
       </c>
       <c r="M35" s="9">
-        <v>0.51</v>
+        <v>0.48599999999999999</v>
       </c>
       <c r="N35" s="8">
-        <v>2.65</v>
-      </c>
-      <c r="O35" s="10">
-        <v>-9.0399999999999991</v>
+        <v>-4.6500000000000004</v>
+      </c>
+      <c r="O35" s="8">
+        <v>-6.34</v>
       </c>
       <c r="P35" s="9">
-        <v>5.61</v>
-      </c>
-      <c r="Q35" s="10">
-        <v>-2.62</v>
+        <v>6.1</v>
+      </c>
+      <c r="Q35" s="8">
+        <v>-2.93</v>
       </c>
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B36" s="7">
-        <v>9.1</v>
+        <v>10.85</v>
       </c>
       <c r="C36" s="7">
-        <v>10.85</v>
+        <v>11.07</v>
       </c>
       <c r="D36" s="7">
-        <v>11.58</v>
+        <v>11.25</v>
       </c>
       <c r="E36" s="7">
-        <v>9.43</v>
-      </c>
-      <c r="F36" s="8">
-        <v>1.75</v>
-      </c>
-      <c r="G36" s="8">
-        <v>19.23</v>
+        <v>9.82</v>
+      </c>
+      <c r="F36" s="10">
+        <v>0.22</v>
+      </c>
+      <c r="G36" s="10">
+        <v>2.0299999999999998</v>
       </c>
       <c r="H36" s="9">
-        <v>0.497</v>
-      </c>
-      <c r="I36" s="8">
-        <v>5.08</v>
-      </c>
-      <c r="J36" s="10">
-        <v>-6.9</v>
+        <v>0.51</v>
+      </c>
+      <c r="I36" s="10">
+        <v>2.65</v>
+      </c>
+      <c r="J36" s="8">
+        <v>-9.0399999999999991</v>
       </c>
       <c r="K36" s="9">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="L36" s="10">
-        <v>-1.93</v>
+        <v>5.61</v>
+      </c>
+      <c r="L36" s="8">
+        <v>-2.62</v>
       </c>
       <c r="M36" s="9">
-        <v>0.497</v>
-      </c>
-      <c r="N36" s="8">
-        <v>5.08</v>
-      </c>
-      <c r="O36" s="10">
-        <v>-6.9</v>
+        <v>0.51</v>
+      </c>
+      <c r="N36" s="10">
+        <v>2.65</v>
+      </c>
+      <c r="O36" s="8">
+        <v>-9.0399999999999991</v>
       </c>
       <c r="P36" s="9">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="Q36" s="10">
-        <v>-1.93</v>
+        <v>5.61</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>-2.62</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B37" s="7">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="C37" s="7">
-        <v>9.1</v>
+        <v>10.85</v>
       </c>
       <c r="D37" s="7">
-        <v>9.86</v>
+        <v>11.58</v>
       </c>
       <c r="E37" s="7">
-        <v>8.92</v>
+        <v>9.43</v>
       </c>
       <c r="F37" s="10">
-        <v>-0.3</v>
+        <v>1.75</v>
       </c>
       <c r="G37" s="10">
-        <v>-3.19</v>
+        <v>19.23</v>
       </c>
       <c r="H37" s="9">
-        <v>0.47299999999999998</v>
+        <v>0.497</v>
       </c>
       <c r="I37" s="10">
-        <v>-10.7</v>
+        <v>5.08</v>
       </c>
       <c r="J37" s="8">
-        <v>8.33</v>
+        <v>-6.9</v>
       </c>
       <c r="K37" s="9">
-        <v>4.6100000000000003</v>
-      </c>
-      <c r="L37" s="10">
-        <v>-1.36</v>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="L37" s="8">
+        <v>-1.93</v>
       </c>
       <c r="M37" s="9">
-        <v>0.47299999999999998</v>
+        <v>0.497</v>
       </c>
       <c r="N37" s="10">
-        <v>-10.7</v>
+        <v>5.08</v>
       </c>
       <c r="O37" s="8">
-        <v>8.33</v>
+        <v>-6.9</v>
       </c>
       <c r="P37" s="9">
-        <v>4.6100000000000003</v>
-      </c>
-      <c r="Q37" s="10">
-        <v>-1.36</v>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="Q37" s="8">
+        <v>-1.93</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B38" s="7">
-        <v>10.07</v>
+        <v>9.4</v>
       </c>
       <c r="C38" s="7">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="D38" s="7">
-        <v>10.07</v>
+        <v>9.86</v>
       </c>
       <c r="E38" s="7">
-        <v>9.4</v>
-      </c>
-      <c r="F38" s="10">
-        <v>-0.67</v>
-      </c>
-      <c r="G38" s="10">
-        <v>-6.65</v>
+        <v>8.92</v>
+      </c>
+      <c r="F38" s="8">
+        <v>-0.3</v>
+      </c>
+      <c r="G38" s="8">
+        <v>-3.19</v>
       </c>
       <c r="H38" s="9">
-        <v>0.52900000000000003</v>
-      </c>
-      <c r="I38" s="10">
-        <v>-0.79</v>
-      </c>
-      <c r="J38" s="8">
-        <v>10.7</v>
+        <v>0.47299999999999998</v>
+      </c>
+      <c r="I38" s="8">
+        <v>-10.7</v>
+      </c>
+      <c r="J38" s="10">
+        <v>8.33</v>
       </c>
       <c r="K38" s="9">
-        <v>4.13</v>
-      </c>
-      <c r="L38" s="10">
-        <v>-2.36</v>
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="L38" s="8">
+        <v>-1.36</v>
       </c>
       <c r="M38" s="9">
-        <v>0.52900000000000003</v>
-      </c>
-      <c r="N38" s="10">
-        <v>-0.79</v>
-      </c>
-      <c r="O38" s="8">
-        <v>10.7</v>
+        <v>0.47299999999999998</v>
+      </c>
+      <c r="N38" s="8">
+        <v>-10.7</v>
+      </c>
+      <c r="O38" s="10">
+        <v>8.33</v>
       </c>
       <c r="P38" s="9">
-        <v>4.13</v>
-      </c>
-      <c r="Q38" s="10">
-        <v>-2.36</v>
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="Q38" s="8">
+        <v>-1.36</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B39" s="7">
-        <v>11</v>
+        <v>10.07</v>
       </c>
       <c r="C39" s="7">
+        <v>9.4</v>
+      </c>
+      <c r="D39" s="7">
         <v>10.07</v>
       </c>
-      <c r="D39" s="7">
-        <v>10.6</v>
-      </c>
       <c r="E39" s="7">
-        <v>10</v>
-      </c>
-      <c r="F39" s="10">
-        <v>-0.93</v>
-      </c>
-      <c r="G39" s="10">
-        <v>-8.4499999999999993</v>
+        <v>9.4</v>
+      </c>
+      <c r="F39" s="8">
+        <v>-0.67</v>
+      </c>
+      <c r="G39" s="8">
+        <v>-6.65</v>
       </c>
       <c r="H39" s="9">
-        <v>0.53400000000000003</v>
-      </c>
-      <c r="I39" s="10">
-        <v>-1.21</v>
-      </c>
-      <c r="J39" s="8">
-        <v>2.65</v>
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="I39" s="8">
+        <v>-0.79</v>
+      </c>
+      <c r="J39" s="10">
+        <v>10.7</v>
       </c>
       <c r="K39" s="9">
-        <v>3.6</v>
-      </c>
-      <c r="L39" s="10">
-        <v>-4.03</v>
+        <v>4.13</v>
+      </c>
+      <c r="L39" s="8">
+        <v>-2.36</v>
       </c>
       <c r="M39" s="9">
-        <v>0.53400000000000003</v>
-      </c>
-      <c r="N39" s="10">
-        <v>-1.21</v>
-      </c>
-      <c r="O39" s="8">
-        <v>2.65</v>
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="N39" s="8">
+        <v>-0.79</v>
+      </c>
+      <c r="O39" s="10">
+        <v>10.7</v>
       </c>
       <c r="P39" s="9">
-        <v>3.6</v>
-      </c>
-      <c r="Q39" s="10">
-        <v>-4.03</v>
+        <v>4.13</v>
+      </c>
+      <c r="Q39" s="8">
+        <v>-2.36</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B40" s="7">
-        <v>9.8000000000000007</v>
+        <v>11</v>
       </c>
       <c r="C40" s="7">
-        <v>11</v>
+        <v>10.07</v>
       </c>
       <c r="D40" s="7">
-        <v>11.03</v>
+        <v>10.6</v>
       </c>
       <c r="E40" s="7">
-        <v>9.8000000000000007</v>
+        <v>10</v>
       </c>
       <c r="F40" s="8">
-        <v>1.2</v>
+        <v>-0.93</v>
       </c>
       <c r="G40" s="8">
-        <v>12.24</v>
+        <v>-8.4499999999999993</v>
       </c>
       <c r="H40" s="9">
-        <v>0.54</v>
-      </c>
-      <c r="I40" s="10">
-        <v>-9.76</v>
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="I40" s="8">
+        <v>-1.21</v>
       </c>
       <c r="J40" s="10">
-        <v>-8.5500000000000007</v>
+        <v>2.65</v>
       </c>
       <c r="K40" s="9">
-        <v>3.07</v>
-      </c>
-      <c r="L40" s="10">
-        <v>-5.0999999999999996</v>
+        <v>3.6</v>
+      </c>
+      <c r="L40" s="8">
+        <v>-4.03</v>
       </c>
       <c r="M40" s="9">
-        <v>0.54</v>
-      </c>
-      <c r="N40" s="10">
-        <v>-9.76</v>
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="N40" s="8">
+        <v>-1.21</v>
       </c>
       <c r="O40" s="10">
-        <v>-8.5500000000000007</v>
+        <v>2.65</v>
       </c>
       <c r="P40" s="9">
-        <v>3.07</v>
-      </c>
-      <c r="Q40" s="10">
-        <v>-5.0999999999999996</v>
+        <v>3.6</v>
+      </c>
+      <c r="Q40" s="8">
+        <v>-4.03</v>
       </c>
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B41" s="7">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="C41" s="7">
         <v>11</v>
       </c>
-      <c r="C41" s="7">
-        <v>9.8000000000000007</v>
-      </c>
       <c r="D41" s="7">
-        <v>11</v>
+        <v>11.03</v>
       </c>
       <c r="E41" s="7">
         <v>9.8000000000000007</v>
       </c>
       <c r="F41" s="10">
-        <v>-1.2</v>
+        <v>1.2</v>
       </c>
       <c r="G41" s="10">
-        <v>-10.91</v>
+        <v>12.24</v>
       </c>
       <c r="H41" s="9">
-        <v>0.59899999999999998</v>
+        <v>0.54</v>
       </c>
       <c r="I41" s="8">
-        <v>11.2</v>
+        <v>-9.76</v>
       </c>
       <c r="J41" s="8">
-        <v>5.3</v>
+        <v>-8.5500000000000007</v>
       </c>
       <c r="K41" s="9">
-        <v>2.5299999999999998</v>
-      </c>
-      <c r="L41" s="10">
-        <v>-4.33</v>
+        <v>3.07</v>
+      </c>
+      <c r="L41" s="8">
+        <v>-5.0999999999999996</v>
       </c>
       <c r="M41" s="9">
-        <v>0.59899999999999998</v>
+        <v>0.54</v>
       </c>
       <c r="N41" s="8">
-        <v>11.2</v>
+        <v>-9.76</v>
       </c>
       <c r="O41" s="8">
-        <v>5.3</v>
+        <v>-8.5500000000000007</v>
       </c>
       <c r="P41" s="9">
-        <v>2.5299999999999998</v>
-      </c>
-      <c r="Q41" s="10">
-        <v>-4.33</v>
+        <v>3.07</v>
+      </c>
+      <c r="Q41" s="8">
+        <v>-5.0999999999999996</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B42" s="7">
-        <v>9.3000000000000007</v>
+        <v>11</v>
       </c>
       <c r="C42" s="7">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="D42" s="7">
         <v>11</v>
       </c>
-      <c r="D42" s="7">
-        <v>12.61</v>
-      </c>
       <c r="E42" s="7">
-        <v>9.3000000000000007</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="F42" s="8">
-        <v>1.7</v>
+        <v>-1.2</v>
       </c>
       <c r="G42" s="8">
-        <v>18.28</v>
+        <v>-10.91</v>
       </c>
       <c r="H42" s="9">
-        <v>0.53800000000000003</v>
-      </c>
-      <c r="I42" s="8">
-        <v>5.34</v>
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="I42" s="10">
+        <v>11.2</v>
       </c>
       <c r="J42" s="10">
-        <v>-7.86</v>
+        <v>5.3</v>
       </c>
       <c r="K42" s="9">
-        <v>1.93</v>
-      </c>
-      <c r="L42" s="10">
-        <v>-6.97</v>
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="L42" s="8">
+        <v>-4.33</v>
       </c>
       <c r="M42" s="9">
-        <v>0.53800000000000003</v>
-      </c>
-      <c r="N42" s="8">
-        <v>5.34</v>
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="N42" s="10">
+        <v>11.2</v>
       </c>
       <c r="O42" s="10">
-        <v>-7.86</v>
+        <v>5.3</v>
       </c>
       <c r="P42" s="9">
-        <v>1.93</v>
-      </c>
-      <c r="Q42" s="10">
-        <v>-6.97</v>
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>-4.33</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B43" s="7">
-        <v>10.57</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="C43" s="7">
+        <v>11</v>
+      </c>
+      <c r="D43" s="7">
+        <v>12.61</v>
+      </c>
+      <c r="E43" s="7">
         <v>9.3000000000000007</v>
       </c>
-      <c r="D43" s="7">
-        <v>10.57</v>
-      </c>
-      <c r="E43" s="7">
-        <v>9.27</v>
-      </c>
       <c r="F43" s="10">
-        <v>-1.27</v>
+        <v>1.7</v>
       </c>
       <c r="G43" s="10">
-        <v>-12.02</v>
+        <v>18.28</v>
       </c>
       <c r="H43" s="9">
-        <v>0.51100000000000001</v>
-      </c>
-      <c r="I43" s="8">
-        <v>37.9</v>
-      </c>
-      <c r="J43" s="10">
-        <v>-11.3</v>
+        <v>0.53800000000000003</v>
+      </c>
+      <c r="I43" s="10">
+        <v>5.34</v>
+      </c>
+      <c r="J43" s="8">
+        <v>-7.86</v>
       </c>
       <c r="K43" s="9">
-        <v>1.39</v>
-      </c>
-      <c r="L43" s="10">
-        <v>-6.62</v>
+        <v>1.93</v>
+      </c>
+      <c r="L43" s="8">
+        <v>-6.97</v>
       </c>
       <c r="M43" s="9">
-        <v>0.51100000000000001</v>
-      </c>
-      <c r="N43" s="8">
-        <v>37.9</v>
-      </c>
-      <c r="O43" s="10">
-        <v>-11.3</v>
+        <v>0.53800000000000003</v>
+      </c>
+      <c r="N43" s="10">
+        <v>5.34</v>
+      </c>
+      <c r="O43" s="8">
+        <v>-7.86</v>
       </c>
       <c r="P43" s="9">
-        <v>1.39</v>
-      </c>
-      <c r="Q43" s="10">
-        <v>-6.62</v>
+        <v>1.93</v>
+      </c>
+      <c r="Q43" s="8">
+        <v>-6.97</v>
       </c>
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B44" s="7">
-        <v>10.68</v>
+        <v>10.57</v>
       </c>
       <c r="C44" s="7">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="D44" s="7">
         <v>10.57</v>
       </c>
-      <c r="D44" s="7">
-        <v>10.96</v>
-      </c>
       <c r="E44" s="7">
-        <v>10</v>
-      </c>
-      <c r="F44" s="10">
-        <v>-0.11</v>
-      </c>
-      <c r="G44" s="10">
-        <v>-1.03</v>
+        <v>9.27</v>
+      </c>
+      <c r="F44" s="8">
+        <v>-1.27</v>
+      </c>
+      <c r="G44" s="8">
+        <v>-12.02</v>
       </c>
       <c r="H44" s="9">
-        <v>0.371</v>
+        <v>0.51100000000000001</v>
       </c>
       <c r="I44" s="10">
-        <v>-27.4</v>
+        <v>37.9</v>
       </c>
       <c r="J44" s="8">
-        <v>1.79</v>
+        <v>-11.3</v>
       </c>
       <c r="K44" s="9">
-        <v>0.88100000000000001</v>
-      </c>
-      <c r="L44" s="10">
-        <v>-3.66</v>
+        <v>1.39</v>
+      </c>
+      <c r="L44" s="8">
+        <v>-6.62</v>
       </c>
       <c r="M44" s="9">
-        <v>0.371</v>
+        <v>0.51100000000000001</v>
       </c>
       <c r="N44" s="10">
-        <v>-27.4</v>
+        <v>37.9</v>
       </c>
       <c r="O44" s="8">
-        <v>1.79</v>
+        <v>-11.3</v>
       </c>
       <c r="P44" s="9">
-        <v>0.88100000000000001</v>
-      </c>
-      <c r="Q44" s="10">
-        <v>-3.66</v>
+        <v>1.39</v>
+      </c>
+      <c r="Q44" s="8">
+        <v>-6.62</v>
       </c>
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B45" s="7">
-        <v>11</v>
+        <v>10.68</v>
       </c>
       <c r="C45" s="7">
-        <v>10.68</v>
+        <v>10.57</v>
       </c>
       <c r="D45" s="7">
-        <v>11.2</v>
+        <v>10.96</v>
       </c>
       <c r="E45" s="7">
-        <v>10.68</v>
-      </c>
-      <c r="F45" s="10">
-        <v>-0.32</v>
-      </c>
-      <c r="G45" s="10">
-        <v>-2.91</v>
+        <v>10</v>
+      </c>
+      <c r="F45" s="8">
+        <v>-0.11</v>
+      </c>
+      <c r="G45" s="8">
+        <v>-1.03</v>
       </c>
       <c r="H45" s="9">
-        <v>0.51</v>
-      </c>
-      <c r="I45" s="10">
-        <v>-1.8</v>
+        <v>0.371</v>
+      </c>
+      <c r="I45" s="8">
+        <v>-27.4</v>
       </c>
       <c r="J45" s="10">
-        <v>-7.27</v>
+        <v>1.79</v>
       </c>
       <c r="K45" s="9">
-        <v>0.51</v>
-      </c>
-      <c r="L45" s="10">
-        <v>-7.27</v>
+        <v>0.88100000000000001</v>
+      </c>
+      <c r="L45" s="8">
+        <v>-3.66</v>
       </c>
       <c r="M45" s="9">
-        <v>0.51</v>
-      </c>
-      <c r="N45" s="10">
-        <v>-1.8</v>
+        <v>0.371</v>
+      </c>
+      <c r="N45" s="8">
+        <v>-27.4</v>
       </c>
       <c r="O45" s="10">
-        <v>-7.27</v>
+        <v>1.79</v>
       </c>
       <c r="P45" s="9">
-        <v>0.51</v>
-      </c>
-      <c r="Q45" s="10">
-        <v>-7.27</v>
+        <v>0.88100000000000001</v>
+      </c>
+      <c r="Q45" s="8">
+        <v>-3.66</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B46" s="7">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="C46" s="7">
-        <v>11</v>
+        <v>10.68</v>
       </c>
       <c r="D46" s="7">
-        <v>11.52</v>
+        <v>11.2</v>
       </c>
       <c r="E46" s="7">
-        <v>10.33</v>
+        <v>10.68</v>
       </c>
       <c r="F46" s="8">
-        <v>0.3</v>
+        <v>-0.32</v>
       </c>
       <c r="G46" s="8">
-        <v>2.8</v>
+        <v>-2.91</v>
       </c>
       <c r="H46" s="9">
-        <v>0.51900000000000002</v>
-      </c>
-      <c r="I46" s="10">
-        <v>-7.4</v>
-      </c>
-      <c r="J46" s="10">
-        <v>-22.3</v>
+        <v>0.51</v>
+      </c>
+      <c r="I46" s="8">
+        <v>-1.8</v>
+      </c>
+      <c r="J46" s="8">
+        <v>-7.27</v>
       </c>
       <c r="K46" s="9">
-        <v>6.28</v>
-      </c>
-      <c r="L46" s="10">
-        <v>-14</v>
+        <v>0.51</v>
+      </c>
+      <c r="L46" s="8">
+        <v>-7.27</v>
       </c>
       <c r="M46" s="9">
-        <v>0.51900000000000002</v>
-      </c>
-      <c r="N46" s="10">
-        <v>-7.4</v>
-      </c>
-      <c r="O46" s="10">
-        <v>-22.3</v>
+        <v>0.51</v>
+      </c>
+      <c r="N46" s="8">
+        <v>-1.8</v>
+      </c>
+      <c r="O46" s="8">
+        <v>-7.27</v>
       </c>
       <c r="P46" s="9">
-        <v>6.28</v>
-      </c>
-      <c r="Q46" s="10">
-        <v>-14</v>
+        <v>0.51</v>
+      </c>
+      <c r="Q46" s="8">
+        <v>-7.27</v>
       </c>
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B47" s="7">
-        <v>11.5</v>
+        <v>10.7</v>
       </c>
       <c r="C47" s="7">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="D47" s="7">
-        <v>11.5</v>
+        <v>11.52</v>
       </c>
       <c r="E47" s="7">
-        <v>10.3</v>
+        <v>10.33</v>
       </c>
       <c r="F47" s="10">
-        <v>-0.8</v>
+        <v>0.3</v>
       </c>
       <c r="G47" s="10">
-        <v>-6.96</v>
+        <v>2.8</v>
       </c>
       <c r="H47" s="9">
-        <v>0.56100000000000005</v>
+        <v>0.51900000000000002</v>
       </c>
       <c r="I47" s="8">
-        <v>5.07</v>
-      </c>
-      <c r="J47" s="10">
-        <v>-0.9</v>
+        <v>-7.4</v>
+      </c>
+      <c r="J47" s="8">
+        <v>-22.3</v>
       </c>
       <c r="K47" s="9">
-        <v>5.76</v>
-      </c>
-      <c r="L47" s="10">
-        <v>-13.1</v>
+        <v>6.28</v>
+      </c>
+      <c r="L47" s="8">
+        <v>-14</v>
       </c>
       <c r="M47" s="9">
-        <v>0.56100000000000005</v>
+        <v>0.51900000000000002</v>
       </c>
       <c r="N47" s="8">
-        <v>5.07</v>
-      </c>
-      <c r="O47" s="10">
-        <v>-0.9</v>
+        <v>-7.4</v>
+      </c>
+      <c r="O47" s="8">
+        <v>-22.3</v>
       </c>
       <c r="P47" s="9">
-        <v>5.76</v>
-      </c>
-      <c r="Q47" s="10">
-        <v>-13.1</v>
+        <v>6.28</v>
+      </c>
+      <c r="Q47" s="8">
+        <v>-14</v>
       </c>
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B48" s="7">
-        <v>11.42</v>
+        <v>11.5</v>
       </c>
       <c r="C48" s="7">
+        <v>10.7</v>
+      </c>
+      <c r="D48" s="7">
         <v>11.5</v>
       </c>
-      <c r="D48" s="7">
-        <v>12.13</v>
-      </c>
       <c r="E48" s="7">
-        <v>10.92</v>
+        <v>10.3</v>
       </c>
       <c r="F48" s="8">
-        <v>0.08</v>
+        <v>-0.8</v>
       </c>
       <c r="G48" s="8">
-        <v>0.7</v>
+        <v>-6.96</v>
       </c>
       <c r="H48" s="9">
-        <v>0.53400000000000003</v>
-      </c>
-      <c r="I48" s="8">
-        <v>22.3</v>
-      </c>
-      <c r="J48" s="10">
-        <v>-21.2</v>
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="I48" s="10">
+        <v>5.07</v>
+      </c>
+      <c r="J48" s="8">
+        <v>-0.9</v>
       </c>
       <c r="K48" s="9">
-        <v>5.2</v>
-      </c>
-      <c r="L48" s="10">
-        <v>-14.3</v>
+        <v>5.76</v>
+      </c>
+      <c r="L48" s="8">
+        <v>-13.1</v>
       </c>
       <c r="M48" s="9">
-        <v>0.53400000000000003</v>
-      </c>
-      <c r="N48" s="8">
-        <v>22.3</v>
-      </c>
-      <c r="O48" s="10">
-        <v>-21.2</v>
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="N48" s="10">
+        <v>5.07</v>
+      </c>
+      <c r="O48" s="8">
+        <v>-0.9</v>
       </c>
       <c r="P48" s="9">
-        <v>5.2</v>
-      </c>
-      <c r="Q48" s="10">
-        <v>-14.3</v>
+        <v>5.76</v>
+      </c>
+      <c r="Q48" s="8">
+        <v>-13.1</v>
       </c>
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43344</v>
+        <v>43374</v>
       </c>
       <c r="B49" s="7">
-        <v>12.24</v>
+        <v>11.42</v>
       </c>
       <c r="C49" s="7">
-        <v>11.42</v>
+        <v>11.5</v>
       </c>
       <c r="D49" s="7">
-        <v>12.37</v>
+        <v>12.13</v>
       </c>
       <c r="E49" s="7">
-        <v>11.28</v>
+        <v>10.92</v>
       </c>
       <c r="F49" s="10">
-        <v>-0.82</v>
+        <v>0.08</v>
       </c>
       <c r="G49" s="10">
-        <v>-6.7</v>
+        <v>0.7</v>
       </c>
       <c r="H49" s="9">
-        <v>0.437</v>
+        <v>0.53400000000000003</v>
       </c>
       <c r="I49" s="10">
-        <v>-8.6999999999999993</v>
-      </c>
-      <c r="J49" s="10">
-        <v>-36.9</v>
+        <v>22.3</v>
+      </c>
+      <c r="J49" s="8">
+        <v>-21.2</v>
       </c>
       <c r="K49" s="9">
-        <v>4.67</v>
-      </c>
-      <c r="L49" s="10">
-        <v>-13.4</v>
+        <v>5.2</v>
+      </c>
+      <c r="L49" s="8">
+        <v>-14.3</v>
       </c>
       <c r="M49" s="9">
-        <v>0.437</v>
+        <v>0.53400000000000003</v>
       </c>
       <c r="N49" s="10">
-        <v>-8.6999999999999993</v>
-      </c>
-      <c r="O49" s="10">
-        <v>-36.9</v>
+        <v>22.3</v>
+      </c>
+      <c r="O49" s="8">
+        <v>-21.2</v>
       </c>
       <c r="P49" s="9">
-        <v>4.67</v>
-      </c>
-      <c r="Q49" s="10">
-        <v>-13.4</v>
+        <v>5.2</v>
+      </c>
+      <c r="Q49" s="8">
+        <v>-14.3</v>
       </c>
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>43313</v>
+        <v>43344</v>
       </c>
       <c r="B50" s="7">
-        <v>9.8800000000000008</v>
+        <v>12.24</v>
       </c>
       <c r="C50" s="7">
-        <v>12.24</v>
+        <v>11.42</v>
       </c>
       <c r="D50" s="7">
-        <v>12.6</v>
+        <v>12.37</v>
       </c>
       <c r="E50" s="7">
-        <v>9.6</v>
+        <v>11.28</v>
       </c>
       <c r="F50" s="8">
-        <v>2.36</v>
+        <v>-0.82</v>
       </c>
       <c r="G50" s="8">
-        <v>23.89</v>
+        <v>-6.7</v>
       </c>
       <c r="H50" s="9">
-        <v>0.47799999999999998</v>
-      </c>
-      <c r="I50" s="10">
-        <v>-8.01</v>
-      </c>
-      <c r="J50" s="10">
-        <v>-26.6</v>
+        <v>0.437</v>
+      </c>
+      <c r="I50" s="8">
+        <v>-8.6999999999999993</v>
+      </c>
+      <c r="J50" s="8">
+        <v>-36.9</v>
       </c>
       <c r="K50" s="9">
-        <v>4.2300000000000004</v>
-      </c>
-      <c r="L50" s="10">
-        <v>-9.9600000000000009</v>
+        <v>4.67</v>
+      </c>
+      <c r="L50" s="8">
+        <v>-13.4</v>
       </c>
       <c r="M50" s="9">
-        <v>0.47799999999999998</v>
-      </c>
-      <c r="N50" s="10">
-        <v>-8.01</v>
-      </c>
-      <c r="O50" s="10">
-        <v>-26.6</v>
+        <v>0.437</v>
+      </c>
+      <c r="N50" s="8">
+        <v>-8.6999999999999993</v>
+      </c>
+      <c r="O50" s="8">
+        <v>-36.9</v>
       </c>
       <c r="P50" s="9">
-        <v>4.2300000000000004</v>
-      </c>
-      <c r="Q50" s="10">
-        <v>-9.9600000000000009</v>
+        <v>4.67</v>
+      </c>
+      <c r="Q50" s="8">
+        <v>-13.4</v>
       </c>
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>43282</v>
+        <v>43313</v>
       </c>
       <c r="B51" s="7">
-        <v>9.76</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="C51" s="7">
-        <v>9.8800000000000008</v>
+        <v>12.24</v>
       </c>
       <c r="D51" s="7">
-        <v>10.029999999999999</v>
+        <v>12.6</v>
       </c>
       <c r="E51" s="7">
-        <v>9.6199999999999992</v>
-      </c>
-      <c r="F51" s="8">
-        <v>0.12</v>
-      </c>
-      <c r="G51" s="8">
-        <v>1.23</v>
+        <v>9.6</v>
+      </c>
+      <c r="F51" s="10">
+        <v>2.36</v>
+      </c>
+      <c r="G51" s="10">
+        <v>23.89</v>
       </c>
       <c r="H51" s="9">
-        <v>0.52</v>
-      </c>
-      <c r="I51" s="10">
-        <v>-12</v>
-      </c>
-      <c r="J51" s="10">
-        <v>-27.4</v>
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="I51" s="8">
+        <v>-8.01</v>
+      </c>
+      <c r="J51" s="8">
+        <v>-26.6</v>
       </c>
       <c r="K51" s="9">
-        <v>3.75</v>
-      </c>
-      <c r="L51" s="10">
-        <v>-7.29</v>
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="L51" s="8">
+        <v>-9.9600000000000009</v>
       </c>
       <c r="M51" s="9">
-        <v>0.52</v>
-      </c>
-      <c r="N51" s="10">
-        <v>-12</v>
-      </c>
-      <c r="O51" s="10">
-        <v>-27.4</v>
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="N51" s="8">
+        <v>-8.01</v>
+      </c>
+      <c r="O51" s="8">
+        <v>-26.6</v>
       </c>
       <c r="P51" s="9">
-        <v>3.75</v>
-      </c>
-      <c r="Q51" s="10">
-        <v>-7.29</v>
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>-9.9600000000000009</v>
       </c>
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>43252</v>
+        <v>43282</v>
       </c>
       <c r="B52" s="7">
+        <v>9.76</v>
+      </c>
+      <c r="C52" s="7">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="D52" s="7">
+        <v>10.029999999999999</v>
+      </c>
+      <c r="E52" s="7">
         <v>9.6199999999999992</v>
       </c>
-      <c r="C52" s="7">
-        <v>9.76</v>
-      </c>
-      <c r="D52" s="7">
-        <v>10.1</v>
-      </c>
-      <c r="E52" s="7">
-        <v>9.6</v>
-      </c>
-      <c r="F52" s="8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="G52" s="8">
-        <v>1.46</v>
+      <c r="F52" s="10">
+        <v>0.12</v>
+      </c>
+      <c r="G52" s="10">
+        <v>1.23</v>
       </c>
       <c r="H52" s="9">
-        <v>0.59099999999999997</v>
+        <v>0.52</v>
       </c>
       <c r="I52" s="8">
-        <v>3.9</v>
-      </c>
-      <c r="J52" s="10">
-        <v>-14.2</v>
+        <v>-12</v>
+      </c>
+      <c r="J52" s="8">
+        <v>-27.4</v>
       </c>
       <c r="K52" s="9">
-        <v>3.23</v>
-      </c>
-      <c r="L52" s="10">
-        <v>-2.96</v>
+        <v>3.75</v>
+      </c>
+      <c r="L52" s="8">
+        <v>-7.29</v>
       </c>
       <c r="M52" s="9">
-        <v>0.59099999999999997</v>
+        <v>0.52</v>
       </c>
       <c r="N52" s="8">
-        <v>3.9</v>
-      </c>
-      <c r="O52" s="10">
-        <v>-14.2</v>
+        <v>-12</v>
+      </c>
+      <c r="O52" s="8">
+        <v>-27.4</v>
       </c>
       <c r="P52" s="9">
-        <v>3.23</v>
-      </c>
-      <c r="Q52" s="10">
-        <v>-2.96</v>
+        <v>3.75</v>
+      </c>
+      <c r="Q52" s="8">
+        <v>-7.29</v>
       </c>
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>43221</v>
+        <v>43252</v>
       </c>
       <c r="B53" s="7">
-        <v>9.6999999999999993</v>
+        <v>9.6199999999999992</v>
       </c>
       <c r="C53" s="7">
-        <v>9.6199999999999992</v>
+        <v>9.76</v>
       </c>
       <c r="D53" s="7">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="E53" s="7">
-        <v>9.56</v>
+        <v>9.6</v>
       </c>
       <c r="F53" s="10">
-        <v>-0.08</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G53" s="10">
-        <v>-0.82</v>
+        <v>1.46</v>
       </c>
       <c r="H53" s="9">
-        <v>0.56899999999999995</v>
+        <v>0.59099999999999997</v>
       </c>
       <c r="I53" s="10">
-        <v>-2.71</v>
-      </c>
-      <c r="J53" s="10">
-        <v>-16.899999999999999</v>
+        <v>3.9</v>
+      </c>
+      <c r="J53" s="8">
+        <v>-14.2</v>
       </c>
       <c r="K53" s="9">
-        <v>2.64</v>
-      </c>
-      <c r="L53" s="10">
-        <v>-0.02</v>
+        <v>3.23</v>
+      </c>
+      <c r="L53" s="8">
+        <v>-2.96</v>
       </c>
       <c r="M53" s="9">
-        <v>0.56899999999999995</v>
+        <v>0.59099999999999997</v>
       </c>
       <c r="N53" s="10">
-        <v>-2.71</v>
-      </c>
-      <c r="O53" s="10">
-        <v>-16.899999999999999</v>
+        <v>3.9</v>
+      </c>
+      <c r="O53" s="8">
+        <v>-14.2</v>
       </c>
       <c r="P53" s="9">
-        <v>2.64</v>
-      </c>
-      <c r="Q53" s="10">
-        <v>-0.02</v>
+        <v>3.23</v>
+      </c>
+      <c r="Q53" s="8">
+        <v>-2.96</v>
       </c>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>43191</v>
+        <v>43221</v>
       </c>
       <c r="B54" s="7">
-        <v>10.029999999999999</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="C54" s="7">
-        <v>9.6999999999999993</v>
+        <v>9.6199999999999992</v>
       </c>
       <c r="D54" s="7">
-        <v>10.029999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="E54" s="7">
-        <v>9.5</v>
-      </c>
-      <c r="F54" s="10">
-        <v>-0.33</v>
-      </c>
-      <c r="G54" s="10">
-        <v>-3.29</v>
+        <v>9.56</v>
+      </c>
+      <c r="F54" s="8">
+        <v>-0.08</v>
+      </c>
+      <c r="G54" s="8">
+        <v>-0.82</v>
       </c>
       <c r="H54" s="9">
-        <v>0.58399999999999996</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="I54" s="8">
-        <v>1.39</v>
-      </c>
-      <c r="J54" s="10">
-        <v>-2.86</v>
+        <v>-2.71</v>
+      </c>
+      <c r="J54" s="8">
+        <v>-16.899999999999999</v>
       </c>
       <c r="K54" s="9">
-        <v>2.0699999999999998</v>
+        <v>2.64</v>
       </c>
       <c r="L54" s="8">
-        <v>5.84</v>
+        <v>-0.02</v>
       </c>
       <c r="M54" s="9">
-        <v>0.58399999999999996</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="N54" s="8">
-        <v>1.39</v>
-      </c>
-      <c r="O54" s="10">
-        <v>-2.86</v>
+        <v>-2.71</v>
+      </c>
+      <c r="O54" s="8">
+        <v>-16.899999999999999</v>
       </c>
       <c r="P54" s="9">
-        <v>2.0699999999999998</v>
+        <v>2.64</v>
       </c>
       <c r="Q54" s="8">
-        <v>5.84</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>43160</v>
+        <v>43191</v>
       </c>
       <c r="B55" s="7">
-        <v>9.19</v>
+        <v>10.029999999999999</v>
       </c>
       <c r="C55" s="7">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="D55" s="7">
         <v>10.029999999999999</v>
       </c>
-      <c r="D55" s="7">
-        <v>10.08</v>
-      </c>
       <c r="E55" s="7">
-        <v>9.18</v>
+        <v>9.5</v>
       </c>
       <c r="F55" s="8">
-        <v>0.84</v>
+        <v>-0.33</v>
       </c>
       <c r="G55" s="8">
-        <v>9.14</v>
+        <v>-3.29</v>
       </c>
       <c r="H55" s="9">
-        <v>0.57599999999999996</v>
-      </c>
-      <c r="I55" s="8">
-        <v>58.3</v>
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="I55" s="10">
+        <v>1.39</v>
       </c>
       <c r="J55" s="8">
-        <v>1.6</v>
+        <v>-2.86</v>
       </c>
       <c r="K55" s="9">
-        <v>1.49</v>
-      </c>
-      <c r="L55" s="8">
-        <v>9.6999999999999993</v>
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="L55" s="10">
+        <v>5.84</v>
       </c>
       <c r="M55" s="9">
-        <v>0.57599999999999996</v>
-      </c>
-      <c r="N55" s="8">
-        <v>58.3</v>
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="N55" s="10">
+        <v>1.39</v>
       </c>
       <c r="O55" s="8">
-        <v>1.6</v>
+        <v>-2.86</v>
       </c>
       <c r="P55" s="9">
-        <v>1.49</v>
-      </c>
-      <c r="Q55" s="8">
-        <v>9.6999999999999993</v>
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="Q55" s="10">
+        <v>5.84</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>43132</v>
+        <v>43160</v>
       </c>
       <c r="B56" s="7">
-        <v>9.3000000000000007</v>
+        <v>9.19</v>
       </c>
       <c r="C56" s="7">
-        <v>9.19</v>
+        <v>10.029999999999999</v>
       </c>
       <c r="D56" s="7">
-        <v>9.3000000000000007</v>
+        <v>10.08</v>
       </c>
       <c r="E56" s="7">
-        <v>9.17</v>
+        <v>9.18</v>
       </c>
       <c r="F56" s="10">
-        <v>-0.11</v>
+        <v>0.84</v>
       </c>
       <c r="G56" s="10">
-        <v>-1.18</v>
+        <v>9.14</v>
       </c>
       <c r="H56" s="9">
-        <v>0.36399999999999999</v>
+        <v>0.57599999999999996</v>
       </c>
       <c r="I56" s="10">
-        <v>-33.799999999999997</v>
+        <v>58.3</v>
       </c>
       <c r="J56" s="10">
-        <v>-11.6</v>
+        <v>1.6</v>
       </c>
       <c r="K56" s="9">
-        <v>0.91400000000000003</v>
-      </c>
-      <c r="L56" s="8">
-        <v>15.5</v>
+        <v>1.49</v>
+      </c>
+      <c r="L56" s="10">
+        <v>9.6999999999999993</v>
       </c>
       <c r="M56" s="9">
-        <v>0.36399999999999999</v>
+        <v>0.57599999999999996</v>
       </c>
       <c r="N56" s="10">
-        <v>-33.799999999999997</v>
+        <v>58.3</v>
       </c>
       <c r="O56" s="10">
-        <v>-11.6</v>
+        <v>1.6</v>
       </c>
       <c r="P56" s="9">
-        <v>0.91400000000000003</v>
-      </c>
-      <c r="Q56" s="8">
-        <v>15.5</v>
+        <v>1.49</v>
+      </c>
+      <c r="Q56" s="10">
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>43101</v>
+        <v>43132</v>
       </c>
       <c r="B57" s="7">
         <v>9.3000000000000007</v>
       </c>
       <c r="C57" s="7">
+        <v>9.19</v>
+      </c>
+      <c r="D57" s="7">
         <v>9.3000000000000007</v>
-      </c>
-      <c r="D57" s="7">
-        <v>9.59</v>
       </c>
       <c r="E57" s="7">
         <v>9.17</v>
       </c>
-      <c r="F57" s="9">
-        <v>0</v>
-      </c>
-      <c r="G57" s="9">
-        <v>0</v>
+      <c r="F57" s="8">
+        <v>-0.11</v>
+      </c>
+      <c r="G57" s="8">
+        <v>-1.18</v>
       </c>
       <c r="H57" s="9">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="I57" s="10">
-        <v>-17.7</v>
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="I57" s="8">
+        <v>-33.799999999999997</v>
       </c>
       <c r="J57" s="8">
-        <v>44.8</v>
+        <v>-11.6</v>
       </c>
       <c r="K57" s="9">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="L57" s="8">
-        <v>44.8</v>
+        <v>0.91400000000000003</v>
+      </c>
+      <c r="L57" s="10">
+        <v>15.5</v>
       </c>
       <c r="M57" s="9">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="N57" s="10">
-        <v>-17.7</v>
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="N57" s="8">
+        <v>-33.799999999999997</v>
       </c>
       <c r="O57" s="8">
-        <v>44.8</v>
+        <v>-11.6</v>
       </c>
       <c r="P57" s="9">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="Q57" s="8">
-        <v>44.8</v>
+        <v>0.91400000000000003</v>
+      </c>
+      <c r="Q57" s="10">
+        <v>15.5</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>43070</v>
+        <v>43101</v>
       </c>
       <c r="B58" s="7">
         <v>9.3000000000000007</v>
@@ -4201,10 +4201,10 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="D58" s="7">
-        <v>9.5399999999999991</v>
+        <v>9.59</v>
       </c>
       <c r="E58" s="7">
-        <v>9.0299999999999994</v>
+        <v>9.17</v>
       </c>
       <c r="F58" s="9">
         <v>0</v>
@@ -4213,42 +4213,42 @@
         <v>0</v>
       </c>
       <c r="H58" s="9">
-        <v>0.66800000000000004</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="I58" s="8">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="J58" s="8">
-        <v>10.4</v>
+        <v>-17.7</v>
+      </c>
+      <c r="J58" s="10">
+        <v>44.8</v>
       </c>
       <c r="K58" s="9">
-        <v>7.3</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L58" s="10">
-        <v>-22.1</v>
+        <v>44.8</v>
       </c>
       <c r="M58" s="9">
-        <v>0.66800000000000004</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="N58" s="8">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="O58" s="8">
-        <v>10.4</v>
+        <v>-17.7</v>
+      </c>
+      <c r="O58" s="10">
+        <v>44.8</v>
       </c>
       <c r="P58" s="9">
-        <v>7.3</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="Q58" s="10">
-        <v>-22.1</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>43040</v>
+        <v>43070</v>
       </c>
       <c r="B59" s="7">
-        <v>9.17</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="C59" s="7">
         <v>9.3000000000000007</v>
@@ -4257,578 +4257,578 @@
         <v>9.5399999999999991</v>
       </c>
       <c r="E59" s="7">
-        <v>9.1300000000000008</v>
-      </c>
-      <c r="F59" s="8">
-        <v>0.13</v>
-      </c>
-      <c r="G59" s="8">
-        <v>1.42</v>
+        <v>9.0299999999999994</v>
+      </c>
+      <c r="F59" s="9">
+        <v>0</v>
+      </c>
+      <c r="G59" s="9">
+        <v>0</v>
       </c>
       <c r="H59" s="9">
-        <v>0.56599999999999995</v>
+        <v>0.66800000000000004</v>
       </c>
       <c r="I59" s="10">
-        <v>-16.5</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="J59" s="10">
-        <v>-33</v>
+        <v>10.4</v>
       </c>
       <c r="K59" s="9">
-        <v>6.64</v>
-      </c>
-      <c r="L59" s="10">
-        <v>-24.3</v>
+        <v>7.3</v>
+      </c>
+      <c r="L59" s="8">
+        <v>-22.1</v>
       </c>
       <c r="M59" s="9">
-        <v>0.56599999999999995</v>
+        <v>0.66800000000000004</v>
       </c>
       <c r="N59" s="10">
-        <v>-16.5</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="O59" s="10">
-        <v>-33</v>
+        <v>10.4</v>
       </c>
       <c r="P59" s="9">
-        <v>6.64</v>
-      </c>
-      <c r="Q59" s="10">
-        <v>-24.3</v>
+        <v>7.3</v>
+      </c>
+      <c r="Q59" s="8">
+        <v>-22.1</v>
       </c>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>43009</v>
+        <v>43040</v>
       </c>
       <c r="B60" s="7">
-        <v>9</v>
+        <v>9.17</v>
       </c>
       <c r="C60" s="7">
-        <v>9.17</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="D60" s="7">
-        <v>9.43</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="E60" s="7">
-        <v>8.9499999999999993</v>
-      </c>
-      <c r="F60" s="8">
-        <v>0.17</v>
-      </c>
-      <c r="G60" s="8">
-        <v>1.89</v>
+        <v>9.1300000000000008</v>
+      </c>
+      <c r="F60" s="10">
+        <v>0.13</v>
+      </c>
+      <c r="G60" s="10">
+        <v>1.42</v>
       </c>
       <c r="H60" s="9">
-        <v>0.67800000000000005</v>
-      </c>
-      <c r="I60" s="10">
-        <v>-2.09</v>
+        <v>0.56599999999999995</v>
+      </c>
+      <c r="I60" s="8">
+        <v>-16.5</v>
       </c>
       <c r="J60" s="8">
-        <v>1.08</v>
+        <v>-33</v>
       </c>
       <c r="K60" s="9">
-        <v>6.07</v>
-      </c>
-      <c r="L60" s="10">
-        <v>-23.4</v>
+        <v>6.64</v>
+      </c>
+      <c r="L60" s="8">
+        <v>-24.3</v>
       </c>
       <c r="M60" s="9">
-        <v>0.67800000000000005</v>
-      </c>
-      <c r="N60" s="10">
-        <v>-2.09</v>
+        <v>0.56599999999999995</v>
+      </c>
+      <c r="N60" s="8">
+        <v>-16.5</v>
       </c>
       <c r="O60" s="8">
-        <v>1.08</v>
+        <v>-33</v>
       </c>
       <c r="P60" s="9">
-        <v>6.07</v>
-      </c>
-      <c r="Q60" s="10">
-        <v>-23.4</v>
+        <v>6.64</v>
+      </c>
+      <c r="Q60" s="8">
+        <v>-24.3</v>
       </c>
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>42979</v>
+        <v>43009</v>
       </c>
       <c r="B61" s="7">
-        <v>8.93</v>
+        <v>9</v>
       </c>
       <c r="C61" s="7">
-        <v>9</v>
+        <v>9.17</v>
       </c>
       <c r="D61" s="7">
-        <v>9.4700000000000006</v>
+        <v>9.43</v>
       </c>
       <c r="E61" s="7">
-        <v>8.83</v>
-      </c>
-      <c r="F61" s="8">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G61" s="8">
-        <v>0.78</v>
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="F61" s="10">
+        <v>0.17</v>
+      </c>
+      <c r="G61" s="10">
+        <v>1.89</v>
       </c>
       <c r="H61" s="9">
-        <v>0.69199999999999995</v>
+        <v>0.67800000000000005</v>
       </c>
       <c r="I61" s="8">
-        <v>6.3</v>
+        <v>-2.09</v>
       </c>
       <c r="J61" s="10">
-        <v>-16.600000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="K61" s="9">
-        <v>5.39</v>
-      </c>
-      <c r="L61" s="10">
-        <v>-25.7</v>
+        <v>6.07</v>
+      </c>
+      <c r="L61" s="8">
+        <v>-23.4</v>
       </c>
       <c r="M61" s="9">
-        <v>0.69199999999999995</v>
+        <v>0.67800000000000005</v>
       </c>
       <c r="N61" s="8">
-        <v>6.3</v>
+        <v>-2.09</v>
       </c>
       <c r="O61" s="10">
-        <v>-16.600000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="P61" s="9">
-        <v>5.39</v>
-      </c>
-      <c r="Q61" s="10">
-        <v>-25.7</v>
+        <v>6.07</v>
+      </c>
+      <c r="Q61" s="8">
+        <v>-23.4</v>
       </c>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>42948</v>
+        <v>42979</v>
       </c>
       <c r="B62" s="7">
-        <v>10</v>
+        <v>8.93</v>
       </c>
       <c r="C62" s="7">
-        <v>8.93</v>
+        <v>9</v>
       </c>
       <c r="D62" s="7">
-        <v>10.1</v>
+        <v>9.4700000000000006</v>
       </c>
       <c r="E62" s="7">
-        <v>8.93</v>
+        <v>8.83</v>
       </c>
       <c r="F62" s="10">
-        <v>-1.07</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G62" s="10">
-        <v>-10.7</v>
+        <v>0.78</v>
       </c>
       <c r="H62" s="9">
-        <v>0.65100000000000002</v>
+        <v>0.69199999999999995</v>
       </c>
       <c r="I62" s="10">
-        <v>-9.1199999999999992</v>
-      </c>
-      <c r="J62" s="10">
-        <v>-14.5</v>
+        <v>6.3</v>
+      </c>
+      <c r="J62" s="8">
+        <v>-16.600000000000001</v>
       </c>
       <c r="K62" s="9">
-        <v>4.7</v>
-      </c>
-      <c r="L62" s="10">
-        <v>-26.8</v>
+        <v>5.39</v>
+      </c>
+      <c r="L62" s="8">
+        <v>-25.7</v>
       </c>
       <c r="M62" s="9">
-        <v>0.65100000000000002</v>
+        <v>0.69199999999999995</v>
       </c>
       <c r="N62" s="10">
-        <v>-9.1199999999999992</v>
-      </c>
-      <c r="O62" s="10">
-        <v>-14.5</v>
+        <v>6.3</v>
+      </c>
+      <c r="O62" s="8">
+        <v>-16.600000000000001</v>
       </c>
       <c r="P62" s="9">
-        <v>4.7</v>
-      </c>
-      <c r="Q62" s="10">
-        <v>-26.8</v>
+        <v>5.39</v>
+      </c>
+      <c r="Q62" s="8">
+        <v>-25.7</v>
       </c>
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>42917</v>
+        <v>42948</v>
       </c>
       <c r="B63" s="7">
-        <v>10.45</v>
+        <v>10</v>
       </c>
       <c r="C63" s="7">
-        <v>10</v>
+        <v>8.93</v>
       </c>
       <c r="D63" s="7">
-        <v>10.48</v>
+        <v>10.1</v>
       </c>
       <c r="E63" s="7">
-        <v>9.61</v>
-      </c>
-      <c r="F63" s="10">
-        <v>-0.45</v>
-      </c>
-      <c r="G63" s="10">
-        <v>-4.3099999999999996</v>
+        <v>8.93</v>
+      </c>
+      <c r="F63" s="8">
+        <v>-1.07</v>
+      </c>
+      <c r="G63" s="8">
+        <v>-10.7</v>
       </c>
       <c r="H63" s="9">
-        <v>0.71599999999999997</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="I63" s="8">
-        <v>4.03</v>
+        <v>-9.1199999999999992</v>
       </c>
       <c r="J63" s="8">
-        <v>6.21</v>
+        <v>-14.5</v>
       </c>
       <c r="K63" s="9">
-        <v>4.05</v>
-      </c>
-      <c r="L63" s="10">
-        <v>-28.5</v>
+        <v>4.7</v>
+      </c>
+      <c r="L63" s="8">
+        <v>-26.8</v>
       </c>
       <c r="M63" s="9">
-        <v>0.71599999999999997</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="N63" s="8">
-        <v>4.03</v>
+        <v>-9.1199999999999992</v>
       </c>
       <c r="O63" s="8">
-        <v>6.21</v>
+        <v>-14.5</v>
       </c>
       <c r="P63" s="9">
-        <v>4.05</v>
-      </c>
-      <c r="Q63" s="10">
-        <v>-28.5</v>
+        <v>4.7</v>
+      </c>
+      <c r="Q63" s="8">
+        <v>-26.8</v>
       </c>
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>42887</v>
+        <v>42917</v>
       </c>
       <c r="B64" s="7">
-        <v>10.24</v>
+        <v>10.45</v>
       </c>
       <c r="C64" s="7">
-        <v>10.45</v>
+        <v>10</v>
       </c>
       <c r="D64" s="7">
-        <v>10.9</v>
+        <v>10.48</v>
       </c>
       <c r="E64" s="7">
-        <v>9.81</v>
+        <v>9.61</v>
       </c>
       <c r="F64" s="8">
-        <v>0.21</v>
+        <v>-0.45</v>
       </c>
       <c r="G64" s="8">
-        <v>2.0499999999999998</v>
+        <v>-4.3099999999999996</v>
       </c>
       <c r="H64" s="9">
-        <v>0.68899999999999995</v>
-      </c>
-      <c r="I64" s="8">
-        <v>0.7</v>
+        <v>0.71599999999999997</v>
+      </c>
+      <c r="I64" s="10">
+        <v>4.03</v>
       </c>
       <c r="J64" s="10">
-        <v>-35.6</v>
+        <v>6.21</v>
       </c>
       <c r="K64" s="9">
-        <v>3.33</v>
-      </c>
-      <c r="L64" s="10">
-        <v>-33.200000000000003</v>
+        <v>4.05</v>
+      </c>
+      <c r="L64" s="8">
+        <v>-28.5</v>
       </c>
       <c r="M64" s="9">
-        <v>0.68899999999999995</v>
-      </c>
-      <c r="N64" s="8">
-        <v>0.7</v>
+        <v>0.71599999999999997</v>
+      </c>
+      <c r="N64" s="10">
+        <v>4.03</v>
       </c>
       <c r="O64" s="10">
-        <v>-35.6</v>
+        <v>6.21</v>
       </c>
       <c r="P64" s="9">
-        <v>3.33</v>
-      </c>
-      <c r="Q64" s="10">
-        <v>-33.200000000000003</v>
+        <v>4.05</v>
+      </c>
+      <c r="Q64" s="8">
+        <v>-28.5</v>
       </c>
     </row>
     <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>42856</v>
+        <v>42887</v>
       </c>
       <c r="B65" s="7">
-        <v>10.83</v>
+        <v>10.24</v>
       </c>
       <c r="C65" s="7">
-        <v>10.24</v>
+        <v>10.45</v>
       </c>
       <c r="D65" s="7">
-        <v>10.83</v>
+        <v>10.9</v>
       </c>
       <c r="E65" s="7">
-        <v>9.8699999999999992</v>
+        <v>9.81</v>
       </c>
       <c r="F65" s="10">
-        <v>-0.59</v>
+        <v>0.21</v>
       </c>
       <c r="G65" s="10">
-        <v>-5.45</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="H65" s="9">
-        <v>0.68400000000000005</v>
-      </c>
-      <c r="I65" s="8">
-        <v>13.7</v>
-      </c>
-      <c r="J65" s="10">
-        <v>-1.9</v>
+        <v>0.68899999999999995</v>
+      </c>
+      <c r="I65" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="J65" s="8">
+        <v>-35.6</v>
       </c>
       <c r="K65" s="9">
-        <v>2.64</v>
-      </c>
-      <c r="L65" s="10">
-        <v>-32.5</v>
+        <v>3.33</v>
+      </c>
+      <c r="L65" s="8">
+        <v>-33.200000000000003</v>
       </c>
       <c r="M65" s="9">
-        <v>0.68400000000000005</v>
-      </c>
-      <c r="N65" s="8">
-        <v>13.7</v>
-      </c>
-      <c r="O65" s="10">
-        <v>-1.9</v>
+        <v>0.68899999999999995</v>
+      </c>
+      <c r="N65" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="O65" s="8">
+        <v>-35.6</v>
       </c>
       <c r="P65" s="9">
-        <v>2.64</v>
-      </c>
-      <c r="Q65" s="10">
-        <v>-32.5</v>
+        <v>3.33</v>
+      </c>
+      <c r="Q65" s="8">
+        <v>-33.200000000000003</v>
       </c>
     </row>
     <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>42826</v>
+        <v>42856</v>
       </c>
       <c r="B66" s="7">
-        <v>10.99</v>
+        <v>10.83</v>
       </c>
       <c r="C66" s="7">
+        <v>10.24</v>
+      </c>
+      <c r="D66" s="7">
         <v>10.83</v>
       </c>
-      <c r="D66" s="7">
-        <v>11.04</v>
-      </c>
       <c r="E66" s="7">
-        <v>10.5</v>
-      </c>
-      <c r="F66" s="10">
-        <v>-0.16</v>
-      </c>
-      <c r="G66" s="10">
-        <v>-1.46</v>
+        <v>9.8699999999999992</v>
+      </c>
+      <c r="F66" s="8">
+        <v>-0.59</v>
+      </c>
+      <c r="G66" s="8">
+        <v>-5.45</v>
       </c>
       <c r="H66" s="9">
-        <v>0.60199999999999998</v>
-      </c>
-      <c r="I66" s="8">
-        <v>6.06</v>
-      </c>
-      <c r="J66" s="10">
-        <v>-30.2</v>
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="I66" s="10">
+        <v>13.7</v>
+      </c>
+      <c r="J66" s="8">
+        <v>-1.9</v>
       </c>
       <c r="K66" s="9">
-        <v>1.96</v>
-      </c>
-      <c r="L66" s="10">
-        <v>-39.1</v>
+        <v>2.64</v>
+      </c>
+      <c r="L66" s="8">
+        <v>-32.5</v>
       </c>
       <c r="M66" s="9">
-        <v>0.60199999999999998</v>
-      </c>
-      <c r="N66" s="8">
-        <v>6.06</v>
-      </c>
-      <c r="O66" s="10">
-        <v>-30.2</v>
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="N66" s="10">
+        <v>13.7</v>
+      </c>
+      <c r="O66" s="8">
+        <v>-1.9</v>
       </c>
       <c r="P66" s="9">
-        <v>1.96</v>
-      </c>
-      <c r="Q66" s="10">
-        <v>-39.1</v>
+        <v>2.64</v>
+      </c>
+      <c r="Q66" s="8">
+        <v>-32.5</v>
       </c>
     </row>
     <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
-        <v>42795</v>
+        <v>42826</v>
       </c>
       <c r="B67" s="7">
-        <v>10.63</v>
+        <v>10.99</v>
       </c>
       <c r="C67" s="7">
-        <v>10.99</v>
+        <v>10.83</v>
       </c>
       <c r="D67" s="7">
-        <v>10.99</v>
+        <v>11.04</v>
       </c>
       <c r="E67" s="7">
         <v>10.5</v>
       </c>
       <c r="F67" s="8">
-        <v>0.36</v>
+        <v>-0.16</v>
       </c>
       <c r="G67" s="8">
-        <v>3.39</v>
+        <v>-1.46</v>
       </c>
       <c r="H67" s="9">
-        <v>0.56699999999999995</v>
-      </c>
-      <c r="I67" s="8">
-        <v>37.799999999999997</v>
-      </c>
-      <c r="J67" s="10">
-        <v>-37.9</v>
+        <v>0.60199999999999998</v>
+      </c>
+      <c r="I67" s="10">
+        <v>6.06</v>
+      </c>
+      <c r="J67" s="8">
+        <v>-30.2</v>
       </c>
       <c r="K67" s="9">
-        <v>1.36</v>
-      </c>
-      <c r="L67" s="10">
-        <v>-42.4</v>
+        <v>1.96</v>
+      </c>
+      <c r="L67" s="8">
+        <v>-39.1</v>
       </c>
       <c r="M67" s="9">
-        <v>0.56699999999999995</v>
-      </c>
-      <c r="N67" s="8">
-        <v>37.799999999999997</v>
-      </c>
-      <c r="O67" s="10">
-        <v>-37.9</v>
+        <v>0.60199999999999998</v>
+      </c>
+      <c r="N67" s="10">
+        <v>6.06</v>
+      </c>
+      <c r="O67" s="8">
+        <v>-30.2</v>
       </c>
       <c r="P67" s="9">
-        <v>1.36</v>
-      </c>
-      <c r="Q67" s="10">
-        <v>-42.4</v>
+        <v>1.96</v>
+      </c>
+      <c r="Q67" s="8">
+        <v>-39.1</v>
       </c>
     </row>
     <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
-        <v>42767</v>
+        <v>42795</v>
       </c>
       <c r="B68" s="7">
+        <v>10.63</v>
+      </c>
+      <c r="C68" s="7">
+        <v>10.99</v>
+      </c>
+      <c r="D68" s="7">
+        <v>10.99</v>
+      </c>
+      <c r="E68" s="7">
         <v>10.5</v>
       </c>
-      <c r="C68" s="7">
-        <v>10.63</v>
-      </c>
-      <c r="D68" s="7">
-        <v>10.83</v>
-      </c>
-      <c r="E68" s="7">
-        <v>10.35</v>
-      </c>
-      <c r="F68" s="8">
-        <v>0.13</v>
-      </c>
-      <c r="G68" s="8">
-        <v>1.24</v>
+      <c r="F68" s="10">
+        <v>0.36</v>
+      </c>
+      <c r="G68" s="10">
+        <v>3.39</v>
       </c>
       <c r="H68" s="9">
-        <v>0.41199999999999998</v>
-      </c>
-      <c r="I68" s="8">
-        <v>8.35</v>
-      </c>
-      <c r="J68" s="10">
-        <v>-27.6</v>
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="I68" s="10">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="J68" s="8">
+        <v>-37.9</v>
       </c>
       <c r="K68" s="9">
-        <v>0.79100000000000004</v>
-      </c>
-      <c r="L68" s="10">
-        <v>-45.2</v>
+        <v>1.36</v>
+      </c>
+      <c r="L68" s="8">
+        <v>-42.4</v>
       </c>
       <c r="M68" s="9">
-        <v>0.41199999999999998</v>
-      </c>
-      <c r="N68" s="8">
-        <v>8.35</v>
-      </c>
-      <c r="O68" s="10">
-        <v>-27.6</v>
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="N68" s="10">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="O68" s="8">
+        <v>-37.9</v>
       </c>
       <c r="P68" s="9">
-        <v>0.79100000000000004</v>
-      </c>
-      <c r="Q68" s="10">
-        <v>-45.2</v>
+        <v>1.36</v>
+      </c>
+      <c r="Q68" s="8">
+        <v>-42.4</v>
       </c>
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
-        <v>42736</v>
+        <v>42767</v>
       </c>
       <c r="B69" s="7">
         <v>10.5</v>
       </c>
       <c r="C69" s="7">
-        <v>10.5</v>
+        <v>10.63</v>
       </c>
       <c r="D69" s="7">
-        <v>10.73</v>
+        <v>10.83</v>
       </c>
       <c r="E69" s="7">
-        <v>10.220000000000001</v>
-      </c>
-      <c r="F69" s="9">
-        <v>0</v>
-      </c>
-      <c r="G69" s="9">
-        <v>0</v>
+        <v>10.35</v>
+      </c>
+      <c r="F69" s="10">
+        <v>0.13</v>
+      </c>
+      <c r="G69" s="10">
+        <v>1.24</v>
       </c>
       <c r="H69" s="9">
-        <v>0.38</v>
+        <v>0.41199999999999998</v>
       </c>
       <c r="I69" s="10">
-        <v>-37.299999999999997</v>
-      </c>
-      <c r="J69" s="10">
-        <v>-56.7</v>
+        <v>8.35</v>
+      </c>
+      <c r="J69" s="8">
+        <v>-27.6</v>
       </c>
       <c r="K69" s="9">
-        <v>0.38</v>
-      </c>
-      <c r="L69" s="10">
-        <v>-56.7</v>
+        <v>0.79100000000000004</v>
+      </c>
+      <c r="L69" s="8">
+        <v>-45.2</v>
       </c>
       <c r="M69" s="9">
-        <v>0.38</v>
+        <v>0.41199999999999998</v>
       </c>
       <c r="N69" s="10">
-        <v>-37.299999999999997</v>
-      </c>
-      <c r="O69" s="10">
-        <v>-56.7</v>
+        <v>8.35</v>
+      </c>
+      <c r="O69" s="8">
+        <v>-27.6</v>
       </c>
       <c r="P69" s="9">
-        <v>0.38</v>
-      </c>
-      <c r="Q69" s="10">
-        <v>-56.7</v>
+        <v>0.79100000000000004</v>
+      </c>
+      <c r="Q69" s="8">
+        <v>-45.2</v>
       </c>
     </row>
     <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
-        <v>42705</v>
+        <v>42736</v>
       </c>
       <c r="B70" s="7">
         <v>10.5</v>
@@ -4837,10 +4837,10 @@
         <v>10.5</v>
       </c>
       <c r="D70" s="7">
-        <v>10.84</v>
+        <v>10.73</v>
       </c>
       <c r="E70" s="7">
-        <v>9.9600000000000009</v>
+        <v>10.220000000000001</v>
       </c>
       <c r="F70" s="9">
         <v>0</v>
@@ -4849,1523 +4849,1523 @@
         <v>0</v>
       </c>
       <c r="H70" s="9">
-        <v>0.60599999999999998</v>
-      </c>
-      <c r="I70" s="10">
-        <v>-28.3</v>
-      </c>
-      <c r="J70" s="10">
-        <v>-41.3</v>
+        <v>0.38</v>
+      </c>
+      <c r="I70" s="8">
+        <v>-37.299999999999997</v>
+      </c>
+      <c r="J70" s="8">
+        <v>-56.7</v>
       </c>
       <c r="K70" s="9">
-        <v>9.3800000000000008</v>
-      </c>
-      <c r="L70" s="10">
-        <v>-9.15</v>
+        <v>0.38</v>
+      </c>
+      <c r="L70" s="8">
+        <v>-56.7</v>
       </c>
       <c r="M70" s="9">
-        <v>0.60599999999999998</v>
-      </c>
-      <c r="N70" s="10">
-        <v>-28.3</v>
-      </c>
-      <c r="O70" s="10">
-        <v>-41.3</v>
+        <v>0.38</v>
+      </c>
+      <c r="N70" s="8">
+        <v>-37.299999999999997</v>
+      </c>
+      <c r="O70" s="8">
+        <v>-56.7</v>
       </c>
       <c r="P70" s="9">
-        <v>9.3800000000000008</v>
-      </c>
-      <c r="Q70" s="10">
-        <v>-9.15</v>
+        <v>0.38</v>
+      </c>
+      <c r="Q70" s="8">
+        <v>-56.7</v>
       </c>
     </row>
     <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
-        <v>42675</v>
+        <v>42705</v>
       </c>
       <c r="B71" s="7">
-        <v>12.01</v>
+        <v>10.5</v>
       </c>
       <c r="C71" s="7">
         <v>10.5</v>
       </c>
       <c r="D71" s="7">
-        <v>12.01</v>
+        <v>10.84</v>
       </c>
       <c r="E71" s="7">
-        <v>10</v>
-      </c>
-      <c r="F71" s="10">
-        <v>-1.51</v>
-      </c>
-      <c r="G71" s="10">
-        <v>-12.57</v>
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="F71" s="9">
+        <v>0</v>
+      </c>
+      <c r="G71" s="9">
+        <v>0</v>
       </c>
       <c r="H71" s="9">
-        <v>0.84499999999999997</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="I71" s="8">
-        <v>26</v>
-      </c>
-      <c r="J71" s="10">
-        <v>-17.3</v>
+        <v>-28.3</v>
+      </c>
+      <c r="J71" s="8">
+        <v>-41.3</v>
       </c>
       <c r="K71" s="9">
-        <v>8.77</v>
-      </c>
-      <c r="L71" s="10">
-        <v>-5.59</v>
+        <v>9.3800000000000008</v>
+      </c>
+      <c r="L71" s="8">
+        <v>-9.15</v>
       </c>
       <c r="M71" s="9">
-        <v>0.84499999999999997</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="N71" s="8">
-        <v>26</v>
-      </c>
-      <c r="O71" s="10">
-        <v>-17.3</v>
+        <v>-28.3</v>
+      </c>
+      <c r="O71" s="8">
+        <v>-41.3</v>
       </c>
       <c r="P71" s="9">
-        <v>8.77</v>
-      </c>
-      <c r="Q71" s="10">
-        <v>-5.59</v>
+        <v>9.3800000000000008</v>
+      </c>
+      <c r="Q71" s="8">
+        <v>-9.15</v>
       </c>
     </row>
     <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
-        <v>42644</v>
+        <v>42675</v>
       </c>
       <c r="B72" s="7">
-        <v>12.5</v>
+        <v>12.01</v>
       </c>
       <c r="C72" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="D72" s="7">
         <v>12.01</v>
       </c>
-      <c r="D72" s="7">
-        <v>12.6</v>
-      </c>
       <c r="E72" s="7">
-        <v>11.88</v>
-      </c>
-      <c r="F72" s="10">
-        <v>-0.49</v>
-      </c>
-      <c r="G72" s="10">
-        <v>-3.92</v>
+        <v>10</v>
+      </c>
+      <c r="F72" s="8">
+        <v>-1.51</v>
+      </c>
+      <c r="G72" s="8">
+        <v>-12.57</v>
       </c>
       <c r="H72" s="9">
-        <v>0.67</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="I72" s="10">
-        <v>-19.2</v>
-      </c>
-      <c r="J72" s="10">
-        <v>-24.4</v>
+        <v>26</v>
+      </c>
+      <c r="J72" s="8">
+        <v>-17.3</v>
       </c>
       <c r="K72" s="9">
-        <v>7.92</v>
-      </c>
-      <c r="L72" s="10">
-        <v>-4.1500000000000004</v>
+        <v>8.77</v>
+      </c>
+      <c r="L72" s="8">
+        <v>-5.59</v>
       </c>
       <c r="M72" s="9">
-        <v>0.67</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="N72" s="10">
-        <v>-19.2</v>
-      </c>
-      <c r="O72" s="10">
-        <v>-24.4</v>
+        <v>26</v>
+      </c>
+      <c r="O72" s="8">
+        <v>-17.3</v>
       </c>
       <c r="P72" s="9">
-        <v>7.92</v>
-      </c>
-      <c r="Q72" s="10">
-        <v>-4.1500000000000004</v>
+        <v>8.77</v>
+      </c>
+      <c r="Q72" s="8">
+        <v>-5.59</v>
       </c>
     </row>
     <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
-        <v>42614</v>
+        <v>42644</v>
       </c>
       <c r="B73" s="7">
-        <v>11.93</v>
+        <v>12.5</v>
       </c>
       <c r="C73" s="7">
-        <v>12.5</v>
+        <v>12.01</v>
       </c>
       <c r="D73" s="7">
-        <v>12.55</v>
+        <v>12.6</v>
       </c>
       <c r="E73" s="7">
-        <v>11.71</v>
+        <v>11.88</v>
       </c>
       <c r="F73" s="8">
-        <v>0.56999999999999995</v>
+        <v>-0.49</v>
       </c>
       <c r="G73" s="8">
-        <v>4.78</v>
+        <v>-3.92</v>
       </c>
       <c r="H73" s="9">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="I73" s="8">
-        <v>8.98</v>
+        <v>-19.2</v>
       </c>
       <c r="J73" s="8">
-        <v>1.84</v>
+        <v>-24.4</v>
       </c>
       <c r="K73" s="9">
-        <v>7.25</v>
-      </c>
-      <c r="L73" s="10">
-        <v>-1.71</v>
+        <v>7.92</v>
+      </c>
+      <c r="L73" s="8">
+        <v>-4.1500000000000004</v>
       </c>
       <c r="M73" s="9">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="N73" s="8">
-        <v>8.98</v>
+        <v>-19.2</v>
       </c>
       <c r="O73" s="8">
-        <v>1.84</v>
+        <v>-24.4</v>
       </c>
       <c r="P73" s="9">
-        <v>7.25</v>
-      </c>
-      <c r="Q73" s="10">
-        <v>-1.71</v>
+        <v>7.92</v>
+      </c>
+      <c r="Q73" s="8">
+        <v>-4.1500000000000004</v>
       </c>
     </row>
     <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
-        <v>42583</v>
+        <v>42614</v>
       </c>
       <c r="B74" s="7">
-        <v>12.54</v>
+        <v>11.93</v>
       </c>
       <c r="C74" s="7">
-        <v>11.93</v>
+        <v>12.5</v>
       </c>
       <c r="D74" s="7">
-        <v>12.86</v>
+        <v>12.55</v>
       </c>
       <c r="E74" s="7">
-        <v>11.93</v>
+        <v>11.71</v>
       </c>
       <c r="F74" s="10">
-        <v>-0.61</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="G74" s="10">
-        <v>-4.8600000000000003</v>
+        <v>4.78</v>
       </c>
       <c r="H74" s="9">
-        <v>0.76100000000000001</v>
-      </c>
-      <c r="I74" s="8">
-        <v>12.9</v>
+        <v>0.83</v>
+      </c>
+      <c r="I74" s="10">
+        <v>8.98</v>
       </c>
       <c r="J74" s="10">
-        <v>-4.87</v>
+        <v>1.84</v>
       </c>
       <c r="K74" s="9">
-        <v>6.42</v>
-      </c>
-      <c r="L74" s="10">
-        <v>-2.15</v>
+        <v>7.25</v>
+      </c>
+      <c r="L74" s="8">
+        <v>-1.71</v>
       </c>
       <c r="M74" s="9">
-        <v>0.76100000000000001</v>
-      </c>
-      <c r="N74" s="8">
-        <v>12.9</v>
+        <v>0.83</v>
+      </c>
+      <c r="N74" s="10">
+        <v>8.98</v>
       </c>
       <c r="O74" s="10">
-        <v>-4.87</v>
+        <v>1.84</v>
       </c>
       <c r="P74" s="9">
-        <v>6.42</v>
-      </c>
-      <c r="Q74" s="10">
-        <v>-2.15</v>
+        <v>7.25</v>
+      </c>
+      <c r="Q74" s="8">
+        <v>-1.71</v>
       </c>
     </row>
     <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
-        <v>42552</v>
+        <v>42583</v>
       </c>
       <c r="B75" s="7">
-        <v>12.2</v>
+        <v>12.54</v>
       </c>
       <c r="C75" s="7">
-        <v>12.54</v>
+        <v>11.93</v>
       </c>
       <c r="D75" s="7">
-        <v>12.55</v>
+        <v>12.86</v>
       </c>
       <c r="E75" s="7">
-        <v>11.95</v>
+        <v>11.93</v>
       </c>
       <c r="F75" s="8">
-        <v>0.34</v>
+        <v>-0.61</v>
       </c>
       <c r="G75" s="8">
-        <v>2.79</v>
+        <v>-4.8600000000000003</v>
       </c>
       <c r="H75" s="9">
-        <v>0.67500000000000004</v>
+        <v>0.76100000000000001</v>
       </c>
       <c r="I75" s="10">
-        <v>-37</v>
-      </c>
-      <c r="J75" s="10">
-        <v>-16.600000000000001</v>
+        <v>12.9</v>
+      </c>
+      <c r="J75" s="8">
+        <v>-4.87</v>
       </c>
       <c r="K75" s="9">
-        <v>5.66</v>
-      </c>
-      <c r="L75" s="10">
-        <v>-1.77</v>
+        <v>6.42</v>
+      </c>
+      <c r="L75" s="8">
+        <v>-2.15</v>
       </c>
       <c r="M75" s="9">
-        <v>0.67500000000000004</v>
+        <v>0.76100000000000001</v>
       </c>
       <c r="N75" s="10">
-        <v>-37</v>
-      </c>
-      <c r="O75" s="10">
-        <v>-16.600000000000001</v>
+        <v>12.9</v>
+      </c>
+      <c r="O75" s="8">
+        <v>-4.87</v>
       </c>
       <c r="P75" s="9">
-        <v>5.66</v>
-      </c>
-      <c r="Q75" s="10">
-        <v>-1.77</v>
+        <v>6.42</v>
+      </c>
+      <c r="Q75" s="8">
+        <v>-2.15</v>
       </c>
     </row>
     <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
-        <v>42522</v>
+        <v>42552</v>
       </c>
       <c r="B76" s="7">
-        <v>12.21</v>
+        <v>12.2</v>
       </c>
       <c r="C76" s="7">
-        <v>12.2</v>
+        <v>12.54</v>
       </c>
       <c r="D76" s="7">
-        <v>12.56</v>
+        <v>12.55</v>
       </c>
       <c r="E76" s="7">
-        <v>12</v>
+        <v>11.95</v>
       </c>
       <c r="F76" s="10">
-        <v>-0.01</v>
+        <v>0.34</v>
       </c>
       <c r="G76" s="10">
-        <v>-0.08</v>
+        <v>2.79</v>
       </c>
       <c r="H76" s="9">
-        <v>1.07</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="I76" s="8">
-        <v>53.5</v>
+        <v>-37</v>
       </c>
       <c r="J76" s="8">
-        <v>8.5399999999999991</v>
+        <v>-16.600000000000001</v>
       </c>
       <c r="K76" s="9">
-        <v>4.99</v>
+        <v>5.66</v>
       </c>
       <c r="L76" s="8">
-        <v>0.63</v>
+        <v>-1.77</v>
       </c>
       <c r="M76" s="9">
-        <v>1.07</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="N76" s="8">
-        <v>53.5</v>
+        <v>-37</v>
       </c>
       <c r="O76" s="8">
-        <v>8.5399999999999991</v>
+        <v>-16.600000000000001</v>
       </c>
       <c r="P76" s="9">
-        <v>4.99</v>
+        <v>5.66</v>
       </c>
       <c r="Q76" s="8">
-        <v>0.63</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
-        <v>42491</v>
+        <v>42522</v>
       </c>
       <c r="B77" s="7">
-        <v>12.4</v>
+        <v>12.21</v>
       </c>
       <c r="C77" s="7">
-        <v>12.21</v>
+        <v>12.2</v>
       </c>
       <c r="D77" s="7">
-        <v>12.6</v>
+        <v>12.56</v>
       </c>
       <c r="E77" s="7">
-        <v>11.88</v>
-      </c>
-      <c r="F77" s="10">
-        <v>-0.19</v>
-      </c>
-      <c r="G77" s="10">
-        <v>-1.53</v>
+        <v>12</v>
+      </c>
+      <c r="F77" s="8">
+        <v>-0.01</v>
+      </c>
+      <c r="G77" s="8">
+        <v>-0.08</v>
       </c>
       <c r="H77" s="9">
-        <v>0.69699999999999995</v>
+        <v>1.07</v>
       </c>
       <c r="I77" s="10">
-        <v>-19.100000000000001</v>
+        <v>53.5</v>
       </c>
       <c r="J77" s="10">
-        <v>-22.4</v>
+        <v>8.5399999999999991</v>
       </c>
       <c r="K77" s="9">
-        <v>3.92</v>
+        <v>4.99</v>
       </c>
       <c r="L77" s="10">
-        <v>-1.33</v>
+        <v>0.63</v>
       </c>
       <c r="M77" s="9">
-        <v>0.69699999999999995</v>
+        <v>1.07</v>
       </c>
       <c r="N77" s="10">
-        <v>-19.100000000000001</v>
+        <v>53.5</v>
       </c>
       <c r="O77" s="10">
-        <v>-22.4</v>
+        <v>8.5399999999999991</v>
       </c>
       <c r="P77" s="9">
-        <v>3.92</v>
+        <v>4.99</v>
       </c>
       <c r="Q77" s="10">
-        <v>-1.33</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
-        <v>42461</v>
+        <v>42491</v>
       </c>
       <c r="B78" s="7">
-        <v>13.6</v>
+        <v>12.4</v>
       </c>
       <c r="C78" s="7">
-        <v>12.4</v>
+        <v>12.21</v>
       </c>
       <c r="D78" s="7">
-        <v>13.7</v>
+        <v>12.6</v>
       </c>
       <c r="E78" s="7">
-        <v>12.35</v>
-      </c>
-      <c r="F78" s="10">
-        <v>-1.2</v>
-      </c>
-      <c r="G78" s="10">
-        <v>-8.82</v>
+        <v>11.88</v>
+      </c>
+      <c r="F78" s="8">
+        <v>-0.19</v>
+      </c>
+      <c r="G78" s="8">
+        <v>-1.53</v>
       </c>
       <c r="H78" s="9">
-        <v>0.86199999999999999</v>
-      </c>
-      <c r="I78" s="10">
-        <v>-5.55</v>
+        <v>0.69699999999999995</v>
+      </c>
+      <c r="I78" s="8">
+        <v>-19.100000000000001</v>
       </c>
       <c r="J78" s="8">
-        <v>0.56999999999999995</v>
+        <v>-22.4</v>
       </c>
       <c r="K78" s="9">
-        <v>3.22</v>
+        <v>3.92</v>
       </c>
       <c r="L78" s="8">
-        <v>4.84</v>
+        <v>-1.33</v>
       </c>
       <c r="M78" s="9">
-        <v>0.86199999999999999</v>
-      </c>
-      <c r="N78" s="10">
-        <v>-5.55</v>
+        <v>0.69699999999999995</v>
+      </c>
+      <c r="N78" s="8">
+        <v>-19.100000000000001</v>
       </c>
       <c r="O78" s="8">
-        <v>0.56999999999999995</v>
+        <v>-22.4</v>
       </c>
       <c r="P78" s="9">
-        <v>3.22</v>
+        <v>3.92</v>
       </c>
       <c r="Q78" s="8">
-        <v>4.84</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
-        <v>42430</v>
+        <v>42461</v>
       </c>
       <c r="B79" s="7">
-        <v>14.04</v>
+        <v>13.6</v>
       </c>
       <c r="C79" s="7">
-        <v>13.6</v>
+        <v>12.4</v>
       </c>
       <c r="D79" s="7">
-        <v>14.21</v>
+        <v>13.7</v>
       </c>
       <c r="E79" s="7">
-        <v>13.6</v>
-      </c>
-      <c r="F79" s="10">
-        <v>-0.44</v>
-      </c>
-      <c r="G79" s="10">
-        <v>-3.13</v>
+        <v>12.35</v>
+      </c>
+      <c r="F79" s="8">
+        <v>-1.2</v>
+      </c>
+      <c r="G79" s="8">
+        <v>-8.82</v>
       </c>
       <c r="H79" s="9">
-        <v>0.91300000000000003</v>
+        <v>0.86199999999999999</v>
       </c>
       <c r="I79" s="8">
-        <v>60.6</v>
+        <v>-5.55</v>
       </c>
       <c r="J79" s="10">
-        <v>-2.14</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="K79" s="9">
-        <v>2.36</v>
-      </c>
-      <c r="L79" s="8">
-        <v>6.49</v>
+        <v>3.22</v>
+      </c>
+      <c r="L79" s="10">
+        <v>4.84</v>
       </c>
       <c r="M79" s="9">
-        <v>0.91300000000000003</v>
+        <v>0.86199999999999999</v>
       </c>
       <c r="N79" s="8">
-        <v>60.6</v>
+        <v>-5.55</v>
       </c>
       <c r="O79" s="10">
-        <v>-2.14</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="P79" s="9">
-        <v>2.36</v>
-      </c>
-      <c r="Q79" s="8">
-        <v>6.49</v>
+        <v>3.22</v>
+      </c>
+      <c r="Q79" s="10">
+        <v>4.84</v>
       </c>
     </row>
     <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
-        <v>42401</v>
+        <v>42430</v>
       </c>
       <c r="B80" s="7">
-        <v>14.45</v>
+        <v>14.04</v>
       </c>
       <c r="C80" s="7">
-        <v>14.04</v>
+        <v>13.6</v>
       </c>
       <c r="D80" s="7">
-        <v>14.4</v>
+        <v>14.21</v>
       </c>
       <c r="E80" s="7">
-        <v>14</v>
-      </c>
-      <c r="F80" s="10">
-        <v>-0.41</v>
-      </c>
-      <c r="G80" s="10">
-        <v>-2.84</v>
+        <v>13.6</v>
+      </c>
+      <c r="F80" s="8">
+        <v>-0.44</v>
+      </c>
+      <c r="G80" s="8">
+        <v>-3.13</v>
       </c>
       <c r="H80" s="9">
-        <v>0.56899999999999995</v>
+        <v>0.91300000000000003</v>
       </c>
       <c r="I80" s="10">
-        <v>-35.200000000000003</v>
+        <v>60.6</v>
       </c>
       <c r="J80" s="8">
-        <v>5.16</v>
+        <v>-2.14</v>
       </c>
       <c r="K80" s="9">
-        <v>1.45</v>
-      </c>
-      <c r="L80" s="8">
-        <v>12.8</v>
+        <v>2.36</v>
+      </c>
+      <c r="L80" s="10">
+        <v>6.49</v>
       </c>
       <c r="M80" s="9">
-        <v>0.56899999999999995</v>
+        <v>0.91300000000000003</v>
       </c>
       <c r="N80" s="10">
-        <v>-35.200000000000003</v>
+        <v>60.6</v>
       </c>
       <c r="O80" s="8">
-        <v>5.16</v>
+        <v>-2.14</v>
       </c>
       <c r="P80" s="9">
-        <v>1.45</v>
-      </c>
-      <c r="Q80" s="8">
-        <v>12.8</v>
+        <v>2.36</v>
+      </c>
+      <c r="Q80" s="10">
+        <v>6.49</v>
       </c>
     </row>
     <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
-        <v>42370</v>
+        <v>42401</v>
       </c>
       <c r="B81" s="7">
-        <v>14.5</v>
+        <v>14.45</v>
       </c>
       <c r="C81" s="7">
-        <v>14.45</v>
+        <v>14.04</v>
       </c>
       <c r="D81" s="7">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="E81" s="7">
-        <v>14.05</v>
-      </c>
-      <c r="F81" s="10">
-        <v>-0.05</v>
-      </c>
-      <c r="G81" s="10">
-        <v>-0.34</v>
+        <v>14</v>
+      </c>
+      <c r="F81" s="8">
+        <v>-0.41</v>
+      </c>
+      <c r="G81" s="8">
+        <v>-2.84</v>
       </c>
       <c r="H81" s="9">
-        <v>0.877</v>
-      </c>
-      <c r="I81" s="10">
-        <v>-14.9</v>
-      </c>
-      <c r="J81" s="8">
-        <v>18.3</v>
+        <v>0.56899999999999995</v>
+      </c>
+      <c r="I81" s="8">
+        <v>-35.200000000000003</v>
+      </c>
+      <c r="J81" s="10">
+        <v>5.16</v>
       </c>
       <c r="K81" s="9">
-        <v>0.877</v>
-      </c>
-      <c r="L81" s="8">
-        <v>18.3</v>
+        <v>1.45</v>
+      </c>
+      <c r="L81" s="10">
+        <v>12.8</v>
       </c>
       <c r="M81" s="9">
-        <v>0.877</v>
-      </c>
-      <c r="N81" s="10">
-        <v>-14.9</v>
-      </c>
-      <c r="O81" s="8">
-        <v>18.3</v>
+        <v>0.56899999999999995</v>
+      </c>
+      <c r="N81" s="8">
+        <v>-35.200000000000003</v>
+      </c>
+      <c r="O81" s="10">
+        <v>5.16</v>
       </c>
       <c r="P81" s="9">
-        <v>0.877</v>
-      </c>
-      <c r="Q81" s="8">
-        <v>18.3</v>
+        <v>1.45</v>
+      </c>
+      <c r="Q81" s="10">
+        <v>12.8</v>
       </c>
     </row>
     <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
-        <v>42339</v>
+        <v>42370</v>
       </c>
       <c r="B82" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="C82" s="7">
+        <v>14.45</v>
+      </c>
+      <c r="D82" s="7">
         <v>14.5</v>
       </c>
-      <c r="D82" s="7">
-        <v>14.6</v>
-      </c>
       <c r="E82" s="7">
-        <v>13.93</v>
+        <v>14.05</v>
       </c>
       <c r="F82" s="8">
-        <v>0.3</v>
+        <v>-0.05</v>
       </c>
       <c r="G82" s="8">
-        <v>2.11</v>
+        <v>-0.34</v>
       </c>
       <c r="H82" s="9">
-        <v>1.03</v>
+        <v>0.877</v>
       </c>
       <c r="I82" s="8">
-        <v>0.95</v>
-      </c>
-      <c r="J82" s="8">
-        <v>22.7</v>
+        <v>-14.9</v>
+      </c>
+      <c r="J82" s="10">
+        <v>18.3</v>
       </c>
       <c r="K82" s="9">
-        <v>10.32</v>
-      </c>
-      <c r="L82" s="8">
-        <v>3.23</v>
+        <v>0.877</v>
+      </c>
+      <c r="L82" s="10">
+        <v>18.3</v>
       </c>
       <c r="M82" s="9">
-        <v>1.03</v>
+        <v>0.877</v>
       </c>
       <c r="N82" s="8">
-        <v>0.95</v>
-      </c>
-      <c r="O82" s="8">
-        <v>22.7</v>
+        <v>-14.9</v>
+      </c>
+      <c r="O82" s="10">
+        <v>18.3</v>
       </c>
       <c r="P82" s="9">
-        <v>10.32</v>
-      </c>
-      <c r="Q82" s="8">
-        <v>3.23</v>
+        <v>0.877</v>
+      </c>
+      <c r="Q82" s="10">
+        <v>18.3</v>
       </c>
     </row>
     <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
-        <v>42309</v>
+        <v>42339</v>
       </c>
       <c r="B83" s="7">
-        <v>17.059999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="C83" s="7">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="D83" s="7">
-        <v>17.059999999999999</v>
+        <v>14.6</v>
       </c>
       <c r="E83" s="7">
-        <v>14.1</v>
+        <v>13.93</v>
       </c>
       <c r="F83" s="10">
-        <v>-2.86</v>
+        <v>0.3</v>
       </c>
       <c r="G83" s="10">
-        <v>-16.760000000000002</v>
+        <v>2.11</v>
       </c>
       <c r="H83" s="9">
-        <v>1.02</v>
-      </c>
-      <c r="I83" s="8">
-        <v>15.1</v>
-      </c>
-      <c r="J83" s="8">
-        <v>28.6</v>
+        <v>1.03</v>
+      </c>
+      <c r="I83" s="10">
+        <v>0.95</v>
+      </c>
+      <c r="J83" s="10">
+        <v>22.7</v>
       </c>
       <c r="K83" s="9">
-        <v>9.2899999999999991</v>
-      </c>
-      <c r="L83" s="8">
-        <v>1.44</v>
+        <v>10.32</v>
+      </c>
+      <c r="L83" s="10">
+        <v>3.23</v>
       </c>
       <c r="M83" s="9">
-        <v>1.02</v>
-      </c>
-      <c r="N83" s="8">
-        <v>15.1</v>
-      </c>
-      <c r="O83" s="8">
-        <v>28.6</v>
+        <v>1.03</v>
+      </c>
+      <c r="N83" s="10">
+        <v>0.95</v>
+      </c>
+      <c r="O83" s="10">
+        <v>22.7</v>
       </c>
       <c r="P83" s="9">
-        <v>9.2899999999999991</v>
-      </c>
-      <c r="Q83" s="8">
-        <v>1.44</v>
+        <v>10.32</v>
+      </c>
+      <c r="Q83" s="10">
+        <v>3.23</v>
       </c>
     </row>
     <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
-        <v>42278</v>
+        <v>42309</v>
       </c>
       <c r="B84" s="7">
-        <v>15</v>
+        <v>17.059999999999999</v>
       </c>
       <c r="C84" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="D84" s="7">
         <v>17.059999999999999</v>
       </c>
-      <c r="D84" s="7">
-        <v>17.190000000000001</v>
-      </c>
       <c r="E84" s="7">
-        <v>14.91</v>
+        <v>14.1</v>
       </c>
       <c r="F84" s="8">
-        <v>2.06</v>
+        <v>-2.86</v>
       </c>
       <c r="G84" s="8">
-        <v>13.73</v>
+        <v>-16.760000000000002</v>
       </c>
       <c r="H84" s="9">
-        <v>0.88700000000000001</v>
-      </c>
-      <c r="I84" s="8">
-        <v>8.8800000000000008</v>
-      </c>
-      <c r="J84" s="8">
-        <v>19.100000000000001</v>
+        <v>1.02</v>
+      </c>
+      <c r="I84" s="10">
+        <v>15.1</v>
+      </c>
+      <c r="J84" s="10">
+        <v>28.6</v>
       </c>
       <c r="K84" s="9">
-        <v>8.27</v>
+        <v>9.2899999999999991</v>
       </c>
       <c r="L84" s="10">
-        <v>-1.1299999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="M84" s="9">
-        <v>0.88700000000000001</v>
-      </c>
-      <c r="N84" s="8">
-        <v>8.8800000000000008</v>
-      </c>
-      <c r="O84" s="8">
-        <v>19.100000000000001</v>
+        <v>1.02</v>
+      </c>
+      <c r="N84" s="10">
+        <v>15.1</v>
+      </c>
+      <c r="O84" s="10">
+        <v>28.6</v>
       </c>
       <c r="P84" s="9">
-        <v>8.27</v>
+        <v>9.2899999999999991</v>
       </c>
       <c r="Q84" s="10">
-        <v>-1.1299999999999999</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
-        <v>42248</v>
+        <v>42278</v>
       </c>
       <c r="B85" s="7">
-        <v>11.58</v>
+        <v>15</v>
       </c>
       <c r="C85" s="7">
-        <v>15</v>
+        <v>17.059999999999999</v>
       </c>
       <c r="D85" s="7">
-        <v>15.1</v>
+        <v>17.190000000000001</v>
       </c>
       <c r="E85" s="7">
-        <v>11</v>
-      </c>
-      <c r="F85" s="8">
-        <v>3.42</v>
-      </c>
-      <c r="G85" s="8">
-        <v>29.53</v>
+        <v>14.91</v>
+      </c>
+      <c r="F85" s="10">
+        <v>2.06</v>
+      </c>
+      <c r="G85" s="10">
+        <v>13.73</v>
       </c>
       <c r="H85" s="9">
-        <v>0.81499999999999995</v>
-      </c>
-      <c r="I85" s="8">
-        <v>1.8</v>
+        <v>0.88700000000000001</v>
+      </c>
+      <c r="I85" s="10">
+        <v>8.8800000000000008</v>
       </c>
       <c r="J85" s="10">
-        <v>-11.1</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="K85" s="9">
-        <v>7.38</v>
-      </c>
-      <c r="L85" s="10">
-        <v>-3.1</v>
+        <v>8.27</v>
+      </c>
+      <c r="L85" s="8">
+        <v>-1.1299999999999999</v>
       </c>
       <c r="M85" s="9">
-        <v>0.81499999999999995</v>
-      </c>
-      <c r="N85" s="8">
-        <v>1.8</v>
+        <v>0.88700000000000001</v>
+      </c>
+      <c r="N85" s="10">
+        <v>8.8800000000000008</v>
       </c>
       <c r="O85" s="10">
-        <v>-11.1</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="P85" s="9">
-        <v>7.38</v>
-      </c>
-      <c r="Q85" s="10">
-        <v>-3.1</v>
+        <v>8.27</v>
+      </c>
+      <c r="Q85" s="8">
+        <v>-1.1299999999999999</v>
       </c>
     </row>
     <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
-        <v>42217</v>
+        <v>42248</v>
       </c>
       <c r="B86" s="7">
-        <v>16.149999999999999</v>
+        <v>11.58</v>
       </c>
       <c r="C86" s="7">
-        <v>11.58</v>
+        <v>15</v>
       </c>
       <c r="D86" s="7">
-        <v>16.600000000000001</v>
+        <v>15.1</v>
       </c>
       <c r="E86" s="7">
-        <v>11.08</v>
+        <v>11</v>
       </c>
       <c r="F86" s="10">
-        <v>-4.57</v>
+        <v>3.42</v>
       </c>
       <c r="G86" s="10">
-        <v>-28.3</v>
+        <v>29.53</v>
       </c>
       <c r="H86" s="9">
-        <v>0.8</v>
+        <v>0.81499999999999995</v>
       </c>
       <c r="I86" s="10">
-        <v>-0.99</v>
-      </c>
-      <c r="J86" s="10">
-        <v>-29</v>
+        <v>1.8</v>
+      </c>
+      <c r="J86" s="8">
+        <v>-11.1</v>
       </c>
       <c r="K86" s="9">
-        <v>6.57</v>
-      </c>
-      <c r="L86" s="10">
-        <v>-2.0099999999999998</v>
+        <v>7.38</v>
+      </c>
+      <c r="L86" s="8">
+        <v>-3.1</v>
       </c>
       <c r="M86" s="9">
-        <v>0.8</v>
+        <v>0.81499999999999995</v>
       </c>
       <c r="N86" s="10">
-        <v>-0.99</v>
-      </c>
-      <c r="O86" s="10">
-        <v>-29</v>
+        <v>1.8</v>
+      </c>
+      <c r="O86" s="8">
+        <v>-11.1</v>
       </c>
       <c r="P86" s="9">
-        <v>6.57</v>
-      </c>
-      <c r="Q86" s="10">
-        <v>-2.0099999999999998</v>
+        <v>7.38</v>
+      </c>
+      <c r="Q86" s="8">
+        <v>-3.1</v>
       </c>
     </row>
     <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
-        <v>42186</v>
+        <v>42217</v>
       </c>
       <c r="B87" s="7">
-        <v>17.350000000000001</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="C87" s="7">
-        <v>16.149999999999999</v>
+        <v>11.58</v>
       </c>
       <c r="D87" s="7">
-        <v>17.3</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="E87" s="7">
-        <v>16.05</v>
-      </c>
-      <c r="F87" s="10">
-        <v>-1.2</v>
-      </c>
-      <c r="G87" s="10">
-        <v>-6.92</v>
+        <v>11.08</v>
+      </c>
+      <c r="F87" s="8">
+        <v>-4.57</v>
+      </c>
+      <c r="G87" s="8">
+        <v>-28.3</v>
       </c>
       <c r="H87" s="9">
-        <v>0.80900000000000005</v>
-      </c>
-      <c r="I87" s="10">
-        <v>-15.4</v>
-      </c>
-      <c r="J87" s="10">
-        <v>-18.399999999999999</v>
+        <v>0.8</v>
+      </c>
+      <c r="I87" s="8">
+        <v>-0.99</v>
+      </c>
+      <c r="J87" s="8">
+        <v>-29</v>
       </c>
       <c r="K87" s="9">
-        <v>5.77</v>
+        <v>6.57</v>
       </c>
       <c r="L87" s="8">
-        <v>3.44</v>
+        <v>-2.0099999999999998</v>
       </c>
       <c r="M87" s="9">
-        <v>0.80900000000000005</v>
-      </c>
-      <c r="N87" s="10">
-        <v>-15.4</v>
-      </c>
-      <c r="O87" s="10">
-        <v>-18.399999999999999</v>
+        <v>0.8</v>
+      </c>
+      <c r="N87" s="8">
+        <v>-0.99</v>
+      </c>
+      <c r="O87" s="8">
+        <v>-29</v>
       </c>
       <c r="P87" s="9">
-        <v>5.77</v>
+        <v>6.57</v>
       </c>
       <c r="Q87" s="8">
-        <v>3.44</v>
+        <v>-2.0099999999999998</v>
       </c>
     </row>
     <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
-        <v>42156</v>
+        <v>42186</v>
       </c>
       <c r="B88" s="7">
-        <v>17.149999999999999</v>
+        <v>17.350000000000001</v>
       </c>
       <c r="C88" s="7">
-        <v>17.350000000000001</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="D88" s="7">
-        <v>18</v>
+        <v>17.3</v>
       </c>
       <c r="E88" s="7">
-        <v>17</v>
+        <v>16.05</v>
       </c>
       <c r="F88" s="8">
-        <v>0.2</v>
+        <v>-1.2</v>
       </c>
       <c r="G88" s="8">
-        <v>1.17</v>
+        <v>-6.92</v>
       </c>
       <c r="H88" s="9">
-        <v>0.98599999999999999</v>
+        <v>0.80900000000000005</v>
       </c>
       <c r="I88" s="8">
-        <v>9.7100000000000009</v>
-      </c>
-      <c r="J88" s="10">
-        <v>-3.99</v>
+        <v>-15.4</v>
+      </c>
+      <c r="J88" s="8">
+        <v>-18.399999999999999</v>
       </c>
       <c r="K88" s="9">
-        <v>4.96</v>
-      </c>
-      <c r="L88" s="8">
-        <v>3.53</v>
+        <v>5.77</v>
+      </c>
+      <c r="L88" s="10">
+        <v>3.44</v>
       </c>
       <c r="M88" s="9">
-        <v>0.98599999999999999</v>
+        <v>0.80900000000000005</v>
       </c>
       <c r="N88" s="8">
-        <v>9.7100000000000009</v>
-      </c>
-      <c r="O88" s="10">
-        <v>-3.99</v>
+        <v>-15.4</v>
+      </c>
+      <c r="O88" s="8">
+        <v>-18.399999999999999</v>
       </c>
       <c r="P88" s="9">
-        <v>4.96</v>
-      </c>
-      <c r="Q88" s="8">
-        <v>3.53</v>
+        <v>5.77</v>
+      </c>
+      <c r="Q88" s="10">
+        <v>3.44</v>
       </c>
     </row>
     <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
-        <v>42125</v>
+        <v>42156</v>
       </c>
       <c r="B89" s="7">
-        <v>18.7</v>
+        <v>17.149999999999999</v>
       </c>
       <c r="C89" s="7">
-        <v>17.149999999999999</v>
+        <v>17.350000000000001</v>
       </c>
       <c r="D89" s="7">
-        <v>18.7</v>
+        <v>18</v>
       </c>
       <c r="E89" s="7">
-        <v>16.95</v>
+        <v>17</v>
       </c>
       <c r="F89" s="10">
-        <v>-1.55</v>
+        <v>0.2</v>
       </c>
       <c r="G89" s="10">
-        <v>-8.2899999999999991</v>
+        <v>1.17</v>
       </c>
       <c r="H89" s="9">
-        <v>0.89900000000000002</v>
-      </c>
-      <c r="I89" s="8">
-        <v>4.82</v>
+        <v>0.98599999999999999</v>
+      </c>
+      <c r="I89" s="10">
+        <v>9.7100000000000009</v>
       </c>
       <c r="J89" s="8">
-        <v>6.17</v>
+        <v>-3.99</v>
       </c>
       <c r="K89" s="9">
-        <v>3.97</v>
-      </c>
-      <c r="L89" s="8">
-        <v>5.58</v>
+        <v>4.96</v>
+      </c>
+      <c r="L89" s="10">
+        <v>3.53</v>
       </c>
       <c r="M89" s="9">
-        <v>0.89900000000000002</v>
-      </c>
-      <c r="N89" s="8">
-        <v>4.82</v>
+        <v>0.98599999999999999</v>
+      </c>
+      <c r="N89" s="10">
+        <v>9.7100000000000009</v>
       </c>
       <c r="O89" s="8">
-        <v>6.17</v>
+        <v>-3.99</v>
       </c>
       <c r="P89" s="9">
-        <v>3.97</v>
-      </c>
-      <c r="Q89" s="8">
-        <v>5.58</v>
+        <v>4.96</v>
+      </c>
+      <c r="Q89" s="10">
+        <v>3.53</v>
       </c>
     </row>
     <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
-        <v>42095</v>
+        <v>42125</v>
       </c>
       <c r="B90" s="7">
-        <v>19.5</v>
+        <v>18.7</v>
       </c>
       <c r="C90" s="7">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="D90" s="7">
         <v>18.7</v>
       </c>
-      <c r="D90" s="7">
-        <v>19.399999999999999</v>
-      </c>
       <c r="E90" s="7">
-        <v>18.7</v>
-      </c>
-      <c r="F90" s="10">
-        <v>-0.8</v>
-      </c>
-      <c r="G90" s="10">
-        <v>-4.0999999999999996</v>
+        <v>16.95</v>
+      </c>
+      <c r="F90" s="8">
+        <v>-1.55</v>
+      </c>
+      <c r="G90" s="8">
+        <v>-8.2899999999999991</v>
       </c>
       <c r="H90" s="9">
-        <v>0.85699999999999998</v>
+        <v>0.89900000000000002</v>
       </c>
       <c r="I90" s="10">
-        <v>-8.1</v>
-      </c>
-      <c r="J90" s="8">
-        <v>20.9</v>
+        <v>4.82</v>
+      </c>
+      <c r="J90" s="10">
+        <v>6.17</v>
       </c>
       <c r="K90" s="9">
-        <v>3.07</v>
-      </c>
-      <c r="L90" s="8">
-        <v>5.41</v>
+        <v>3.97</v>
+      </c>
+      <c r="L90" s="10">
+        <v>5.58</v>
       </c>
       <c r="M90" s="9">
-        <v>0.85699999999999998</v>
+        <v>0.89900000000000002</v>
       </c>
       <c r="N90" s="10">
-        <v>-8.1</v>
-      </c>
-      <c r="O90" s="8">
-        <v>20.9</v>
+        <v>4.82</v>
+      </c>
+      <c r="O90" s="10">
+        <v>6.17</v>
       </c>
       <c r="P90" s="9">
-        <v>3.07</v>
-      </c>
-      <c r="Q90" s="8">
-        <v>5.41</v>
+        <v>3.97</v>
+      </c>
+      <c r="Q90" s="10">
+        <v>5.58</v>
       </c>
     </row>
     <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
-        <v>42064</v>
+        <v>42095</v>
       </c>
       <c r="B91" s="7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="C91" s="7">
-        <v>19.5</v>
+        <v>18.7</v>
       </c>
       <c r="D91" s="7">
-        <v>20.2</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="E91" s="7">
-        <v>19</v>
-      </c>
-      <c r="F91" s="10">
-        <v>-0.5</v>
-      </c>
-      <c r="G91" s="10">
-        <v>-2.5</v>
+        <v>18.7</v>
+      </c>
+      <c r="F91" s="8">
+        <v>-0.8</v>
+      </c>
+      <c r="G91" s="8">
+        <v>-4.0999999999999996</v>
       </c>
       <c r="H91" s="9">
-        <v>0.93300000000000005</v>
+        <v>0.85699999999999998</v>
       </c>
       <c r="I91" s="8">
-        <v>72.599999999999994</v>
-      </c>
-      <c r="J91" s="8">
-        <v>40.299999999999997</v>
+        <v>-8.1</v>
+      </c>
+      <c r="J91" s="10">
+        <v>20.9</v>
       </c>
       <c r="K91" s="9">
-        <v>2.21</v>
-      </c>
-      <c r="L91" s="8">
-        <v>0.43</v>
+        <v>3.07</v>
+      </c>
+      <c r="L91" s="10">
+        <v>5.41</v>
       </c>
       <c r="M91" s="9">
-        <v>0.93300000000000005</v>
+        <v>0.85699999999999998</v>
       </c>
       <c r="N91" s="8">
-        <v>72.599999999999994</v>
-      </c>
-      <c r="O91" s="8">
-        <v>40.299999999999997</v>
+        <v>-8.1</v>
+      </c>
+      <c r="O91" s="10">
+        <v>20.9</v>
       </c>
       <c r="P91" s="9">
-        <v>2.21</v>
-      </c>
-      <c r="Q91" s="8">
-        <v>0.43</v>
+        <v>3.07</v>
+      </c>
+      <c r="Q91" s="10">
+        <v>5.41</v>
       </c>
     </row>
     <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
-        <v>42036</v>
+        <v>42064</v>
       </c>
       <c r="B92" s="7">
-        <v>19.7</v>
+        <v>20</v>
       </c>
       <c r="C92" s="7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="D92" s="7">
-        <v>20.07</v>
+        <v>20.2</v>
       </c>
       <c r="E92" s="7">
-        <v>19.010000000000002</v>
+        <v>19</v>
       </c>
       <c r="F92" s="8">
-        <v>0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="G92" s="8">
-        <v>1.52</v>
+        <v>-2.5</v>
       </c>
       <c r="H92" s="9">
-        <v>0.54100000000000004</v>
+        <v>0.93300000000000005</v>
       </c>
       <c r="I92" s="10">
-        <v>-27</v>
+        <v>72.599999999999994</v>
       </c>
       <c r="J92" s="10">
-        <v>-38.799999999999997</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="K92" s="9">
-        <v>1.28</v>
+        <v>2.21</v>
       </c>
       <c r="L92" s="10">
-        <v>-16.8</v>
+        <v>0.43</v>
       </c>
       <c r="M92" s="9">
-        <v>0.54100000000000004</v>
+        <v>0.93300000000000005</v>
       </c>
       <c r="N92" s="10">
-        <v>-27</v>
+        <v>72.599999999999994</v>
       </c>
       <c r="O92" s="10">
-        <v>-38.799999999999997</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="P92" s="9">
-        <v>1.28</v>
+        <v>2.21</v>
       </c>
       <c r="Q92" s="10">
-        <v>-16.8</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
-        <v>42005</v>
+        <v>42036</v>
       </c>
       <c r="B93" s="7">
-        <v>20.9</v>
+        <v>19.7</v>
       </c>
       <c r="C93" s="7">
-        <v>19.7</v>
+        <v>20</v>
       </c>
       <c r="D93" s="7">
-        <v>21.28</v>
+        <v>20.07</v>
       </c>
       <c r="E93" s="7">
         <v>19.010000000000002</v>
       </c>
       <c r="F93" s="10">
-        <v>-1.2</v>
+        <v>0.3</v>
       </c>
       <c r="G93" s="10">
-        <v>-5.74</v>
+        <v>1.52</v>
       </c>
       <c r="H93" s="9">
-        <v>0.74099999999999999</v>
-      </c>
-      <c r="I93" s="10">
-        <v>-15.2</v>
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="I93" s="8">
+        <v>-27</v>
       </c>
       <c r="J93" s="8">
-        <v>12.9</v>
+        <v>-38.799999999999997</v>
       </c>
       <c r="K93" s="9">
-        <v>0.74099999999999999</v>
+        <v>1.28</v>
       </c>
       <c r="L93" s="8">
-        <v>12.9</v>
+        <v>-16.8</v>
       </c>
       <c r="M93" s="9">
-        <v>0.74099999999999999</v>
-      </c>
-      <c r="N93" s="10">
-        <v>-15.2</v>
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="N93" s="8">
+        <v>-27</v>
       </c>
       <c r="O93" s="8">
-        <v>12.9</v>
+        <v>-38.799999999999997</v>
       </c>
       <c r="P93" s="9">
-        <v>0.74099999999999999</v>
+        <v>1.28</v>
       </c>
       <c r="Q93" s="8">
-        <v>12.9</v>
+        <v>-16.8</v>
       </c>
     </row>
     <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
-        <v>41974</v>
+        <v>42005</v>
       </c>
       <c r="B94" s="7">
-        <v>18.809999999999999</v>
+        <v>20.9</v>
       </c>
       <c r="C94" s="7">
-        <v>20.9</v>
+        <v>19.7</v>
       </c>
       <c r="D94" s="7">
-        <v>21.99</v>
+        <v>21.28</v>
       </c>
       <c r="E94" s="7">
-        <v>18.73</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="F94" s="8">
-        <v>2.09</v>
+        <v>-1.2</v>
       </c>
       <c r="G94" s="8">
-        <v>11.11</v>
+        <v>-5.74</v>
       </c>
       <c r="H94" s="9">
-        <v>0.84</v>
+        <v>0.74099999999999999</v>
       </c>
       <c r="I94" s="8">
-        <v>2.34</v>
-      </c>
-      <c r="J94" s="8">
-        <v>13.7</v>
+        <v>-15.2</v>
+      </c>
+      <c r="J94" s="10">
+        <v>12.9</v>
       </c>
       <c r="K94" s="9">
-        <v>10</v>
-      </c>
-      <c r="L94" s="8">
-        <v>59.2</v>
+        <v>0.74099999999999999</v>
+      </c>
+      <c r="L94" s="10">
+        <v>12.9</v>
       </c>
       <c r="M94" s="9">
-        <v>0.84</v>
+        <v>0.74099999999999999</v>
       </c>
       <c r="N94" s="8">
-        <v>2.34</v>
-      </c>
-      <c r="O94" s="8">
-        <v>13.7</v>
+        <v>-15.2</v>
+      </c>
+      <c r="O94" s="10">
+        <v>12.9</v>
       </c>
       <c r="P94" s="9">
-        <v>10</v>
-      </c>
-      <c r="Q94" s="8">
-        <v>59.2</v>
+        <v>0.74099999999999999</v>
+      </c>
+      <c r="Q94" s="10">
+        <v>12.9</v>
       </c>
     </row>
     <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
-        <v>41944</v>
+        <v>41974</v>
       </c>
       <c r="B95" s="7">
-        <v>19.059999999999999</v>
+        <v>18.809999999999999</v>
       </c>
       <c r="C95" s="7">
-        <v>18.809999999999999</v>
+        <v>20.9</v>
       </c>
       <c r="D95" s="7">
-        <v>19.5</v>
+        <v>21.99</v>
       </c>
       <c r="E95" s="7">
-        <v>18.809999999999999</v>
+        <v>18.73</v>
       </c>
       <c r="F95" s="10">
-        <v>-0.25</v>
+        <v>2.09</v>
       </c>
       <c r="G95" s="10">
-        <v>-1.31</v>
+        <v>11.11</v>
       </c>
       <c r="H95" s="9">
-        <v>0.79400000000000004</v>
-      </c>
-      <c r="I95" s="8">
-        <v>3.89</v>
-      </c>
-      <c r="J95" s="8">
-        <v>42.7</v>
+        <v>0.84</v>
+      </c>
+      <c r="I95" s="10">
+        <v>2.34</v>
+      </c>
+      <c r="J95" s="10">
+        <v>13.7</v>
       </c>
       <c r="K95" s="9">
-        <v>9.16</v>
-      </c>
-      <c r="L95" s="8">
-        <v>65.2</v>
+        <v>10</v>
+      </c>
+      <c r="L95" s="10">
+        <v>59.2</v>
       </c>
       <c r="M95" s="9">
-        <v>0.79400000000000004</v>
-      </c>
-      <c r="N95" s="8">
-        <v>3.89</v>
-      </c>
-      <c r="O95" s="8">
-        <v>42.7</v>
+        <v>0.84</v>
+      </c>
+      <c r="N95" s="10">
+        <v>2.34</v>
+      </c>
+      <c r="O95" s="10">
+        <v>13.7</v>
       </c>
       <c r="P95" s="9">
-        <v>9.16</v>
-      </c>
-      <c r="Q95" s="8">
-        <v>65.2</v>
+        <v>10</v>
+      </c>
+      <c r="Q95" s="10">
+        <v>59.2</v>
       </c>
     </row>
     <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
-        <v>41913</v>
+        <v>41944</v>
       </c>
       <c r="B96" s="7">
-        <v>22.9</v>
+        <v>19.059999999999999</v>
       </c>
       <c r="C96" s="7">
-        <v>19.059999999999999</v>
+        <v>18.809999999999999</v>
       </c>
       <c r="D96" s="7">
-        <v>22.66</v>
+        <v>19.5</v>
       </c>
       <c r="E96" s="7">
-        <v>19</v>
-      </c>
-      <c r="F96" s="10">
-        <v>-3.84</v>
-      </c>
-      <c r="G96" s="10">
-        <v>-16.77</v>
+        <v>18.809999999999999</v>
+      </c>
+      <c r="F96" s="8">
+        <v>-0.25</v>
+      </c>
+      <c r="G96" s="8">
+        <v>-1.31</v>
       </c>
       <c r="H96" s="9">
-        <v>0.745</v>
+        <v>0.79400000000000004</v>
       </c>
       <c r="I96" s="10">
-        <v>-19.2</v>
-      </c>
-      <c r="J96" s="8">
-        <v>23.7</v>
+        <v>3.89</v>
+      </c>
+      <c r="J96" s="10">
+        <v>42.7</v>
       </c>
       <c r="K96" s="9">
-        <v>8.36</v>
-      </c>
-      <c r="L96" s="8">
-        <v>67.7</v>
+        <v>9.16</v>
+      </c>
+      <c r="L96" s="10">
+        <v>65.2</v>
       </c>
       <c r="M96" s="9">
-        <v>0.745</v>
+        <v>0.79400000000000004</v>
       </c>
       <c r="N96" s="10">
-        <v>-19.2</v>
-      </c>
-      <c r="O96" s="8">
-        <v>23.7</v>
+        <v>3.89</v>
+      </c>
+      <c r="O96" s="10">
+        <v>42.7</v>
       </c>
       <c r="P96" s="9">
-        <v>8.36</v>
-      </c>
-      <c r="Q96" s="8">
-        <v>67.7</v>
+        <v>9.16</v>
+      </c>
+      <c r="Q96" s="10">
+        <v>65.2</v>
       </c>
     </row>
     <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
-        <v>41883</v>
+        <v>41913</v>
       </c>
       <c r="B97" s="7">
-        <v>26.49</v>
+        <v>22.9</v>
       </c>
       <c r="C97" s="7">
-        <v>22.9</v>
+        <v>19.059999999999999</v>
       </c>
       <c r="D97" s="7">
-        <v>32</v>
+        <v>22.66</v>
       </c>
       <c r="E97" s="7">
-        <v>22</v>
-      </c>
-      <c r="F97" s="10">
-        <v>-4.59</v>
-      </c>
-      <c r="G97" s="10">
-        <v>-16.7</v>
+        <v>19</v>
+      </c>
+      <c r="F97" s="8">
+        <v>-3.84</v>
+      </c>
+      <c r="G97" s="8">
+        <v>-16.77</v>
       </c>
       <c r="H97" s="9">
-        <v>0.91700000000000004</v>
-      </c>
-      <c r="I97" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J97" s="8">
-        <v>63.2</v>
+        <v>0.745</v>
+      </c>
+      <c r="I97" s="8">
+        <v>-19.2</v>
+      </c>
+      <c r="J97" s="10">
+        <v>23.7</v>
       </c>
       <c r="K97" s="9">
-        <v>7.62</v>
-      </c>
-      <c r="L97" s="8">
-        <v>73.8</v>
+        <v>8.36</v>
+      </c>
+      <c r="L97" s="10">
+        <v>67.7</v>
       </c>
       <c r="M97" s="9">
-        <v>0.91700000000000004</v>
-      </c>
-      <c r="N97" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O97" s="8">
-        <v>63.2</v>
+        <v>0.745</v>
+      </c>
+      <c r="N97" s="8">
+        <v>-19.2</v>
+      </c>
+      <c r="O97" s="10">
+        <v>23.7</v>
       </c>
       <c r="P97" s="9">
-        <v>7.62</v>
-      </c>
-      <c r="Q97" s="8">
-        <v>73.8</v>
+        <v>8.36</v>
+      </c>
+      <c r="Q97" s="10">
+        <v>67.7</v>
       </c>
     </row>
     <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
-        <v>41852</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E98" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F98" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G98" s="9" t="s">
-        <v>17</v>
+        <v>41883</v>
+      </c>
+      <c r="B98" s="7">
+        <v>26.49</v>
+      </c>
+      <c r="C98" s="7">
+        <v>22.9</v>
+      </c>
+      <c r="D98" s="7">
+        <v>32</v>
+      </c>
+      <c r="E98" s="7">
+        <v>22</v>
+      </c>
+      <c r="F98" s="8">
+        <v>-4.59</v>
+      </c>
+      <c r="G98" s="8">
+        <v>-16.7</v>
       </c>
       <c r="H98" s="9">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="I98" s="10">
-        <v>-5.84</v>
-      </c>
-      <c r="J98" s="8">
-        <v>119.1</v>
+        <v>0.91700000000000004</v>
+      </c>
+      <c r="I98" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J98" s="10">
+        <v>63.2</v>
       </c>
       <c r="K98" s="9">
-        <v>6.7</v>
-      </c>
-      <c r="L98" s="8">
-        <v>76.900000000000006</v>
+        <v>7.62</v>
+      </c>
+      <c r="L98" s="10">
+        <v>73.8</v>
       </c>
       <c r="M98" s="9">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="N98" s="10">
-        <v>-5.84</v>
-      </c>
-      <c r="O98" s="8">
-        <v>119.1</v>
+        <v>0.91700000000000004</v>
+      </c>
+      <c r="N98" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O98" s="10">
+        <v>63.2</v>
       </c>
       <c r="P98" s="9">
-        <v>6.7</v>
-      </c>
-      <c r="Q98" s="8">
-        <v>76.900000000000006</v>
+        <v>7.62</v>
+      </c>
+      <c r="Q98" s="10">
+        <v>73.8</v>
       </c>
     </row>
     <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
-        <v>41821</v>
+        <v>41852</v>
       </c>
       <c r="B99" s="7" t="s">
         <v>17</v>
@@ -6386,39 +6386,39 @@
         <v>17</v>
       </c>
       <c r="H99" s="9">
-        <v>0.99099999999999999</v>
-      </c>
-      <c r="I99" s="10">
-        <v>-7.7</v>
-      </c>
-      <c r="J99" s="8">
-        <v>72.400000000000006</v>
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="I99" s="8">
+        <v>-5.84</v>
+      </c>
+      <c r="J99" s="10">
+        <v>119.1</v>
       </c>
       <c r="K99" s="9">
-        <v>5.57</v>
-      </c>
-      <c r="L99" s="8">
-        <v>70.2</v>
+        <v>6.7</v>
+      </c>
+      <c r="L99" s="10">
+        <v>76.900000000000006</v>
       </c>
       <c r="M99" s="9">
-        <v>0.99099999999999999</v>
-      </c>
-      <c r="N99" s="10">
-        <v>-7.7</v>
-      </c>
-      <c r="O99" s="8">
-        <v>72.400000000000006</v>
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="N99" s="8">
+        <v>-5.84</v>
+      </c>
+      <c r="O99" s="10">
+        <v>119.1</v>
       </c>
       <c r="P99" s="9">
-        <v>5.57</v>
-      </c>
-      <c r="Q99" s="8">
-        <v>70.2</v>
+        <v>6.7</v>
+      </c>
+      <c r="Q99" s="10">
+        <v>76.900000000000006</v>
       </c>
     </row>
     <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
-        <v>41791</v>
+        <v>41821</v>
       </c>
       <c r="B100" s="7" t="s">
         <v>17</v>
@@ -6439,39 +6439,39 @@
         <v>17</v>
       </c>
       <c r="H100" s="9">
-        <v>1.03</v>
+        <v>0.99099999999999999</v>
       </c>
       <c r="I100" s="8">
-        <v>22.7</v>
-      </c>
-      <c r="J100" s="8">
-        <v>102.9</v>
+        <v>-7.7</v>
+      </c>
+      <c r="J100" s="10">
+        <v>72.400000000000006</v>
       </c>
       <c r="K100" s="9">
-        <v>4.79</v>
-      </c>
-      <c r="L100" s="8">
-        <v>77.400000000000006</v>
+        <v>5.57</v>
+      </c>
+      <c r="L100" s="10">
+        <v>70.2</v>
       </c>
       <c r="M100" s="9">
-        <v>1.03</v>
+        <v>0.99099999999999999</v>
       </c>
       <c r="N100" s="8">
-        <v>22.7</v>
-      </c>
-      <c r="O100" s="8">
-        <v>102.9</v>
+        <v>-7.7</v>
+      </c>
+      <c r="O100" s="10">
+        <v>72.400000000000006</v>
       </c>
       <c r="P100" s="9">
-        <v>4.79</v>
-      </c>
-      <c r="Q100" s="8">
-        <v>77.400000000000006</v>
+        <v>5.57</v>
+      </c>
+      <c r="Q100" s="10">
+        <v>70.2</v>
       </c>
     </row>
     <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
-        <v>41760</v>
+        <v>41791</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>17</v>
@@ -6492,39 +6492,39 @@
         <v>17</v>
       </c>
       <c r="H101" s="9">
-        <v>0.84599999999999997</v>
-      </c>
-      <c r="I101" s="8">
-        <v>10.1</v>
-      </c>
-      <c r="J101" s="8">
-        <v>67.400000000000006</v>
+        <v>1.03</v>
+      </c>
+      <c r="I101" s="10">
+        <v>22.7</v>
+      </c>
+      <c r="J101" s="10">
+        <v>102.9</v>
       </c>
       <c r="K101" s="9">
-        <v>3.76</v>
-      </c>
-      <c r="L101" s="8">
-        <v>71.5</v>
+        <v>4.79</v>
+      </c>
+      <c r="L101" s="10">
+        <v>77.400000000000006</v>
       </c>
       <c r="M101" s="9">
-        <v>0.84599999999999997</v>
-      </c>
-      <c r="N101" s="8">
-        <v>10.1</v>
-      </c>
-      <c r="O101" s="8">
-        <v>67.400000000000006</v>
+        <v>1.03</v>
+      </c>
+      <c r="N101" s="10">
+        <v>22.7</v>
+      </c>
+      <c r="O101" s="10">
+        <v>102.9</v>
       </c>
       <c r="P101" s="9">
-        <v>3.76</v>
-      </c>
-      <c r="Q101" s="8">
-        <v>71.5</v>
+        <v>4.79</v>
+      </c>
+      <c r="Q101" s="10">
+        <v>77.400000000000006</v>
       </c>
     </row>
     <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
-        <v>41730</v>
+        <v>41760</v>
       </c>
       <c r="B102" s="7" t="s">
         <v>17</v>
@@ -6545,39 +6545,39 @@
         <v>17</v>
       </c>
       <c r="H102" s="9">
-        <v>0.70899999999999996</v>
-      </c>
-      <c r="I102" s="8">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="J102" s="8">
-        <v>46.7</v>
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="I102" s="10">
+        <v>10.1</v>
+      </c>
+      <c r="J102" s="10">
+        <v>67.400000000000006</v>
       </c>
       <c r="K102" s="9">
-        <v>2.91</v>
-      </c>
-      <c r="L102" s="8">
-        <v>72.7</v>
+        <v>3.76</v>
+      </c>
+      <c r="L102" s="10">
+        <v>71.5</v>
       </c>
       <c r="M102" s="9">
-        <v>0.70899999999999996</v>
-      </c>
-      <c r="N102" s="8">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="O102" s="8">
-        <v>46.7</v>
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="N102" s="10">
+        <v>10.1</v>
+      </c>
+      <c r="O102" s="10">
+        <v>67.400000000000006</v>
       </c>
       <c r="P102" s="9">
-        <v>2.91</v>
-      </c>
-      <c r="Q102" s="8">
-        <v>72.7</v>
+        <v>3.76</v>
+      </c>
+      <c r="Q102" s="10">
+        <v>71.5</v>
       </c>
     </row>
     <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
-        <v>41699</v>
+        <v>41730</v>
       </c>
       <c r="B103" s="7" t="s">
         <v>17</v>
@@ -6598,39 +6598,39 @@
         <v>17</v>
       </c>
       <c r="H103" s="9">
-        <v>0.66500000000000004</v>
+        <v>0.70899999999999996</v>
       </c>
       <c r="I103" s="10">
-        <v>-22.5</v>
-      </c>
-      <c r="J103" s="8">
-        <v>44.9</v>
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="J103" s="10">
+        <v>46.7</v>
       </c>
       <c r="K103" s="9">
-        <v>2.21</v>
-      </c>
-      <c r="L103" s="8">
-        <v>83.1</v>
+        <v>2.91</v>
+      </c>
+      <c r="L103" s="10">
+        <v>72.7</v>
       </c>
       <c r="M103" s="9">
-        <v>0.66500000000000004</v>
+        <v>0.70899999999999996</v>
       </c>
       <c r="N103" s="10">
-        <v>-22.5</v>
-      </c>
-      <c r="O103" s="8">
-        <v>44.9</v>
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="O103" s="10">
+        <v>46.7</v>
       </c>
       <c r="P103" s="9">
-        <v>2.21</v>
-      </c>
-      <c r="Q103" s="8">
-        <v>83.1</v>
+        <v>2.91</v>
+      </c>
+      <c r="Q103" s="10">
+        <v>72.7</v>
       </c>
     </row>
     <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
-        <v>41671</v>
+        <v>41699</v>
       </c>
       <c r="B104" s="7" t="s">
         <v>17</v>
@@ -6651,39 +6651,39 @@
         <v>17</v>
       </c>
       <c r="H104" s="9">
-        <v>0.88400000000000001</v>
+        <v>0.66500000000000004</v>
       </c>
       <c r="I104" s="8">
-        <v>36</v>
-      </c>
-      <c r="J104" s="8">
-        <v>161.9</v>
+        <v>-22.5</v>
+      </c>
+      <c r="J104" s="10">
+        <v>44.9</v>
       </c>
       <c r="K104" s="9">
-        <v>1.54</v>
-      </c>
-      <c r="L104" s="8">
-        <v>106.7</v>
+        <v>2.21</v>
+      </c>
+      <c r="L104" s="10">
+        <v>83.1</v>
       </c>
       <c r="M104" s="9">
-        <v>0.88400000000000001</v>
+        <v>0.66500000000000004</v>
       </c>
       <c r="N104" s="8">
-        <v>36</v>
-      </c>
-      <c r="O104" s="8">
-        <v>161.9</v>
+        <v>-22.5</v>
+      </c>
+      <c r="O104" s="10">
+        <v>44.9</v>
       </c>
       <c r="P104" s="9">
-        <v>1.54</v>
-      </c>
-      <c r="Q104" s="8">
-        <v>106.7</v>
+        <v>2.21</v>
+      </c>
+      <c r="Q104" s="10">
+        <v>83.1</v>
       </c>
     </row>
     <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
-        <v>41640</v>
+        <v>41671</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>17</v>
@@ -6704,39 +6704,39 @@
         <v>17</v>
       </c>
       <c r="H105" s="9">
-        <v>0.65600000000000003</v>
+        <v>0.88400000000000001</v>
       </c>
       <c r="I105" s="10">
-        <v>-11.9</v>
-      </c>
-      <c r="J105" s="8">
-        <v>60.9</v>
+        <v>36</v>
+      </c>
+      <c r="J105" s="10">
+        <v>161.9</v>
       </c>
       <c r="K105" s="9">
-        <v>0.65600000000000003</v>
-      </c>
-      <c r="L105" s="8">
-        <v>60.9</v>
+        <v>1.54</v>
+      </c>
+      <c r="L105" s="10">
+        <v>106.7</v>
       </c>
       <c r="M105" s="9">
-        <v>0.65600000000000003</v>
+        <v>0.88400000000000001</v>
       </c>
       <c r="N105" s="10">
-        <v>-11.9</v>
-      </c>
-      <c r="O105" s="8">
-        <v>60.9</v>
+        <v>36</v>
+      </c>
+      <c r="O105" s="10">
+        <v>161.9</v>
       </c>
       <c r="P105" s="9">
-        <v>0.65600000000000003</v>
-      </c>
-      <c r="Q105" s="8">
-        <v>60.9</v>
+        <v>1.54</v>
+      </c>
+      <c r="Q105" s="10">
+        <v>106.7</v>
       </c>
     </row>
     <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
-        <v>41609</v>
+        <v>41640</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>17</v>
@@ -6757,39 +6757,39 @@
         <v>17</v>
       </c>
       <c r="H106" s="9">
-        <v>0.73899999999999999</v>
+        <v>0.65600000000000003</v>
       </c>
       <c r="I106" s="8">
-        <v>35.4</v>
-      </c>
-      <c r="J106" s="8">
-        <v>94.3</v>
+        <v>-11.9</v>
+      </c>
+      <c r="J106" s="10">
+        <v>60.9</v>
       </c>
       <c r="K106" s="9">
-        <v>6.28</v>
-      </c>
-      <c r="L106" s="8">
-        <v>44.6</v>
+        <v>0.65600000000000003</v>
+      </c>
+      <c r="L106" s="10">
+        <v>60.9</v>
       </c>
       <c r="M106" s="9">
-        <v>0.73899999999999999</v>
+        <v>0.65600000000000003</v>
       </c>
       <c r="N106" s="8">
-        <v>35.4</v>
-      </c>
-      <c r="O106" s="8">
-        <v>94.3</v>
+        <v>-11.9</v>
+      </c>
+      <c r="O106" s="10">
+        <v>60.9</v>
       </c>
       <c r="P106" s="9">
-        <v>6.28</v>
-      </c>
-      <c r="Q106" s="8">
-        <v>44.6</v>
+        <v>0.65600000000000003</v>
+      </c>
+      <c r="Q106" s="10">
+        <v>60.9</v>
       </c>
     </row>
     <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
-        <v>41579</v>
+        <v>41609</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>17</v>
@@ -6810,39 +6810,39 @@
         <v>17</v>
       </c>
       <c r="H107" s="9">
-        <v>0.54600000000000004</v>
+        <v>0.73899999999999999</v>
       </c>
       <c r="I107" s="10">
-        <v>-11.1</v>
-      </c>
-      <c r="J107" s="8">
-        <v>43.1</v>
+        <v>35.4</v>
+      </c>
+      <c r="J107" s="10">
+        <v>94.3</v>
       </c>
       <c r="K107" s="9">
-        <v>5.53</v>
-      </c>
-      <c r="L107" s="8">
-        <v>39.5</v>
+        <v>6.28</v>
+      </c>
+      <c r="L107" s="10">
+        <v>44.6</v>
       </c>
       <c r="M107" s="9">
-        <v>0.55600000000000005</v>
+        <v>0.73899999999999999</v>
       </c>
       <c r="N107" s="10">
-        <v>-9.4</v>
-      </c>
-      <c r="O107" s="8">
-        <v>45.9</v>
+        <v>35.4</v>
+      </c>
+      <c r="O107" s="10">
+        <v>94.3</v>
       </c>
       <c r="P107" s="9">
-        <v>5.54</v>
-      </c>
-      <c r="Q107" s="8">
-        <v>39.799999999999997</v>
+        <v>6.28</v>
+      </c>
+      <c r="Q107" s="10">
+        <v>44.6</v>
       </c>
     </row>
     <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
-        <v>41548</v>
+        <v>41579</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>17</v>
@@ -6863,39 +6863,39 @@
         <v>17</v>
       </c>
       <c r="H108" s="9">
-        <v>0.61399999999999999</v>
+        <v>0.54600000000000004</v>
       </c>
       <c r="I108" s="8">
-        <v>5.83</v>
-      </c>
-      <c r="J108" s="8">
-        <v>43.4</v>
+        <v>-11.1</v>
+      </c>
+      <c r="J108" s="10">
+        <v>43.1</v>
       </c>
       <c r="K108" s="9">
-        <v>4.9800000000000004</v>
-      </c>
-      <c r="L108" s="8">
-        <v>39.1</v>
+        <v>5.53</v>
+      </c>
+      <c r="L108" s="10">
+        <v>39.5</v>
       </c>
       <c r="M108" s="9">
-        <v>0.61399999999999999</v>
+        <v>0.55600000000000005</v>
       </c>
       <c r="N108" s="8">
-        <v>5.83</v>
-      </c>
-      <c r="O108" s="8">
-        <v>43.4</v>
+        <v>-9.4</v>
+      </c>
+      <c r="O108" s="10">
+        <v>45.9</v>
       </c>
       <c r="P108" s="9">
-        <v>4.9800000000000004</v>
-      </c>
-      <c r="Q108" s="8">
-        <v>39.1</v>
+        <v>5.54</v>
+      </c>
+      <c r="Q108" s="10">
+        <v>39.799999999999997</v>
       </c>
     </row>
     <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
-        <v>41518</v>
+        <v>41548</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>17</v>
@@ -6916,39 +6916,39 @@
         <v>17</v>
       </c>
       <c r="H109" s="9">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="I109" s="8">
-        <v>12.8</v>
-      </c>
-      <c r="J109" s="8">
-        <v>55.4</v>
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="I109" s="10">
+        <v>5.83</v>
+      </c>
+      <c r="J109" s="10">
+        <v>43.4</v>
       </c>
       <c r="K109" s="9">
-        <v>4.37</v>
-      </c>
-      <c r="L109" s="8">
-        <v>38.5</v>
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="L109" s="10">
+        <v>39.1</v>
       </c>
       <c r="M109" s="9">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="N109" s="8">
-        <v>12.8</v>
-      </c>
-      <c r="O109" s="8">
-        <v>55.4</v>
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="N109" s="10">
+        <v>5.83</v>
+      </c>
+      <c r="O109" s="10">
+        <v>43.4</v>
       </c>
       <c r="P109" s="9">
-        <v>4.37</v>
-      </c>
-      <c r="Q109" s="8">
-        <v>38.5</v>
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="Q109" s="10">
+        <v>39.1</v>
       </c>
     </row>
     <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
-        <v>41487</v>
+        <v>41518</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>17</v>
@@ -6969,39 +6969,39 @@
         <v>17</v>
       </c>
       <c r="H110" s="9">
-        <v>0.51400000000000001</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="I110" s="10">
-        <v>-10.5</v>
-      </c>
-      <c r="J110" s="8">
-        <v>14.4</v>
+        <v>12.8</v>
+      </c>
+      <c r="J110" s="10">
+        <v>55.4</v>
       </c>
       <c r="K110" s="9">
-        <v>3.79</v>
-      </c>
-      <c r="L110" s="8">
-        <v>36.200000000000003</v>
+        <v>4.37</v>
+      </c>
+      <c r="L110" s="10">
+        <v>38.5</v>
       </c>
       <c r="M110" s="9">
-        <v>0.51400000000000001</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="N110" s="10">
-        <v>-10.5</v>
-      </c>
-      <c r="O110" s="8">
-        <v>14.4</v>
+        <v>12.8</v>
+      </c>
+      <c r="O110" s="10">
+        <v>55.4</v>
       </c>
       <c r="P110" s="9">
-        <v>3.79</v>
-      </c>
-      <c r="Q110" s="8">
-        <v>36.200000000000003</v>
+        <v>4.37</v>
+      </c>
+      <c r="Q110" s="10">
+        <v>38.5</v>
       </c>
     </row>
     <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
-        <v>41456</v>
+        <v>41487</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>17</v>
@@ -7022,39 +7022,39 @@
         <v>17</v>
       </c>
       <c r="H111" s="9">
-        <v>0.57499999999999996</v>
+        <v>0.51400000000000001</v>
       </c>
       <c r="I111" s="8">
-        <v>13.6</v>
-      </c>
-      <c r="J111" s="8">
-        <v>81.400000000000006</v>
+        <v>-10.5</v>
+      </c>
+      <c r="J111" s="10">
+        <v>14.4</v>
       </c>
       <c r="K111" s="9">
-        <v>3.27</v>
-      </c>
-      <c r="L111" s="8">
-        <v>40.5</v>
+        <v>3.79</v>
+      </c>
+      <c r="L111" s="10">
+        <v>36.200000000000003</v>
       </c>
       <c r="M111" s="9">
-        <v>0.57499999999999996</v>
+        <v>0.51400000000000001</v>
       </c>
       <c r="N111" s="8">
-        <v>13.6</v>
-      </c>
-      <c r="O111" s="8">
-        <v>81.400000000000006</v>
+        <v>-10.5</v>
+      </c>
+      <c r="O111" s="10">
+        <v>14.4</v>
       </c>
       <c r="P111" s="9">
-        <v>3.27</v>
-      </c>
-      <c r="Q111" s="8">
-        <v>40.5</v>
+        <v>3.79</v>
+      </c>
+      <c r="Q111" s="10">
+        <v>36.200000000000003</v>
       </c>
     </row>
     <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
-        <v>41426</v>
+        <v>41456</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>17</v>
@@ -7075,39 +7075,39 @@
         <v>17</v>
       </c>
       <c r="H112" s="9">
-        <v>0.50600000000000001</v>
-      </c>
-      <c r="I112" s="8">
-        <v>0.11</v>
-      </c>
-      <c r="J112" s="8">
-        <v>39.799999999999997</v>
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="I112" s="10">
+        <v>13.6</v>
+      </c>
+      <c r="J112" s="10">
+        <v>81.400000000000006</v>
       </c>
       <c r="K112" s="9">
-        <v>2.7</v>
-      </c>
-      <c r="L112" s="8">
-        <v>34.6</v>
+        <v>3.27</v>
+      </c>
+      <c r="L112" s="10">
+        <v>40.5</v>
       </c>
       <c r="M112" s="9">
-        <v>0.50600000000000001</v>
-      </c>
-      <c r="N112" s="8">
-        <v>0.11</v>
-      </c>
-      <c r="O112" s="8">
-        <v>39.799999999999997</v>
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="N112" s="10">
+        <v>13.6</v>
+      </c>
+      <c r="O112" s="10">
+        <v>81.400000000000006</v>
       </c>
       <c r="P112" s="9">
-        <v>2.7</v>
-      </c>
-      <c r="Q112" s="8">
-        <v>34.6</v>
+        <v>3.27</v>
+      </c>
+      <c r="Q112" s="10">
+        <v>40.5</v>
       </c>
     </row>
     <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
-        <v>41395</v>
+        <v>41426</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>17</v>
@@ -7130,37 +7130,37 @@
       <c r="H113" s="9">
         <v>0.50600000000000001</v>
       </c>
-      <c r="I113" s="8">
-        <v>4.63</v>
-      </c>
-      <c r="J113" s="8">
-        <v>35.799999999999997</v>
+      <c r="I113" s="10">
+        <v>0.11</v>
+      </c>
+      <c r="J113" s="10">
+        <v>39.799999999999997</v>
       </c>
       <c r="K113" s="9">
-        <v>2.19</v>
-      </c>
-      <c r="L113" s="8">
-        <v>33.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="L113" s="10">
+        <v>34.6</v>
       </c>
       <c r="M113" s="9">
         <v>0.50600000000000001</v>
       </c>
-      <c r="N113" s="8">
-        <v>4.63</v>
-      </c>
-      <c r="O113" s="8">
-        <v>35.799999999999997</v>
+      <c r="N113" s="10">
+        <v>0.11</v>
+      </c>
+      <c r="O113" s="10">
+        <v>39.799999999999997</v>
       </c>
       <c r="P113" s="9">
-        <v>2.19</v>
-      </c>
-      <c r="Q113" s="8">
-        <v>33.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="Q113" s="10">
+        <v>34.6</v>
       </c>
     </row>
     <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
-        <v>41365</v>
+        <v>41395</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>17</v>
@@ -7181,39 +7181,39 @@
         <v>17</v>
       </c>
       <c r="H114" s="9">
-        <v>0.48299999999999998</v>
-      </c>
-      <c r="I114" s="8">
-        <v>5.31</v>
-      </c>
-      <c r="J114" s="8">
-        <v>31</v>
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="I114" s="10">
+        <v>4.63</v>
+      </c>
+      <c r="J114" s="10">
+        <v>35.799999999999997</v>
       </c>
       <c r="K114" s="9">
-        <v>1.69</v>
-      </c>
-      <c r="L114" s="8">
-        <v>32.700000000000003</v>
+        <v>2.19</v>
+      </c>
+      <c r="L114" s="10">
+        <v>33.4</v>
       </c>
       <c r="M114" s="9">
-        <v>0.48299999999999998</v>
-      </c>
-      <c r="N114" s="8">
-        <v>5.31</v>
-      </c>
-      <c r="O114" s="8">
-        <v>31</v>
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="N114" s="10">
+        <v>4.63</v>
+      </c>
+      <c r="O114" s="10">
+        <v>35.799999999999997</v>
       </c>
       <c r="P114" s="9">
-        <v>1.69</v>
-      </c>
-      <c r="Q114" s="8">
-        <v>32.700000000000003</v>
+        <v>2.19</v>
+      </c>
+      <c r="Q114" s="10">
+        <v>33.4</v>
       </c>
     </row>
     <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
-        <v>41334</v>
+        <v>41365</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>17</v>
@@ -7234,39 +7234,39 @@
         <v>17</v>
       </c>
       <c r="H115" s="9">
-        <v>0.45900000000000002</v>
-      </c>
-      <c r="I115" s="8">
-        <v>35.9</v>
-      </c>
-      <c r="J115" s="8">
-        <v>7.49</v>
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="I115" s="10">
+        <v>5.31</v>
+      </c>
+      <c r="J115" s="10">
+        <v>31</v>
       </c>
       <c r="K115" s="9">
-        <v>1.2</v>
-      </c>
-      <c r="L115" s="8">
-        <v>32.200000000000003</v>
+        <v>1.69</v>
+      </c>
+      <c r="L115" s="10">
+        <v>32.700000000000003</v>
       </c>
       <c r="M115" s="9">
-        <v>0.45900000000000002</v>
-      </c>
-      <c r="N115" s="8">
-        <v>35.9</v>
-      </c>
-      <c r="O115" s="8">
-        <v>7.49</v>
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="N115" s="10">
+        <v>5.31</v>
+      </c>
+      <c r="O115" s="10">
+        <v>31</v>
       </c>
       <c r="P115" s="9">
-        <v>1.2</v>
-      </c>
-      <c r="Q115" s="8">
-        <v>32.200000000000003</v>
+        <v>1.69</v>
+      </c>
+      <c r="Q115" s="10">
+        <v>32.700000000000003</v>
       </c>
     </row>
     <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
-        <v>41306</v>
+        <v>41334</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>17</v>
@@ -7287,39 +7287,39 @@
         <v>17</v>
       </c>
       <c r="H116" s="9">
-        <v>0.33800000000000002</v>
+        <v>0.45900000000000002</v>
       </c>
       <c r="I116" s="10">
-        <v>-17.2</v>
-      </c>
-      <c r="J116" s="8">
-        <v>25.2</v>
+        <v>35.9</v>
+      </c>
+      <c r="J116" s="10">
+        <v>7.49</v>
       </c>
       <c r="K116" s="9">
-        <v>0.745</v>
-      </c>
-      <c r="L116" s="8">
-        <v>54.1</v>
+        <v>1.2</v>
+      </c>
+      <c r="L116" s="10">
+        <v>32.200000000000003</v>
       </c>
       <c r="M116" s="9">
-        <v>0.33800000000000002</v>
+        <v>0.45900000000000002</v>
       </c>
       <c r="N116" s="10">
-        <v>-17.2</v>
-      </c>
-      <c r="O116" s="8">
-        <v>25.2</v>
+        <v>35.9</v>
+      </c>
+      <c r="O116" s="10">
+        <v>7.49</v>
       </c>
       <c r="P116" s="9">
-        <v>0.745</v>
-      </c>
-      <c r="Q116" s="8">
-        <v>54.1</v>
+        <v>1.2</v>
+      </c>
+      <c r="Q116" s="10">
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
-        <v>41275</v>
+        <v>41306</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>17</v>
@@ -7340,39 +7340,39 @@
         <v>17</v>
       </c>
       <c r="H117" s="9">
-        <v>0.40799999999999997</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="I117" s="8">
-        <v>7.24</v>
-      </c>
-      <c r="J117" s="8">
-        <v>90.4</v>
+        <v>-17.2</v>
+      </c>
+      <c r="J117" s="10">
+        <v>25.2</v>
       </c>
       <c r="K117" s="9">
-        <v>0.40799999999999997</v>
-      </c>
-      <c r="L117" s="8">
-        <v>90.4</v>
+        <v>0.745</v>
+      </c>
+      <c r="L117" s="10">
+        <v>54.1</v>
       </c>
       <c r="M117" s="9">
-        <v>0.40799999999999997</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="N117" s="8">
-        <v>7.24</v>
-      </c>
-      <c r="O117" s="8">
-        <v>90.4</v>
+        <v>-17.2</v>
+      </c>
+      <c r="O117" s="10">
+        <v>25.2</v>
       </c>
       <c r="P117" s="9">
-        <v>0.40799999999999997</v>
-      </c>
-      <c r="Q117" s="8">
-        <v>90.4</v>
+        <v>0.745</v>
+      </c>
+      <c r="Q117" s="10">
+        <v>54.1</v>
       </c>
     </row>
     <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
-        <v>41244</v>
+        <v>41275</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>17</v>
@@ -7393,39 +7393,39 @@
         <v>17</v>
       </c>
       <c r="H118" s="9">
-        <v>0.38</v>
+        <v>0.40799999999999997</v>
       </c>
       <c r="I118" s="10">
-        <v>-0.3</v>
-      </c>
-      <c r="J118" s="8">
-        <v>45.5</v>
+        <v>7.24</v>
+      </c>
+      <c r="J118" s="10">
+        <v>90.4</v>
       </c>
       <c r="K118" s="9">
-        <v>4.34</v>
-      </c>
-      <c r="L118" s="8">
-        <v>2.92</v>
-      </c>
-      <c r="M118" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="N118" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O118" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P118" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q118" s="9" t="s">
-        <v>17</v>
+        <v>0.40799999999999997</v>
+      </c>
+      <c r="L118" s="10">
+        <v>90.4</v>
+      </c>
+      <c r="M118" s="9">
+        <v>0.40799999999999997</v>
+      </c>
+      <c r="N118" s="10">
+        <v>7.24</v>
+      </c>
+      <c r="O118" s="10">
+        <v>90.4</v>
+      </c>
+      <c r="P118" s="9">
+        <v>0.40799999999999997</v>
+      </c>
+      <c r="Q118" s="10">
+        <v>90.4</v>
       </c>
     </row>
     <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
-        <v>41214</v>
+        <v>41244</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>17</v>
@@ -7446,19 +7446,19 @@
         <v>17</v>
       </c>
       <c r="H119" s="9">
-        <v>0.38100000000000001</v>
-      </c>
-      <c r="I119" s="10">
-        <v>-10.9</v>
-      </c>
-      <c r="J119" s="8">
-        <v>48.6</v>
+        <v>0.38</v>
+      </c>
+      <c r="I119" s="8">
+        <v>-0.3</v>
+      </c>
+      <c r="J119" s="10">
+        <v>45.5</v>
       </c>
       <c r="K119" s="9">
-        <v>3.96</v>
-      </c>
-      <c r="L119" s="8">
-        <v>0.11</v>
+        <v>4.34</v>
+      </c>
+      <c r="L119" s="10">
+        <v>2.92</v>
       </c>
       <c r="M119" s="9" t="s">
         <v>17</v>
@@ -7478,7 +7478,7 @@
     </row>
     <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
-        <v>41183</v>
+        <v>41214</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>17</v>
@@ -7499,19 +7499,19 @@
         <v>17</v>
       </c>
       <c r="H120" s="9">
-        <v>0.42799999999999999</v>
+        <v>0.38100000000000001</v>
       </c>
       <c r="I120" s="8">
-        <v>14.7</v>
-      </c>
-      <c r="J120" s="8">
-        <v>78.099999999999994</v>
+        <v>-10.9</v>
+      </c>
+      <c r="J120" s="10">
+        <v>48.6</v>
       </c>
       <c r="K120" s="9">
-        <v>3.58</v>
+        <v>3.96</v>
       </c>
       <c r="L120" s="10">
-        <v>-3.24</v>
+        <v>0.11</v>
       </c>
       <c r="M120" s="9" t="s">
         <v>17</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
-        <v>41153</v>
+        <v>41183</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>17</v>
@@ -7552,19 +7552,19 @@
         <v>17</v>
       </c>
       <c r="H121" s="9">
-        <v>0.373</v>
+        <v>0.42799999999999999</v>
       </c>
       <c r="I121" s="10">
-        <v>-17</v>
-      </c>
-      <c r="J121" s="8">
-        <v>33.6</v>
+        <v>14.7</v>
+      </c>
+      <c r="J121" s="10">
+        <v>78.099999999999994</v>
       </c>
       <c r="K121" s="9">
-        <v>3.15</v>
-      </c>
-      <c r="L121" s="10">
-        <v>-8.8800000000000008</v>
+        <v>3.58</v>
+      </c>
+      <c r="L121" s="8">
+        <v>-3.24</v>
       </c>
       <c r="M121" s="9" t="s">
         <v>17</v>
@@ -7584,7 +7584,7 @@
     </row>
     <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
-        <v>41122</v>
+        <v>41153</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>17</v>
@@ -7605,19 +7605,19 @@
         <v>17</v>
       </c>
       <c r="H122" s="9">
-        <v>0.45</v>
+        <v>0.373</v>
       </c>
       <c r="I122" s="8">
-        <v>41.9</v>
-      </c>
-      <c r="J122" s="8">
-        <v>12.7</v>
+        <v>-17</v>
+      </c>
+      <c r="J122" s="10">
+        <v>33.6</v>
       </c>
       <c r="K122" s="9">
-        <v>2.78</v>
-      </c>
-      <c r="L122" s="10">
-        <v>-12.6</v>
+        <v>3.15</v>
+      </c>
+      <c r="L122" s="8">
+        <v>-8.8800000000000008</v>
       </c>
       <c r="M122" s="9" t="s">
         <v>17</v>
@@ -7637,7 +7637,7 @@
     </row>
     <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
-        <v>41091</v>
+        <v>41122</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>17</v>
@@ -7658,19 +7658,19 @@
         <v>17</v>
       </c>
       <c r="H123" s="9">
-        <v>0.317</v>
+        <v>0.45</v>
       </c>
       <c r="I123" s="10">
-        <v>-12.4</v>
+        <v>41.9</v>
       </c>
       <c r="J123" s="10">
-        <v>-8.73</v>
+        <v>12.7</v>
       </c>
       <c r="K123" s="9">
-        <v>2.33</v>
-      </c>
-      <c r="L123" s="10">
-        <v>-16.2</v>
+        <v>2.78</v>
+      </c>
+      <c r="L123" s="8">
+        <v>-12.6</v>
       </c>
       <c r="M123" s="9" t="s">
         <v>17</v>
@@ -7690,7 +7690,7 @@
     </row>
     <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
-        <v>41061</v>
+        <v>41091</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>17</v>
@@ -7711,19 +7711,19 @@
         <v>17</v>
       </c>
       <c r="H124" s="9">
-        <v>0.36199999999999999</v>
-      </c>
-      <c r="I124" s="10">
-        <v>-2.78</v>
-      </c>
-      <c r="J124" s="10">
-        <v>-9.4700000000000006</v>
+        <v>0.317</v>
+      </c>
+      <c r="I124" s="8">
+        <v>-12.4</v>
+      </c>
+      <c r="J124" s="8">
+        <v>-8.73</v>
       </c>
       <c r="K124" s="9">
-        <v>2.0099999999999998</v>
-      </c>
-      <c r="L124" s="10">
-        <v>-17.600000000000001</v>
+        <v>2.33</v>
+      </c>
+      <c r="L124" s="8">
+        <v>-16.2</v>
       </c>
       <c r="M124" s="9" t="s">
         <v>17</v>
@@ -7743,7 +7743,7 @@
     </row>
     <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
-        <v>41030</v>
+        <v>41061</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>17</v>
@@ -7764,19 +7764,19 @@
         <v>17</v>
       </c>
       <c r="H125" s="9">
-        <v>0.372</v>
+        <v>0.36199999999999999</v>
       </c>
       <c r="I125" s="8">
-        <v>0.98</v>
-      </c>
-      <c r="J125" s="10">
-        <v>-17.7</v>
+        <v>-2.78</v>
+      </c>
+      <c r="J125" s="8">
+        <v>-9.4700000000000006</v>
       </c>
       <c r="K125" s="9">
-        <v>1.64</v>
-      </c>
-      <c r="L125" s="10">
-        <v>-19.3</v>
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="L125" s="8">
+        <v>-17.600000000000001</v>
       </c>
       <c r="M125" s="9" t="s">
         <v>17</v>
@@ -7796,54 +7796,107 @@
     </row>
     <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
+        <v>41030</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H126" s="9">
+        <v>0.372</v>
+      </c>
+      <c r="I126" s="10">
+        <v>0.98</v>
+      </c>
+      <c r="J126" s="8">
+        <v>-17.7</v>
+      </c>
+      <c r="K126" s="9">
+        <v>1.64</v>
+      </c>
+      <c r="L126" s="8">
+        <v>-19.3</v>
+      </c>
+      <c r="M126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q126" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A127" s="6">
         <v>41000</v>
       </c>
-      <c r="B126" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C126" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D126" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E126" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F126" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G126" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H126" s="9">
+      <c r="B127" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E127" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F127" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G127" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H127" s="9">
         <v>0.36899999999999999</v>
       </c>
-      <c r="I126" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J126" s="10">
+      <c r="I127" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J127" s="8">
         <v>-8.41</v>
       </c>
-      <c r="K126" s="9">
+      <c r="K127" s="9">
         <v>1.27</v>
       </c>
-      <c r="L126" s="10">
+      <c r="L127" s="8">
         <v>-19.7</v>
       </c>
-      <c r="M126" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="N126" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O126" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P126" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q126" s="9" t="s">
+      <c r="M127" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N127" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O127" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P127" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q127" s="9" t="s">
         <v>17</v>
       </c>
     </row>
